--- a/FuzzyMatch/Lebanese_Villages_Matched_v6.xlsx
+++ b/FuzzyMatch/Lebanese_Villages_Matched_v6.xlsx
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="18">
@@ -80241,7 +80241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81209,29 +81209,29 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Kab Elias</t>
+          <t>Kaoutarite El-Riz</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Zahleh</t>
+          <t>Saida</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bekaa</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>كابوسية (زحلة) [75.0]</t>
+          <t>القنيطرة (قرى صيدا) [77.1]</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Kaoutarite El-Riz</t>
+          <t>Kaoutarite El-Siyad</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -81246,63 +81246,68 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>القنيطرة (قرى صيدا) [77.1]</t>
+          <t>كوثرية السياد (قرى صيدا) [82.4]</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Kaoutarite El-Siyad</t>
+          <t>Katté</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Saida</t>
+          <t>Akkar</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Akkar</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>كوثرية السياد (قرى صيدا) [82.4]</t>
+          <t>البقيعة (عكار) [75.0]</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Katté</t>
+          <t>Kfar-Mashoune et Dmalsa</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Akkar</t>
+          <t>Jubail</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Akkar</t>
+          <t>Mount Lebanon</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>البقيعة (عكار) [75.0]</t>
+          <t>كفر مسحون (جبيل) [80.0]</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>مزرعة السياد (جبيل) [72.0]</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Kfar-Mashoune et Dmalsa</t>
+          <t>Kobbaï</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Jubail</t>
+          <t>Baabda</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -81312,46 +81317,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>كفر مسحون (جبيل) [80.0]</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>مزرعة السياد (جبيل) [72.0]</t>
+          <t>قبيع (بعبدا) [75.0]</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Kobbaï</t>
+          <t>Lebaa</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Baabda</t>
+          <t>Jezzine</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Mount Lebanon</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>قبيع (بعبدا) [75.0]</t>
+          <t>لبعه (جزين) [85.7]</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Lebaa</t>
+          <t>Mazraat Dhaira</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Jezzine</t>
+          <t>Sour</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -81361,14 +81361,14 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>لبعه (جزين) [85.7]</t>
+          <t>الظهيرة (صور) [72.7]</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Mazraat Dhaira</t>
+          <t>Mazraat Ez-Zalloutieh</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -81383,36 +81383,36 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>الظهيرة (صور) [72.7]</t>
+          <t>الزلوطية (صور) [77.1]</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Mazraat Ez-Zalloutieh</t>
+          <t>Mazraet-el-Siyad</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Sour</t>
+          <t>Jubail</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Mount Lebanon</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>الزلوطية (صور) [77.1]</t>
+          <t>مزرعة السياد (جبيل) [72.7]</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Mazraet-el-Siyad</t>
+          <t>Mechmech</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -81427,14 +81427,14 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>مزرعة السياد (جبيل) [72.7]</t>
+          <t>كفر مسحون (جبيل) [77.1]</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Mechmech</t>
+          <t>Mehrine</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -81449,107 +81449,107 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>كفر مسحون (جبيل) [77.1]</t>
+          <t>كفر مسحون (جبيل) [75.0]</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Mehrine</t>
+          <t>Merh Kfarsghabe</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Jubail</t>
+          <t>Zgharta</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Mount Lebanon</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>كفر مسحون (جبيل) [75.0]</t>
+          <t>مزرعة حوقا (زغرتا) [72.0]</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Merh Kfarsghabe</t>
+          <t>Michaa Mrajhiné</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Zgharta</t>
+          <t>Hermel</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Baalbak - Hermel</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>مزرعة حوقا (زغرتا) [72.0]</t>
+          <t>مراح العين (قضاءي بعلبك والهرمل) [72.0]</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Michaa Mrajhiné</t>
+          <t>Miemié</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Hermel</t>
+          <t>Saida</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Baalbak - Hermel</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>مراح العين (قضاءي بعلبك والهرمل) [72.0]</t>
+          <t>المية ومية (قرى صيدا) [72.7]</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Miemié</t>
+          <t>Mrabine</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Saida</t>
+          <t>Minieh-Danieh</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>المية ومية (قرى صيدا) [72.7]</t>
+          <t>نمرين (الضنية) [75.0]</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Mrabine</t>
+          <t>Mugher-el-Ahwel</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Minieh-Danieh</t>
+          <t>Bcharre</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -81559,41 +81559,46 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>نمرين (الضنية) [75.0]</t>
+          <t>المغر وبلا (بشري) [85.7]</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Mugher-el-Ahwel</t>
+          <t>Naamat</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Bcharre</t>
+          <t>Chouf</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Mount Lebanon</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>المغر وبلا (بشري) [85.7]</t>
+          <t>الناعمه (الشوف) [80.0]</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>حارة الناعمه (الشوف) [72.0]</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Naamat</t>
+          <t>Nammoura et Kfar Jerif</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Chouf</t>
+          <t>Kasrouane</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -81603,41 +81608,46 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>الناعمه (الشوف) [80.0]</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>حارة الناعمه (الشوف) [72.0]</t>
+          <t>النموره وكفر جريف (كسروان) [80.0]</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Nammoura et Kfar Jerif</t>
+          <t>Ouadi El-Osse</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Kasrouane</t>
+          <t>Hermel</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Mount Lebanon</t>
+          <t>Baalbak - Hermel</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>النموره وكفر جريف (كسروان) [80.0]</t>
+          <t>وادي الصفا الشرقي (قضاءي بعلبك والهرمل) [85.5]</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>وادي المشمشه (قضاءي بعلبك والهرمل) [85.5]</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>وادي النيرة (قضاءي بعلبك والهرمل) [85.5]</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Ouadi El-Osse</t>
+          <t>Ras Baalbek El-Gharbi</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -81652,24 +81662,19 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>وادي الصفا الشرقي (قضاءي بعلبك والهرمل) [85.5]</t>
+          <t>قلعة غربي (قضاءي بعلبك والهرمل) [81.8]</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>وادي المشمشه (قضاءي بعلبك والهرمل) [85.5]</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>وادي النيرة (قضاءي بعلبك والهرمل) [85.5]</t>
+          <t>الريش حي الغربي (قضاءي بعلبك والهرمل) [77.8]</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Ras Baalbek El-Gharbi</t>
+          <t>Ras-Baalbek - Wadi Faara</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -81684,56 +81689,51 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>قلعة غربي (قضاءي بعلبك والهرمل) [81.8]</t>
+          <t>وادي التركمان (قضاءي بعلبك والهرمل) [85.5]</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>الريش حي الغربي (قضاءي بعلبك والهرمل) [77.8]</t>
+          <t>وادي الرطل (قضاءي بعلبك والهرمل) [85.5]</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>وادي المشمشه (قضاءي بعلبك والهرمل) [85.5]</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Ras-Baalbek - Wadi Faara</t>
+          <t>Sarhita</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Hermel</t>
+          <t>Jubail</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Baalbak - Hermel</t>
+          <t>Mount Lebanon</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>وادي التركمان (قضاءي بعلبك والهرمل) [85.5]</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>وادي الرطل (قضاءي بعلبك والهرمل) [85.5]</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>وادي المشمشه (قضاءي بعلبك والهرمل) [85.5]</t>
+          <t>سرعيتا (جبيل) [76.9]</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sarhita</t>
+          <t>Souhailet El-Faouka</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Jubail</t>
+          <t>Kasrouane</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -81743,107 +81743,107 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>سرعيتا (جبيل) [76.9]</t>
+          <t>السهيله (كسروان) [77.1]</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>ساحل علما (كسروان) [77.1]</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Souhailet El-Faouka</t>
+          <t>Tal Sibhel</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Kasrouane</t>
+          <t>Akkar</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Mount Lebanon</t>
+          <t>Akkar</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>السهيله (كسروان) [77.1]</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>ساحل علما (كسروان) [77.1]</t>
+          <t>القبيات القطلبه (عكار) [72.0]</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Tal Sibhel</t>
+          <t>Tripoli Al-Mouhaitra</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Akkar</t>
+          <t>Tripoli</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Akkar</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>القبيات القطلبه (عكار) [72.0]</t>
+          <t>المهاترة (مدينة طرابلس) [80.0]</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Tripoli Al-Mouhaitra</t>
+          <t>Wadi Abou Youssef</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Tripoli</t>
+          <t>Chouf</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Mount Lebanon</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>المهاترة (مدينة طرابلس) [80.0]</t>
+          <t>وادي دير دوريت (الشوف) [85.5]</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Wadi Abou Youssef</t>
+          <t>Wadi-el-Arayeche</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Chouf</t>
+          <t>Zahleh</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Mount Lebanon</t>
+          <t>Bekaa</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>وادي دير دوريت (الشوف) [85.5]</t>
+          <t>زحلة وادي العرايش (زحلة) [85.5]</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Wadi-el-Arayeche</t>
+          <t>Zahlé (Terres)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -81858,14 +81858,14 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>زحلة وادي العرايش (زحلة) [85.5]</t>
+          <t>زحلة وادي العرايش (زحلة) [85.7]</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Zahlé (Terres)</t>
+          <t>Zahlé Maallaka Kerek</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -81880,37 +81880,15 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>زحلة وادي العرايش (زحلة) [85.7]</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Zahlé Maallaka Kerek</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Zahleh</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Bekaa</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
           <t>زحلة المعلقه (زحلة) [85.7]</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>زحلة كرك نوح (زحلة) [80.0]</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>زحلة المعلقه الشمالي (زحلة) [77.1]</t>
         </is>
@@ -81927,7 +81905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D696"/>
+  <dimension ref="A1:D695"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -90034,7 +90012,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Kab Elias</t>
+          <t>Ksara</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -90056,7 +90034,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Ksara</t>
+          <t>Maallaka (Terres)</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -90078,7 +90056,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Maallaka (Terres)</t>
+          <t>Maazraat-el-Ramtanieh</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -90100,7 +90078,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Maazraat-el-Ramtanieh</t>
+          <t>Mandara</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -90122,7 +90100,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Mandara</t>
+          <t>Mejdel-Anjar</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -90144,7 +90122,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Mejdel-Anjar</t>
+          <t>Nasriyat Rizk</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -90166,7 +90144,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Nasriyat Rizk</t>
+          <t>Tal-al-Amara</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -90188,7 +90166,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Tal-al-Amara</t>
+          <t>Tchiflik Eddé</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -90210,7 +90188,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Tchiflik Eddé</t>
+          <t>Tchiflik Kikano</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -90232,7 +90210,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Tchiflik Kikano</t>
+          <t>Wadi-el-Arayeche</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -90254,7 +90232,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Wadi-el-Arayeche</t>
+          <t>Zahlé (Terres)</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -90276,7 +90254,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Zahlé (Terres)</t>
+          <t>Zahlé Maallaka Kerek</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -90298,7 +90276,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Zahlé Maallaka Kerek</t>
+          <t>Zahlé Mar Gérios</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -90320,7 +90298,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Zahlé Mar Gérios</t>
+          <t>Zebdol</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -90342,17 +90320,17 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Zebdol</t>
+          <t>Aadoua</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Zahleh</t>
+          <t>Zgharta</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>Bekaa</t>
+          <t>North</t>
         </is>
       </c>
     </row>
@@ -90364,7 +90342,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Aadoua</t>
+          <t>Al-Harik</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -90386,7 +90364,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Al-Harik</t>
+          <t>Al-Jdeidé</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -90408,7 +90386,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Al-Jdeidé</t>
+          <t>Al-Khaldyé</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -90430,7 +90408,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Al-Khaldyé</t>
+          <t>Arbet Koshaya</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -90452,7 +90430,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Arbet Koshaya</t>
+          <t>Ardate</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -90474,7 +90452,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Ardate</t>
+          <t>Bsebhil</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -90496,7 +90474,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Bsebhil</t>
+          <t>Danhi</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -90518,7 +90496,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Danhi</t>
+          <t>Ehden</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -90540,7 +90518,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Ehden</t>
+          <t>Ejbeh</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -90562,7 +90540,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Ejbeh</t>
+          <t>El-Tellé</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -90584,7 +90562,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>El-Tellé</t>
+          <t>Mazraat Ejbeh</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -90606,7 +90584,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Mazraat Ejbeh</t>
+          <t>Mazraat Jneide</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -90628,7 +90606,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Mazraat Jneide</t>
+          <t>Mejdlaya</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -90650,7 +90628,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Mejdlaya</t>
+          <t>Merh Kfarsghabe</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -90672,7 +90650,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Merh Kfarsghabe</t>
+          <t>Sakhra</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -90689,22 +90667,22 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Sakhra</t>
+          <t>راشكده</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Zgharta</t>
+          <t>البترون</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>الشمال</t>
         </is>
       </c>
     </row>
@@ -90716,7 +90694,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>راشكده</t>
+          <t>عورا</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -90738,7 +90716,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>عورا</t>
+          <t>غوما</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -90760,7 +90738,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>غوما</t>
+          <t>قندولا</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -90782,17 +90760,17 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>قندولا</t>
+          <t>الدبية</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>البترون</t>
+          <t>الشوف</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>الشمال</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -90804,7 +90782,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>الدبية</t>
+          <t>المحتقره دير المخلص</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -90826,7 +90804,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>المحتقره دير المخلص</t>
+          <t>الناعمه</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -90848,7 +90826,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>الناعمه</t>
+          <t>بقعاتا</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -90870,7 +90848,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>بقعاتا</t>
+          <t>جديدة الشوف</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -90892,7 +90870,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>جديدة الشوف</t>
+          <t>حارة الناعمه</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -90914,7 +90892,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>حارة الناعمه</t>
+          <t>حارة بعاصير</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -90936,7 +90914,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>حارة بعاصير</t>
+          <t>عين الاسد والشميس</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -90958,7 +90936,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>عين الاسد والشميس</t>
+          <t>عين الحور</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -90980,7 +90958,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>عين الحور</t>
+          <t>كليليه</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -91002,7 +90980,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>كليليه</t>
+          <t>مرج برجا</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -91024,7 +91002,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>مرج برجا</t>
+          <t>وادي دير دوريت</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -91046,17 +91024,17 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>وادي دير دوريت</t>
+          <t>الروضة</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>الشوف</t>
+          <t>الضنية</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>الشمال</t>
         </is>
       </c>
     </row>
@@ -91068,7 +91046,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>الروضة</t>
+          <t>المطل</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -91090,7 +91068,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>المطل</t>
+          <t>حرف السياد</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -91112,7 +91090,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>حرف السياد</t>
+          <t>عزقي</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -91134,7 +91112,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>عزقي</t>
+          <t>قزحيا</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -91156,7 +91134,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>قزحيا</t>
+          <t>كرم المهر</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -91178,7 +91156,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>كرم المهر</t>
+          <t>كفربنين</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -91200,7 +91178,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>كفربنين</t>
+          <t>نمرين</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -91222,12 +91200,12 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>نمرين</t>
+          <t>البحصاص</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>الضنية</t>
+          <t>الكورة</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
@@ -91244,7 +91222,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>البحصاص</t>
+          <t>حارة الخاصة</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -91266,7 +91244,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>حارة الخاصة</t>
+          <t>ضهر العين</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -91288,7 +91266,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>ضهر العين</t>
+          <t>ضهور الهوا</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -91310,17 +91288,17 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>ضهور الهوا</t>
+          <t>الرابية</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>الكورة</t>
+          <t>المتن</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>الشمال</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -91332,7 +91310,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>الرابية</t>
+          <t>سد البوشريه</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -91354,7 +91332,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>سد البوشريه</t>
+          <t>مزرعة بنابيل</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -91376,17 +91354,17 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>مزرعة بنابيل</t>
+          <t>المنية</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>المتن</t>
+          <t>المنية</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>الشمال</t>
         </is>
       </c>
     </row>
@@ -91398,17 +91376,17 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>المنية</t>
+          <t>كفروة</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>المنية</t>
+          <t>النبطية</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>الشمال</t>
+          <t>النبطية</t>
         </is>
       </c>
     </row>
@@ -91420,17 +91398,17 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>كفروة</t>
+          <t>المغر وبلا</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>النبطية</t>
+          <t>بشري</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>النبطية</t>
+          <t>الشمال</t>
         </is>
       </c>
     </row>
@@ -91442,17 +91420,17 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>المغر وبلا</t>
+          <t>الحدث شمالي</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>بشري</t>
+          <t>بعبدا</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>الشمال</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -91464,7 +91442,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>الحدث شمالي</t>
+          <t>الحدث قبلي</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -91486,7 +91464,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>الحدث قبلي</t>
+          <t>الشياح حي الكنيسة</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -91508,7 +91486,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>الشياح حي الكنيسة</t>
+          <t>الشياح حي كرم الزيتون</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -91530,7 +91508,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>الشياح حي كرم الزيتون</t>
+          <t>الغبيري بئر حسن</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -91552,7 +91530,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>الغبيري بئر حسن</t>
+          <t>الغبيري حي الجامع</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -91574,7 +91552,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>الغبيري حي الجامع</t>
+          <t>الفياضية</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -91596,7 +91574,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>الفياضية</t>
+          <t>القلعه</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -91618,7 +91596,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>القلعه</t>
+          <t>المريجه</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -91640,7 +91618,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>المريجه</t>
+          <t>تحويطة النهر</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -91662,7 +91640,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>تحويطة النهر</t>
+          <t>حارة البطم</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -91684,7 +91662,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>حارة البطم</t>
+          <t>حارة حريك قرانوح</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -91706,7 +91684,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>حارة حريك قرانوح</t>
+          <t>دير مار الياس الكحلونية</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -91728,7 +91706,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>دير مار الياس الكحلونية</t>
+          <t>سبنيه</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -91750,7 +91728,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>سبنيه</t>
+          <t>قبيع</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -91772,17 +91750,17 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>قبيع</t>
+          <t>حداثا</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>بعبدا</t>
+          <t>بنت جبيل</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>النبطية</t>
         </is>
       </c>
     </row>
@@ -91794,7 +91772,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>حداثا</t>
+          <t>عيتا الجبل</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -91816,17 +91794,17 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>عيتا الجبل</t>
+          <t>الجليسه</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>بنت جبيل</t>
+          <t>جبيل</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>النبطية</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -91838,7 +91816,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>الجليسه</t>
+          <t>العاقورة - م</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -91860,7 +91838,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>العاقورة - م</t>
+          <t>الفيدار</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -91882,7 +91860,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>الفيدار</t>
+          <t>المزاريب</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -91904,7 +91882,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>المزاريب</t>
+          <t>المنصف</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -91926,7 +91904,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>المنصف</t>
+          <t>بنتاعل</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -91948,7 +91926,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>بنتاعل</t>
+          <t>دملصا</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -91970,7 +91948,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>دملصا</t>
+          <t>دير القطاره</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -91992,7 +91970,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>دير القطاره</t>
+          <t>سرعيتا</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -92014,7 +91992,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>سرعيتا</t>
+          <t>عين الدلبة</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -92036,7 +92014,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>عين الدلبة</t>
+          <t>عين الشلال</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -92058,7 +92036,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>عين الشلال</t>
+          <t>عين الغويبة</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -92080,7 +92058,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>عين الغويبة</t>
+          <t>قرطبا الشمالية</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -92102,7 +92080,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>قرطبا الشمالية</t>
+          <t>كفر مسحون</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -92124,7 +92102,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>كفر مسحون</t>
+          <t>مزرعة السياد</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -92146,17 +92124,17 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>مزرعة السياد</t>
+          <t>بحنين - كفرتعلا</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>جبيل</t>
+          <t>جزين</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>الجنوب</t>
         </is>
       </c>
     </row>
@@ -92168,7 +92146,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>بحنين - كفرتعلا</t>
+          <t>عين مجدلين</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -92190,7 +92168,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>عين مجدلين</t>
+          <t>قتالة</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -92212,7 +92190,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>قتالة</t>
+          <t>لبعه</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -92234,17 +92212,17 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>لبعه</t>
+          <t>الكرمة</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>جزين</t>
+          <t>زحلة</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>الجنوب</t>
+          <t>البقاع</t>
         </is>
       </c>
     </row>
@@ -92256,7 +92234,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>الكرمة</t>
+          <t>بتياس</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -92278,7 +92256,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>بتياس</t>
+          <t>جلالا</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -92300,7 +92278,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>جلالا</t>
+          <t>حاجي حببلي</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -92322,7 +92300,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>حاجي حببلي</t>
+          <t>حي السلم</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -92344,7 +92322,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>حي السلم</t>
+          <t>حي الفيكاني</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -92366,7 +92344,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>حي الفيكاني</t>
+          <t>خضر بك</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -92388,7 +92366,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>خضر بك</t>
+          <t>زحلة المعلقه</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
@@ -92410,7 +92388,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>زحلة المعلقه</t>
+          <t>زحلة المعلقه الشمالي</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -92432,7 +92410,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>زحلة المعلقه الشمالي</t>
+          <t>زحلة حي السيدة</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -92454,7 +92432,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>زحلة حي السيدة</t>
+          <t>زحلة كرك نوح</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -92476,7 +92454,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>زحلة كرك نوح</t>
+          <t>زحلة مار مخايل</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -92498,7 +92476,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>زحلة مار مخايل</t>
+          <t>زحلة وادي العرايش</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -92520,7 +92498,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>زحلة وادي العرايش</t>
+          <t>شهابية الفاعور</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -92542,7 +92520,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>شهابية الفاعور</t>
+          <t>كابوسية</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -92564,7 +92542,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>كابوسية</t>
+          <t>يوغون اولوك</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -92586,17 +92564,17 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>يوغون اولوك</t>
+          <t>اجبع</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>زحلة</t>
+          <t>زغرتا</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>البقاع</t>
+          <t>الشمال</t>
         </is>
       </c>
     </row>
@@ -92608,7 +92586,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>اجبع</t>
+          <t>اسلوت</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -92630,7 +92608,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>اسلوت</t>
+          <t>القادريه</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -92652,7 +92630,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>القادريه</t>
+          <t>بيت عبيد</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -92674,7 +92652,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>بيت عبيد</t>
+          <t>بيت عوكر</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
@@ -92696,7 +92674,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>بيت عوكر</t>
+          <t>حارة الفوار</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -92718,7 +92696,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>حارة الفوار</t>
+          <t>حرف ارده</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -92740,7 +92718,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>حرف ارده</t>
+          <t>حرف مزيارة</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -92762,7 +92740,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>حرف مزيارة</t>
+          <t>عربة قزحيا</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -92784,7 +92762,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>عربة قزحيا</t>
+          <t>مزرعة الفريديس</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -92806,7 +92784,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>مزرعة الفريديس</t>
+          <t>مزرعة حوقا</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -92828,17 +92806,17 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>مزرعة حوقا</t>
+          <t>البازوريه</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>زغرتا</t>
+          <t>صور</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>الشمال</t>
+          <t>الجنوب</t>
         </is>
       </c>
     </row>
@@ -92850,7 +92828,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>البازوريه</t>
+          <t>البرغليه</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -92872,7 +92850,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>البرغليه</t>
+          <t>البساتين</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -92894,7 +92872,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>البساتين</t>
+          <t>البص  قسم 1</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -92916,7 +92894,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>البص  قسم 1</t>
+          <t>البص  قسم 3</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -92938,7 +92916,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>البص  قسم 3</t>
+          <t>البص قسم 5</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -92960,7 +92938,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>البص قسم 5</t>
+          <t>الحميري</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -92982,7 +92960,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>الحميري</t>
+          <t>الرشيديه</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -93004,7 +92982,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>الرشيديه</t>
+          <t>الزلوطية</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -93026,7 +93004,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>الزلوطية</t>
+          <t>السماعية</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -93048,7 +93026,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>السماعية</t>
+          <t>الشهابية</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -93070,7 +93048,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>الشهابية</t>
+          <t>الظهيرة</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -93092,7 +93070,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>الظهيرة</t>
+          <t>المالكية</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
@@ -93114,7 +93092,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>المالكية</t>
+          <t>بثتيات</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -93136,7 +93114,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>بثتيات</t>
+          <t>شبريحا</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
@@ -93158,7 +93136,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>شبريحا</t>
+          <t>شمع</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -93180,7 +93158,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>شمع</t>
+          <t>صور حي الارثوذكس</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -93202,7 +93180,7 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>صور حي الارثوذكس</t>
+          <t>صور حي الجامع</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -93224,7 +93202,7 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>صور حي الجامع</t>
+          <t>صور حي الجورة</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -93246,7 +93224,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>صور حي الجورة</t>
+          <t>صور حي الحسينية</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -93268,7 +93246,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>صور حي الحسينية</t>
+          <t>صور حي الكاثوليك</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -93290,7 +93268,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>صور حي الكاثوليك</t>
+          <t>صور حي المصاروي</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -93312,7 +93290,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>صور حي المصاروي</t>
+          <t>صور حي المنارة</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -93334,7 +93312,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>صور حي المنارة</t>
+          <t>صور حي الموارنة</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -93356,7 +93334,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>صور حي الموارنة</t>
+          <t>عين الزرقا</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -93378,7 +93356,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>عين الزرقا</t>
+          <t>محرونه</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -93400,17 +93378,17 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>محرونه</t>
+          <t>البساتين</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>صور</t>
+          <t>عاليه</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>الجنوب</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -93422,7 +93400,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>البساتين</t>
+          <t>التعزانية</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -93444,7 +93422,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>التعزانية</t>
+          <t>جسر القاضي</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -93466,7 +93444,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>جسر القاضي</t>
+          <t>عاليه قبلي</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -93488,7 +93466,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>عاليه قبلي</t>
+          <t>عاليه وسطاني</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
@@ -93510,7 +93488,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>عاليه وسطاني</t>
+          <t>عين الفريديس</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -93532,7 +93510,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>عين الفريديس</t>
+          <t>محطة بحمدون</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -93554,17 +93532,17 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>محطة بحمدون</t>
+          <t>البساتين</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>عاليه</t>
+          <t>عكار</t>
         </is>
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>عكار</t>
         </is>
       </c>
     </row>
@@ -93576,7 +93554,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>البساتين</t>
+          <t>البقيعة</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -93598,7 +93576,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>البقيعة</t>
+          <t>الحويش</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -93620,7 +93598,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>الحويش</t>
+          <t>الدوسه</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -93642,7 +93620,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>الدوسه</t>
+          <t>السهلة</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -93664,7 +93642,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>السهلة</t>
+          <t>الشيخ عياش</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -93686,7 +93664,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>الشيخ عياش</t>
+          <t>العماير</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -93708,7 +93686,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>العماير</t>
+          <t>العوادة</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
@@ -93730,7 +93708,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>العوادة</t>
+          <t>الفرض</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -93752,7 +93730,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>الفرض</t>
+          <t>القبيات الذوق</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
@@ -93774,7 +93752,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>القبيات الذوق</t>
+          <t>القبيات الضهر</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -93796,7 +93774,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>القبيات الضهر</t>
+          <t>القبيات الغربية</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -93818,7 +93796,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>القبيات الغربية</t>
+          <t>القبيات القطلبه</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
@@ -93840,7 +93818,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>القبيات القطلبه</t>
+          <t>القبيات غوايا</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
@@ -93862,7 +93840,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>القبيات غوايا</t>
+          <t>القبيات مرتموره</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
@@ -93884,7 +93862,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>القبيات مرتموره</t>
+          <t>المونسة</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -93906,7 +93884,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>المونسة</t>
+          <t>الهيشة</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -93928,7 +93906,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>الهيشة</t>
+          <t>برج العرب</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
@@ -93950,7 +93928,7 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>برج العرب</t>
+          <t>بني صخر</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
@@ -93972,7 +93950,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>بني صخر</t>
+          <t>بيت الحاج</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
@@ -93994,7 +93972,7 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>بيت الحاج</t>
+          <t>تل معيان</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
@@ -94016,7 +93994,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>تل معيان</t>
+          <t>تلبيبة</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
@@ -94038,7 +94016,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>تلبيبة</t>
+          <t>جبل المنصورة</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
@@ -94060,7 +94038,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>جبل المنصورة</t>
+          <t>جرمنايا</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
@@ -94082,7 +94060,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>جرمنايا</t>
+          <t>خربة الجرد</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
@@ -94104,7 +94082,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>خربة الجرد</t>
+          <t>خريبة الجندي</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
@@ -94126,7 +94104,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>خريبة الجندي</t>
+          <t>خط البترول</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -94148,7 +94126,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>خط البترول</t>
+          <t>رجم عيسى</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
@@ -94170,7 +94148,7 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>رجم عيسى</t>
+          <t>ضهر القنبر</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
@@ -94192,7 +94170,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>ضهر القنبر</t>
+          <t>عبودية</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
@@ -94214,7 +94192,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>عبودية</t>
+          <t>عين الذهب</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
@@ -94236,7 +94214,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>عين الذهب</t>
+          <t>قنية</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
@@ -94258,7 +94236,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>قنية</t>
+          <t>كرم زبدين</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
@@ -94280,7 +94258,7 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>كرم زبدين</t>
+          <t>مراح الخوخ</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
@@ -94302,17 +94280,17 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>مراح الخوخ</t>
+          <t>الحجة</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>عكار</t>
+          <t>قرى صيدا</t>
         </is>
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>عكار</t>
+          <t>الجنوب</t>
         </is>
       </c>
     </row>
@@ -94324,7 +94302,7 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>الحجة</t>
+          <t>القنيطرة</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
@@ -94346,7 +94324,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>القنيطرة</t>
+          <t>المعمرية</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
@@ -94368,7 +94346,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>المعمرية</t>
+          <t>المية ومية</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
@@ -94390,7 +94368,7 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>المية ومية</t>
+          <t>كوثرية السياد</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
@@ -94412,17 +94390,17 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>كوثرية السياد</t>
+          <t>الروضة</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>قرى صيدا</t>
+          <t>قضاءي البقاع الغربي وراشيا</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>الجنوب</t>
+          <t>البقاع</t>
         </is>
       </c>
     </row>
@@ -94434,7 +94412,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>الروضة</t>
+          <t>الشبرقية</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
@@ -94456,7 +94434,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>الشبرقية</t>
+          <t>دير العشائر</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
@@ -94478,7 +94456,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>دير العشائر</t>
+          <t>راشيا حي الفوقا</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
@@ -94500,7 +94478,7 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>راشيا حي الفوقا</t>
+          <t>راشيا حي الكواسبه</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
@@ -94522,7 +94500,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>راشيا حي الكواسبه</t>
+          <t>راشيا حي الميدان</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
@@ -94544,7 +94522,7 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>راشيا حي الميدان</t>
+          <t>عيحا</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
@@ -94566,7 +94544,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>عيحا</t>
+          <t>عين التينه</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
@@ -94588,7 +94566,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>عين التينه</t>
+          <t>كفردنيس</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
@@ -94610,7 +94588,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>كفردنيس</t>
+          <t>كفرقوق</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
@@ -94632,7 +94610,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>كفرقوق</t>
+          <t>محيدثه</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
@@ -94654,17 +94632,17 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>محيدثه</t>
+          <t>الانصار</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>قضاءي البقاع الغربي وراشيا</t>
+          <t>قضاءي بعلبك والهرمل</t>
         </is>
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>البقاع</t>
+          <t>بعلبك والهرمل</t>
         </is>
       </c>
     </row>
@@ -94676,7 +94654,7 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>الانصار</t>
+          <t>البرانيه حي المسيحيين</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
@@ -94698,7 +94676,7 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>البرانيه حي المسيحيين</t>
+          <t>البرباره محلة المسيحيين</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
@@ -94720,7 +94698,7 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>البرباره محلة المسيحيين</t>
+          <t>البويضة</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
@@ -94742,7 +94720,7 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>البويضة</t>
+          <t>البويضة الحي الغربي</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
@@ -94764,7 +94742,7 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>البويضة الحي الغربي</t>
+          <t>البويضة الشمالية</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
@@ -94786,7 +94764,7 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>البويضة الشمالية</t>
+          <t>التوفيقيه</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
@@ -94808,7 +94786,7 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>التوفيقيه</t>
+          <t>الجوبانية</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
@@ -94830,7 +94808,7 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>الجوبانية</t>
+          <t>الحدث الشمالي</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
@@ -94852,7 +94830,7 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>الحدث الشمالي</t>
+          <t>الحدث الغربي</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
@@ -94874,7 +94852,7 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>الحدث الغربي</t>
+          <t>الحريقه</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
@@ -94896,7 +94874,7 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>الحريقه</t>
+          <t>الحلانيه</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
@@ -94918,7 +94896,7 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>الحلانيه</t>
+          <t>الخضر الشرقي</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
@@ -94940,7 +94918,7 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>الخضر الشرقي</t>
+          <t>الخضر الغربي</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
@@ -94962,7 +94940,7 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>الخضر الغربي</t>
+          <t>الخضر حي الاشعل</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
@@ -94984,7 +94962,7 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>الخضر حي الاشعل</t>
+          <t>الخضر حي الجنوبي</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
@@ -95006,7 +94984,7 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>الخضر حي الجنوبي</t>
+          <t>الخضر حي الشعب</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
@@ -95028,7 +95006,7 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>الخضر حي الشعب</t>
+          <t>الريش حي الشرقي</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
@@ -95050,7 +95028,7 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>الريش حي الشرقي</t>
+          <t>الريش حي الشميس</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
@@ -95072,7 +95050,7 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>الريش حي الشميس</t>
+          <t>الريش حي الغربي</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
@@ -95094,7 +95072,7 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>الريش حي الغربي</t>
+          <t>الزرازير</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
@@ -95116,7 +95094,7 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>الزرازير</t>
+          <t>الزويتيني</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
@@ -95138,7 +95116,7 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>الزويتيني</t>
+          <t>السعيده</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
@@ -95160,7 +95138,7 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>السعيده</t>
+          <t>السويسة</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
@@ -95182,7 +95160,7 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>السويسة</t>
+          <t>الشواغير التحتا</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
@@ -95204,7 +95182,7 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>الشواغير التحتا</t>
+          <t>الشواغير الفوقا</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
@@ -95226,7 +95204,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>الشواغير الفوقا</t>
+          <t>الصوانية</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
@@ -95248,7 +95226,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>الصوانية</t>
+          <t>العقيدية</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
@@ -95270,7 +95248,7 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>العقيدية</t>
+          <t>العلاق</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
@@ -95292,7 +95270,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>العلاق</t>
+          <t>الفاكهة حي الجامع</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
@@ -95314,7 +95292,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>الفاكهة حي الجامع</t>
+          <t>الفاكهة حي مار جرجس</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
@@ -95336,7 +95314,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>الفاكهة حي مار جرجس</t>
+          <t>القاع</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
@@ -95358,7 +95336,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>القاع</t>
+          <t>القدام</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
@@ -95380,7 +95358,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>القدام</t>
+          <t>القرينة</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
@@ -95402,7 +95380,7 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>القرينة</t>
+          <t>القصر</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
@@ -95424,7 +95402,7 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>القصر</t>
+          <t>الكواخ</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
@@ -95446,7 +95424,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>الكواخ</t>
+          <t>المعاصر</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
@@ -95468,7 +95446,7 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>المعاصر</t>
+          <t>النبي رشاده</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
@@ -95490,7 +95468,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>النبي رشاده</t>
+          <t>النبي شيت حي الجنوبي</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
@@ -95512,7 +95490,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>النبي شيت حي الجنوبي</t>
+          <t>النبي شيت حي الشرقي</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
@@ -95534,7 +95512,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>النبي شيت حي الشرقي</t>
+          <t>النبي شيت حي الشمالي</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
@@ -95556,7 +95534,7 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>النبي شيت حي الشمالي</t>
+          <t>النبي شيت حي العريض</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
@@ -95578,7 +95556,7 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>النبي شيت حي العريض</t>
+          <t>النبي شيت حي العقبة</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
@@ -95600,7 +95578,7 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>النبي شيت حي العقبة</t>
+          <t>النبي شيت حي الغربي</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
@@ -95622,7 +95600,7 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>النبي شيت حي الغربي</t>
+          <t>النبي شيت حي طبشار</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
@@ -95644,7 +95622,7 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>النبي شيت حي طبشار</t>
+          <t>النبي نعام</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
@@ -95666,7 +95644,7 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>النبي نعام</t>
+          <t>النقرة</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
@@ -95688,7 +95666,7 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>النقرة</t>
+          <t>بريصا</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
@@ -95710,7 +95688,7 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>بريصا</t>
+          <t>بيت ابو صليبي</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
@@ -95732,7 +95710,7 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>بيت ابو صليبي</t>
+          <t>جوار الحشيش</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
@@ -95754,7 +95732,7 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>جوار الحشيش</t>
+          <t>حوش السيد علي</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
@@ -95776,7 +95754,7 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>حوش السيد علي</t>
+          <t>حي الزهراء</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
@@ -95798,7 +95776,7 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>حي الزهراء</t>
+          <t>حي الصلح</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
@@ -95820,7 +95798,7 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>حي الصلح</t>
+          <t>حي العباسية</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
@@ -95842,7 +95820,7 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>حي العباسية</t>
+          <t>حي عز الدين</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
@@ -95864,7 +95842,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>حي عز الدين</t>
+          <t>دار الواسعة</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
@@ -95886,7 +95864,7 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>دار الواسعة</t>
+          <t>رماسا</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
@@ -95908,7 +95886,7 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>رماسا</t>
+          <t>سهلات الماء</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
@@ -95930,7 +95908,7 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>سهلات الماء</t>
+          <t>شعت حي الضهر</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
@@ -95952,7 +95930,7 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>شعت حي الضهر</t>
+          <t>صفرا</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
@@ -95974,7 +95952,7 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>صفرا</t>
+          <t>غفره</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
@@ -95996,7 +95974,7 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>غفره</t>
+          <t>فلاوي</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
@@ -96018,7 +95996,7 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>فلاوي</t>
+          <t>فيسان</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
@@ -96040,7 +96018,7 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>فيسان</t>
+          <t>قبة دورس</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
@@ -96062,7 +96040,7 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>قبة دورس</t>
+          <t>قلد السبع</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
@@ -96084,7 +96062,7 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>قلد السبع</t>
+          <t>قلعة</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
@@ -96106,7 +96084,7 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>قلعة</t>
+          <t>قلعة غربي</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
@@ -96128,7 +96106,7 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>قلعة غربي</t>
+          <t>قنافذ</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
@@ -96150,7 +96128,7 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>قنافذ</t>
+          <t>كفردبش</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
@@ -96172,7 +96150,7 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>كفردبش</t>
+          <t>مراح العين</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
@@ -96194,7 +96172,7 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>مراح العين</t>
+          <t>مزرعة آل سويدان</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
@@ -96216,7 +96194,7 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>مزرعة آل سويدان</t>
+          <t>مزرعة ابو صليبي</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
@@ -96238,7 +96216,7 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>مزرعة ابو صليبي</t>
+          <t>مزرعة التوت</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
@@ -96260,7 +96238,7 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>مزرعة التوت</t>
+          <t>مزرعة الضليل</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
@@ -96282,7 +96260,7 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>مزرعة الضليل</t>
+          <t>مزرعة الفقيه</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
@@ -96304,7 +96282,7 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>مزرعة الفقيه</t>
+          <t>مزرعة بيت الطشم</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
@@ -96326,7 +96304,7 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>مزرعة بيت الطشم</t>
+          <t>مزرعة بيت مطر</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
@@ -96348,7 +96326,7 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>مزرعة بيت مطر</t>
+          <t>مزرعة سجد</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
@@ -96370,7 +96348,7 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>مزرعة سجد</t>
+          <t>مصنع الزهرة</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
@@ -96392,7 +96370,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>مصنع الزهرة</t>
+          <t>وادي التركمان</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
@@ -96414,7 +96392,7 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>وادي التركمان</t>
+          <t>وادي الرطل</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
@@ -96436,7 +96414,7 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>وادي الرطل</t>
+          <t>وادي الزين</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
@@ -96458,7 +96436,7 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>وادي الزين</t>
+          <t>وادي الصفا الشرقي</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
@@ -96480,7 +96458,7 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>وادي الصفا الشرقي</t>
+          <t>وادي المشمشه</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
@@ -96502,7 +96480,7 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>وادي المشمشه</t>
+          <t>وادي النيرة</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
@@ -96524,7 +96502,7 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>وادي النيرة</t>
+          <t>وادي بنيت</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
@@ -96546,17 +96524,17 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>وادي بنيت</t>
+          <t>الجديدة حي السراي</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>قضاءي بعلبك والهرمل</t>
+          <t>قضاءي مرجعيون وحاصبيا</t>
         </is>
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>بعلبك والهرمل</t>
+          <t>النبطية</t>
         </is>
       </c>
     </row>
@@ -96568,7 +96546,7 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>الجديدة حي السراي</t>
+          <t>الجديدة حي العيون</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
@@ -96590,7 +96568,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>الجديدة حي العيون</t>
+          <t>الجديدة حي القلعة</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
@@ -96612,7 +96590,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>الجديدة حي القلعة</t>
+          <t>الجديدة حي المدارس</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
@@ -96634,7 +96612,7 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>الجديدة حي المدارس</t>
+          <t>الدلافة</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -96656,7 +96634,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>الدلافة</t>
+          <t>الفرديس</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
@@ -96678,7 +96656,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>الفرديس</t>
+          <t>الهبارية</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -96700,7 +96678,7 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>الهبارية</t>
+          <t>الوزاني</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
@@ -96722,7 +96700,7 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>الوزاني</t>
+          <t>برج الملوك</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
@@ -96744,7 +96722,7 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>برج الملوك</t>
+          <t>بويضة</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
@@ -96766,7 +96744,7 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>بويضة</t>
+          <t>حاصبيا حي السراي</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
@@ -96788,7 +96766,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>حاصبيا حي السراي</t>
+          <t>حاصبيا حي العين</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
@@ -96810,7 +96788,7 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>حاصبيا حي العين</t>
+          <t>حاصبيا حي الفوقاني</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
@@ -96832,7 +96810,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>حاصبيا حي الفوقاني</t>
+          <t>حاصبيا حي صفيفة</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
@@ -96854,7 +96832,7 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>حاصبيا حي صفيفة</t>
+          <t>رب ثلاثين</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
@@ -96876,7 +96854,7 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>رب ثلاثين</t>
+          <t>سرده والعمره</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
@@ -96898,7 +96876,7 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>سرده والعمره</t>
+          <t>عديسه</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
@@ -96920,7 +96898,7 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>عديسه</t>
+          <t>كفرشوبا</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
@@ -96942,17 +96920,17 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>كفرشوبا</t>
+          <t>السهيله</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>قضاءي مرجعيون وحاصبيا</t>
+          <t>كسروان</t>
         </is>
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>النبطية</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -96964,7 +96942,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>السهيله</t>
+          <t>النموره وكفر جريف</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
@@ -96986,7 +96964,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>النموره وكفر جريف</t>
+          <t>ساحل علما</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
@@ -97008,7 +96986,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>ساحل علما</t>
+          <t>شوان والعبره</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
@@ -97030,7 +97008,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>شوان والعبره</t>
+          <t>غزير القناة</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
@@ -97052,7 +97030,7 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>غزير القناة</t>
+          <t>غزير المعاملتين</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
@@ -97074,17 +97052,17 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>غزير المعاملتين</t>
+          <t>التبانة</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>كسروان</t>
+          <t>مدينة طرابلس</t>
         </is>
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>الشمال</t>
         </is>
       </c>
     </row>
@@ -97096,7 +97074,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>التبانة</t>
+          <t>الرمانة</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
@@ -97118,7 +97096,7 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>الرمانة</t>
+          <t>الزاهرية</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
@@ -97140,7 +97118,7 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>الزاهرية</t>
+          <t>السويقه</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
@@ -97162,7 +97140,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>السويقه</t>
+          <t>القبة</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
@@ -97184,7 +97162,7 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>القبة</t>
+          <t>المهاترة</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
@@ -97206,7 +97184,7 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>المهاترة</t>
+          <t>وادي النحلة</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
@@ -97215,28 +97193,6 @@
         </is>
       </c>
       <c r="D695" t="inlineStr">
-        <is>
-          <t>الشمال</t>
-        </is>
-      </c>
-    </row>
-    <row r="696">
-      <c r="A696" t="inlineStr">
-        <is>
-          <t>Arabic</t>
-        </is>
-      </c>
-      <c r="B696" t="inlineStr">
-        <is>
-          <t>وادي النحلة</t>
-        </is>
-      </c>
-      <c r="C696" t="inlineStr">
-        <is>
-          <t>مدينة طرابلس</t>
-        </is>
-      </c>
-      <c r="D696" t="inlineStr">
         <is>
           <t>الشمال</t>
         </is>

--- a/FuzzyMatch/Lebanese_Villages_Matched_v6.xlsx
+++ b/FuzzyMatch/Lebanese_Villages_Matched_v6.xlsx
@@ -438,7 +438,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
@@ -450,7 +450,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>/tmp/v5.xlsx</t>
+          <t>v5fix.xlsx</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14">
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="18">
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="19">
@@ -40935,6 +40935,11 @@
           <t>Ktalé</t>
         </is>
       </c>
+      <c r="B1407" t="inlineStr">
+        <is>
+          <t>قتالة</t>
+        </is>
+      </c>
       <c r="C1407" t="inlineStr">
         <is>
           <t>Jezzine</t>
@@ -40942,12 +40947,12 @@
       </c>
       <c r="D1407" t="inlineStr">
         <is>
-          <t>Mount Lebanon</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E1407" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Fuzzy-auto (100.0)</t>
         </is>
       </c>
     </row>
@@ -61820,6 +61825,11 @@
           <t>قتالة</t>
         </is>
       </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>Ktalé</t>
+        </is>
+      </c>
       <c r="C694" t="inlineStr">
         <is>
           <t>جزين</t>
@@ -83158,7 +83168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D665"/>
+  <dimension ref="A1:D663"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86821,7 +86831,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Ktalé</t>
+          <t>Lebaa</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -86831,7 +86841,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Mount Lebanon</t>
+          <t>South</t>
         </is>
       </c>
     </row>
@@ -86843,7 +86853,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Lebaa</t>
+          <t>Mazraat Dahr el-Deir</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -86865,7 +86875,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Mazraat Dahr el-Deir</t>
+          <t>Mazraat Daraya</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -86887,7 +86897,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Mazraat Daraya</t>
+          <t>Mazraat El Ouazaaiyé</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -86909,7 +86919,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Mazraat El Ouazaaiyé</t>
+          <t>Mazraat Louzid (Louayziyé)</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -86931,7 +86941,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Mazraat Louzid (Louayziyé)</t>
+          <t>Sfarai</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -86953,7 +86963,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Sfarai</t>
+          <t>Tamra</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -86975,7 +86985,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Tamra</t>
+          <t>Wadi Laimoune</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -86997,7 +87007,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Wadi Laimoune</t>
+          <t>litige</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -87019,17 +87029,17 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>litige</t>
+          <t>Al Kattara</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Jezzine</t>
+          <t>Jubail</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Mount Lebanon</t>
         </is>
       </c>
     </row>
@@ -87041,7 +87051,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Al Kattara</t>
+          <t>Alita</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -87063,7 +87073,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Alita</t>
+          <t>Arab El-Haibe</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -87085,7 +87095,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Arab El-Haibe</t>
+          <t>Aïn-El-Ghouaibé</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -87107,7 +87117,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Aïn-El-Ghouaibé</t>
+          <t>Aïn-el-Delbé</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -87129,7 +87139,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Aïn-el-Delbé</t>
+          <t>Belhos</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -87151,7 +87161,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Belhos</t>
+          <t>Berket Hejoula</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -87173,7 +87183,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Berket Hejoula</t>
+          <t>Bintaél (Fdar-El-Soufla)</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -87195,7 +87205,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Bintaél (Fdar-El-Soufla)</t>
+          <t>Breige</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -87217,7 +87227,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Breige</t>
+          <t>Deir Mar Sarkis</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -87239,7 +87249,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Deir Mar Sarkis</t>
+          <t>El-Jlaicé</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -87261,7 +87271,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>El-Jlaicé</t>
+          <t>El-Kfoune</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -87283,7 +87293,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>El-Kfoune</t>
+          <t>El-Mouncef</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -87305,7 +87315,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>El-Mouncef</t>
+          <t>Hboub</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -87327,7 +87337,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Hboub</t>
+          <t>Hedayné</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -87349,7 +87359,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Hedayné</t>
+          <t>Jouret-el-Kattine</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -87371,7 +87381,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Jouret-el-Kattine</t>
+          <t>Kartaboune</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -87393,7 +87403,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Kartaboune</t>
+          <t>Kfar Kaouass</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -87415,7 +87425,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Kfar Kaouass</t>
+          <t>Kfar-Mashoune et Dmalsa</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -87437,7 +87447,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Kfar-Mashoune et Dmalsa</t>
+          <t>Mastita</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -87459,7 +87469,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Mastita</t>
+          <t>Mazraet-el-Siyad</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -87481,7 +87491,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Mazraet-el-Siyad</t>
+          <t>Mechmech</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -87503,7 +87513,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Mechmech</t>
+          <t>Mehrine</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -87525,7 +87535,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Mehrine</t>
+          <t>Sarhita</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -87547,7 +87557,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Sarhita</t>
+          <t>Sirine</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -87569,7 +87579,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Sirine</t>
+          <t>Tedmor et Serghal</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -87591,7 +87601,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Tedmor et Serghal</t>
+          <t>litige</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -87613,12 +87623,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>litige</t>
+          <t>Aïn El-Delbé</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Jubail</t>
+          <t>Kasrouane</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -87635,7 +87645,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Aïn El-Delbé</t>
+          <t>Aïntoura</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -87657,7 +87667,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Aïntoura</t>
+          <t>Boukak El-Dine</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -87679,7 +87689,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Boukak El-Dine</t>
+          <t>Deir Baklouche</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -87701,7 +87711,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Deir Baklouche</t>
+          <t>Djounié Salel Alma</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -87723,7 +87733,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Djounié Salel Alma</t>
+          <t>Djounié Sarba</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -87745,7 +87755,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Djounié Sarba</t>
+          <t>El-Abri et Chouan</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -87767,7 +87777,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>El-Abri et Chouan</t>
+          <t>El-Mghaer</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -87789,7 +87799,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>El-Mghaer</t>
+          <t>Jouret Mhad</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -87811,7 +87821,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Jouret Mhad</t>
+          <t>Kharayeb Nahr Ibrahim</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -87833,7 +87843,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Kharayeb Nahr Ibrahim</t>
+          <t>Mazraet El-Ras</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -87855,7 +87865,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Mazraet El-Ras</t>
+          <t>Mazraet Mrah el-Mir</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -87877,7 +87887,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Mazraet Mrah el-Mir</t>
+          <t>Mouchaa Kesrouan (Faraya)</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -87899,7 +87909,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Mouchaa Kesrouan (Faraya)</t>
+          <t>Mouchaa Kesrouan (Kfardebian)</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -87921,7 +87931,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Mouchaa Kesrouan (Kfardebian)</t>
+          <t>Nammoura et Kfar Jerif</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -87943,7 +87953,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Nammoura et Kfar Jerif</t>
+          <t>Souhailet El-Faouka</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -87965,7 +87975,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Souhailet El-Faouka</t>
+          <t>Wata Salam</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -87987,7 +87997,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Wata Salam</t>
+          <t>litige</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -88009,17 +88019,17 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>litige</t>
+          <t>Al-Boukaia</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Kasrouane</t>
+          <t>Koura</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Mount Lebanon</t>
+          <t>North</t>
         </is>
       </c>
     </row>
@@ -88031,7 +88041,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Al-Boukaia</t>
+          <t>Al-Hraïché</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -88053,7 +88063,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Al-Hraïché</t>
+          <t>Belmand</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -88075,7 +88085,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Belmand</t>
+          <t>Kfar Hatta</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -88097,17 +88107,17 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Kfar Hatta</t>
+          <t>Adchite El-Koussair</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Koura</t>
+          <t>Marjaayoun</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Nabatiyeh</t>
         </is>
       </c>
     </row>
@@ -88119,7 +88129,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Adchite El-Koussair</t>
+          <t>Adeicé</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -88141,7 +88151,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Adeicé</t>
+          <t>Deir Mimas Doumiat</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -88163,7 +88173,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Deir Mimas Doumiat</t>
+          <t>El-Amra</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -88185,7 +88195,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>El-Amra</t>
+          <t>El-Kherbeh</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -88207,7 +88217,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>El-Kherbeh</t>
+          <t>Houra</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -88229,7 +88239,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Houra</t>
+          <t>Mazraet el-Sarada</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -88251,7 +88261,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Mazraet el-Sarada</t>
+          <t>Mazraet-El-Jrein</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -88273,7 +88283,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Mazraet-El-Jrein</t>
+          <t>Merjayoun</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -88295,7 +88305,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Merjayoun</t>
+          <t>Rabb Salacine</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -88317,17 +88327,17 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Rabb Salacine</t>
+          <t>Aassaymout</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Marjaayoun</t>
+          <t>Minieh-Danieh</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Nabatiyeh</t>
+          <t>North</t>
         </is>
       </c>
     </row>
@@ -88339,7 +88349,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Aassaymout</t>
+          <t>Al-Beddaoui</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -88361,7 +88371,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Al-Beddaoui</t>
+          <t>Al-Minieh</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -88383,7 +88393,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Al-Minieh</t>
+          <t>Al-Rihanié</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -88393,7 +88403,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Akkar</t>
         </is>
       </c>
     </row>
@@ -88405,7 +88415,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Al-Rihanié</t>
+          <t>Azka</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -88415,7 +88425,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Akkar</t>
+          <t>North</t>
         </is>
       </c>
     </row>
@@ -88427,7 +88437,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Azka</t>
+          <t>Bchnnata</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -88449,7 +88459,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Bchnnata</t>
+          <t>Bechhara</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -88471,7 +88481,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Bechhara</t>
+          <t>Beit Zaoud</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -88493,7 +88503,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Beit Zaoud</t>
+          <t>Btehline</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -88515,7 +88525,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Btehline</t>
+          <t>Debaael</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -88537,7 +88547,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Debaael</t>
+          <t>El-Watié et Harf Siad</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -88559,7 +88569,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>El-Watié et Harf Siad</t>
+          <t>Jarjoura</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -88581,7 +88591,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Jarjoura</t>
+          <t>Jaroun</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -88603,7 +88613,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Jaroun</t>
+          <t>Kfar Bibnine</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -88625,7 +88635,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Kfar Bibnine</t>
+          <t>Kharnoub</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -88647,7 +88657,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Kharnoub</t>
+          <t>Mazraat Ketrane</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -88669,7 +88679,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Mazraat Ketrane</t>
+          <t>Mazraet El-Krême</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -88691,7 +88701,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Mazraet El-Krême</t>
+          <t>Mrabine</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -88713,7 +88723,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Mrabine</t>
+          <t>Nemrine et Bakoura</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -88735,7 +88745,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Nemrine et Bakoura</t>
+          <t>Qraine</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -88757,7 +88767,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Qraine</t>
+          <t>Tourbol</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -88779,7 +88789,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Tourbol</t>
+          <t>Zouk Bhanine</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -88801,7 +88811,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Zouk Bhanine</t>
+          <t>litige</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -88823,17 +88833,17 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>litige</t>
+          <t>Abba</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Minieh-Danieh</t>
+          <t>Nabatiyeh</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Nabatiyeh</t>
         </is>
       </c>
     </row>
@@ -88845,7 +88855,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Abba</t>
+          <t>Ali El-Taher</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -88867,7 +88877,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Ali El-Taher</t>
+          <t>Bfarwé</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -88889,7 +88899,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Bfarwé</t>
+          <t>El-Hamra</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -88911,7 +88921,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>El-Hamra</t>
+          <t>Hmaïla</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -88933,7 +88943,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Hmaïla</t>
+          <t>Izzé</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -88955,7 +88965,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Izzé</t>
+          <t>Jernaya</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -88965,7 +88975,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Nabatiyeh</t>
+          <t>South</t>
         </is>
       </c>
     </row>
@@ -88977,7 +88987,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Jernaya</t>
+          <t>Kafr Dajjal</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -88987,7 +88997,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Nabatiyeh</t>
         </is>
       </c>
     </row>
@@ -88999,7 +89009,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Kafr Dajjal</t>
+          <t>Kfar Remmane</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -89021,7 +89031,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Kfar Remmane</t>
+          <t>Ksaibé</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -89043,7 +89053,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Ksaibé</t>
+          <t>Mazraat-el-Khreibé</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -89065,7 +89075,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Mazraat-el-Khreibé</t>
+          <t>Mazraet Bsaffour</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -89087,7 +89097,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Mazraet Bsaffour</t>
+          <t>Mazraet Chaal Baal</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -89109,7 +89119,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Mazraet Chaal Baal</t>
+          <t>Mazraet Dmoul</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -89131,7 +89141,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Mazraet Dmoul</t>
+          <t>Mazraet El-Bayad</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -89153,7 +89163,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Mazraet El-Bayad</t>
+          <t>Mazraet Kalaat Meiss</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -89175,7 +89185,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Mazraet Kalaat Meiss</t>
+          <t>Mazraet Kfar Jaouz</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -89197,17 +89207,17 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Mazraet Kfar Jaouz</t>
+          <t>Aïn Horché</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Nabatiyeh</t>
+          <t>Rachiaya</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Nabatiyeh</t>
+          <t>Bekaa</t>
         </is>
       </c>
     </row>
@@ -89219,7 +89229,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Aïn Horché</t>
+          <t>Conflict</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -89241,7 +89251,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Conflict</t>
+          <t>Haouche El-Kannabé</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -89263,7 +89273,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Haouche El-Kannabé</t>
+          <t>Kfar Dinès</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -89285,7 +89295,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Kfar Dinès</t>
+          <t>Kfar Kouk</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -89307,7 +89317,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Kfar Kouk</t>
+          <t>Mohaïdcé</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -89329,7 +89339,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Mohaïdcé</t>
+          <t>Nabi Safa</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -89351,7 +89361,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Nabi Safa</t>
+          <t>litige</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -89373,17 +89383,17 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>litige</t>
+          <t>Arab Soukar</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Rachiaya</t>
+          <t>Saida</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Bekaa</t>
+          <t>South</t>
         </is>
       </c>
     </row>
@@ -89395,7 +89405,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Arab Soukar</t>
+          <t>Aïn-el-Dib</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -89417,7 +89427,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Aïn-el-Dib</t>
+          <t>Daoudiyé</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -89439,7 +89449,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Daoudiyé</t>
+          <t>Deir Takla</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -89461,7 +89471,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Deir Takla</t>
+          <t>El Hartiyé</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -89483,7 +89493,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>El Hartiyé</t>
+          <t>El-Hajjé</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -89505,7 +89515,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>El-Hajjé</t>
+          <t>El-Husseiniyé</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -89527,7 +89537,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>El-Husseiniyé</t>
+          <t>El-Mhammariyé</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -89549,7 +89559,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>El-Mhammariyé</t>
+          <t>Jaziré</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -89571,7 +89581,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Jaziré</t>
+          <t>Kaoutarite El-Riz</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -89593,7 +89603,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Kaoutarite El-Riz</t>
+          <t>Kaoutarite El-Siyad</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -89615,7 +89625,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Kaoutarite El-Siyad</t>
+          <t>Kfar Badda</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -89637,7 +89647,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Kfar Badda</t>
+          <t>Kfar Hatta</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -89659,7 +89669,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Kfar Hatta</t>
+          <t>Kherbet Bassal</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -89681,7 +89691,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Kherbet Bassal</t>
+          <t>Kherbet El-Douair</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -89703,7 +89713,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Kherbet El-Douair</t>
+          <t>Matriet El-Choumar</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -89725,7 +89735,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Matriet El-Choumar</t>
+          <t>Mazraat El-Wasta</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -89747,7 +89757,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Mazraat El-Wasta</t>
+          <t>Mazraat Jimjim</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -89769,7 +89779,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Mazraat Jimjim</t>
+          <t>Mazraet Matarite Jebah</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -89791,7 +89801,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Mazraet Matarite Jebah</t>
+          <t>Miemié</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -89813,7 +89823,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Miemié</t>
+          <t>Mohaidalé</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -89835,7 +89845,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Mohaidalé</t>
+          <t>Msaileh</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -89857,7 +89867,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Msaileh</t>
+          <t>Samiate</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -89879,7 +89889,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Samiate</t>
+          <t>Sari</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -89901,7 +89911,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Sari</t>
+          <t>Saïda Ville</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -89923,7 +89933,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Saïda Ville</t>
+          <t>Sfenté</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -89945,7 +89955,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Sfenté</t>
+          <t>Snaiber</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -89967,7 +89977,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Snaiber</t>
+          <t>Tibna</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -89989,7 +89999,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Tibna</t>
+          <t>Yahoudiat</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -90011,12 +90021,12 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Yahoudiat</t>
+          <t>Aaiyé</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Saida</t>
+          <t>Sour</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -90033,7 +90043,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Aaiyé</t>
+          <t>Abou Chech</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -90055,7 +90065,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Abou Chech</t>
+          <t>Bazouriat</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -90077,7 +90087,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Bazouriat</t>
+          <t>Bestiace</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -90099,7 +90109,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Bestiace</t>
+          <t>Btaychiyé</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -90121,7 +90131,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Btaychiyé</t>
+          <t>Chameh</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -90143,7 +90153,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Chameh</t>
+          <t>Debhalé</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -90165,7 +90175,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Debhalé</t>
+          <t>Eskandaroun</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -90187,7 +90197,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Eskandaroun</t>
+          <t>Hamoul</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -90209,7 +90219,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Hamoul</t>
+          <t>Hmairé</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -90231,7 +90241,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Hmairé</t>
+          <t>Izzié</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -90253,7 +90263,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Izzié</t>
+          <t>Jejime</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -90275,7 +90285,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Jejime</t>
+          <t>Kneissé</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -90297,7 +90307,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Kneissé</t>
+          <t>Mahaïlib</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -90319,7 +90329,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Mahaïlib</t>
+          <t>Mazraat Dhaira</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -90341,7 +90351,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Mazraat Dhaira</t>
+          <t>Mazraat Ez-Zalloutieh</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -90363,7 +90373,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Mazraat Ez-Zalloutieh</t>
+          <t>Mazraat Torsemhat</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -90385,7 +90395,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Mazraat Torsemhat</t>
+          <t>Niha</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -90407,7 +90417,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Niha</t>
+          <t>Rafid-el-Mernaba</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -90429,7 +90439,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Rafid-el-Mernaba</t>
+          <t>Tairzibna</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -90451,7 +90461,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Tairzibna</t>
+          <t>Trafelsiyé</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -90473,17 +90483,17 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Trafelsiyé</t>
+          <t>Al-Mina No1</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Sour</t>
+          <t>Tripoli</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
     </row>
@@ -90495,7 +90505,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Al-Mina No1</t>
+          <t>Al-Mina No2</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -90517,7 +90527,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Al-Mina No2</t>
+          <t>Al-Mina No3</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -90539,7 +90549,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Al-Mina No3</t>
+          <t>Tripoli Al-Kobbé</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -90561,7 +90571,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Tripoli Al-Kobbé</t>
+          <t>Tripoli Al-Mouhaitra</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -90583,7 +90593,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Tripoli Al-Mouhaitra</t>
+          <t>Tripoli Al-Rmmanieh</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -90605,7 +90615,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Tripoli Al-Rmmanieh</t>
+          <t>Tripoli Al-Souéka</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -90627,7 +90637,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Tripoli Al-Souéka</t>
+          <t>Tripoli Al-Tabbaneh</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -90649,7 +90659,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Tripoli Al-Tabbaneh</t>
+          <t>Tripoli Al-Tal</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -90671,7 +90681,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Tripoli Al-Tal</t>
+          <t>Tripoli Al-Zehrieh</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -90693,7 +90703,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Tripoli Al-Zehrieh</t>
+          <t>Tripoli Jardins</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -90715,7 +90725,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Tripoli Jardins</t>
+          <t>Tripoli Zeitoun</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -90737,17 +90747,17 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Tripoli Zeitoun</t>
+          <t>Al-Djeziré</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Tripoli</t>
+          <t>West Bekaa</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Bekaa</t>
         </is>
       </c>
     </row>
@@ -90759,7 +90769,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Al-Djeziré</t>
+          <t>Al-Istable</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -90781,7 +90791,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Al-Istable</t>
+          <t>Al-Wakf</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -90803,7 +90813,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Al-Wakf</t>
+          <t>Ammik et "Jouret Ammik"</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -90825,7 +90835,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Ammik et "Jouret Ammik"</t>
+          <t>Aïn-el-Tiné</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -90847,7 +90857,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Aïn-el-Tiné</t>
+          <t>Chouberkié "Ammik"</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -90869,7 +90879,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Chouberkié "Ammik"</t>
+          <t>Dair Tahmiche</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -90891,7 +90901,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Dair Tahmiche</t>
+          <t>Deir-Aïn-el-Jaouzé</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -90913,7 +90923,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Deir-Aïn-el-Jaouzé</t>
+          <t>Harime-el-Soughra</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -90935,7 +90945,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Harime-el-Soughra</t>
+          <t>Khiara-el-Atika</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -90957,12 +90967,12 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Khiara-el-Atika</t>
+          <t>Al-Mazraa</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>West Bekaa</t>
+          <t>Zahleh</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -90979,7 +90989,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Al-Mazraa</t>
+          <t>Chouberkié  Tabet</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -91001,7 +91011,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Chouberkié  Tabet</t>
+          <t>Conflict</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -91023,7 +91033,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Conflict</t>
+          <t>Haouche Kaissar</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -91045,7 +91055,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Haouche Kaissar</t>
+          <t>Haouche Sayadi</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -91067,7 +91077,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Haouche Sayadi</t>
+          <t>Haouche-al-Omara (Terres)</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -91089,7 +91099,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Haouche-al-Omara (Terres)</t>
+          <t>Hochemoche</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -91111,7 +91121,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Hochemoche</t>
+          <t>Ksara</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -91133,7 +91143,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Ksara</t>
+          <t>Maallaka (Terres)</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -91155,7 +91165,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Maallaka (Terres)</t>
+          <t>Maazraat-el-Ramtanieh</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -91177,7 +91187,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Maazraat-el-Ramtanieh</t>
+          <t>Mandara</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -91199,7 +91209,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Mandara</t>
+          <t>Mejdel-Anjar</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -91221,7 +91231,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Mejdel-Anjar</t>
+          <t>Nasriyat Rizk</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -91243,7 +91253,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Nasriyat Rizk</t>
+          <t>Tal-al-Amara</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -91265,7 +91275,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Tal-al-Amara</t>
+          <t>Tchiflik Eddé</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -91287,7 +91297,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Tchiflik Eddé</t>
+          <t>Tchiflik Kikano</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -91309,7 +91319,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Tchiflik Kikano</t>
+          <t>Wadi-el-Arayeche</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -91331,7 +91341,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Wadi-el-Arayeche</t>
+          <t>Zahlé (Terres)</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -91353,7 +91363,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Zahlé (Terres)</t>
+          <t>Zahlé Maallaka Kerek</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -91375,7 +91385,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Zahlé Maallaka Kerek</t>
+          <t>Zahlé Mar Gérios</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -91397,7 +91407,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Zahlé Mar Gérios</t>
+          <t>Zebdol</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -91419,17 +91429,17 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Zebdol</t>
+          <t>Aadoua</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Zahleh</t>
+          <t>Zgharta</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>Bekaa</t>
+          <t>North</t>
         </is>
       </c>
     </row>
@@ -91441,7 +91451,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Aadoua</t>
+          <t>Al-Harik</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -91463,7 +91473,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Al-Harik</t>
+          <t>Al-Jdeidé</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -91485,7 +91495,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Al-Jdeidé</t>
+          <t>Al-Khaldyé</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -91507,7 +91517,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Al-Khaldyé</t>
+          <t>Arbet Koshaya</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -91529,7 +91539,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Arbet Koshaya</t>
+          <t>Ardate</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -91551,7 +91561,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Ardate</t>
+          <t>Bsebhil</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -91573,7 +91583,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Bsebhil</t>
+          <t>Danhi</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -91595,7 +91605,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Danhi</t>
+          <t>Ehden</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -91617,7 +91627,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Ehden</t>
+          <t>Ejbeh</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -91639,7 +91649,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Ejbeh</t>
+          <t>El-Tellé</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -91661,7 +91671,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>El-Tellé</t>
+          <t>Mazraat Ejbeh</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -91683,7 +91693,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Mazraat Ejbeh</t>
+          <t>Mazraat Jneide</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -91705,7 +91715,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Mazraat Jneide</t>
+          <t>Mejdlaya</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -91727,7 +91737,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Mejdlaya</t>
+          <t>Merh Kfarsghabe</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -91749,7 +91759,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Merh Kfarsghabe</t>
+          <t>Sakhra</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -91766,22 +91776,22 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Sakhra</t>
+          <t>راشكده</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Zgharta</t>
+          <t>البترون</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>الشمال</t>
         </is>
       </c>
     </row>
@@ -91793,7 +91803,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>راشكده</t>
+          <t>عورا</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -91815,7 +91825,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>عورا</t>
+          <t>غوما</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -91837,7 +91847,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>غوما</t>
+          <t>قندولا</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -91859,17 +91869,17 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>قندولا</t>
+          <t>الدبية</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>البترون</t>
+          <t>الشوف</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>الشمال</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -91881,7 +91891,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>الدبية</t>
+          <t>المحتقره دير المخلص</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -91903,7 +91913,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>المحتقره دير المخلص</t>
+          <t>الناعمه</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -91925,7 +91935,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>الناعمه</t>
+          <t>بقعاتا</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -91947,7 +91957,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>بقعاتا</t>
+          <t>جديدة الشوف</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -91969,7 +91979,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>جديدة الشوف</t>
+          <t>حارة الناعمه</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -91991,7 +92001,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>حارة الناعمه</t>
+          <t>حارة بعاصير</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -92013,7 +92023,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>حارة بعاصير</t>
+          <t>عين الاسد والشميس</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -92035,7 +92045,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>عين الاسد والشميس</t>
+          <t>عين الحور</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -92057,7 +92067,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>عين الحور</t>
+          <t>كليليه</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -92079,7 +92089,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>كليليه</t>
+          <t>مرج برجا</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -92101,7 +92111,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>مرج برجا</t>
+          <t>وادي دير دوريت</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -92123,17 +92133,17 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>وادي دير دوريت</t>
+          <t>الروضة</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>الشوف</t>
+          <t>الضنية</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>الشمال</t>
         </is>
       </c>
     </row>
@@ -92145,7 +92155,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>الروضة</t>
+          <t>المطل</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -92167,7 +92177,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>المطل</t>
+          <t>حرف السياد</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -92189,7 +92199,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>حرف السياد</t>
+          <t>عزقي</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -92211,7 +92221,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>عزقي</t>
+          <t>قزحيا</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -92233,7 +92243,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>قزحيا</t>
+          <t>كرم المهر</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -92255,7 +92265,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>كرم المهر</t>
+          <t>كفربنين</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -92277,7 +92287,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>كفربنين</t>
+          <t>نمرين</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -92299,12 +92309,12 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>نمرين</t>
+          <t>البحصاص</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>الضنية</t>
+          <t>الكورة</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
@@ -92321,7 +92331,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>البحصاص</t>
+          <t>حارة الخاصة</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -92343,7 +92353,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>حارة الخاصة</t>
+          <t>ضهر العين</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -92365,7 +92375,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>ضهر العين</t>
+          <t>ضهور الهوا</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -92387,17 +92397,17 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>ضهور الهوا</t>
+          <t>الرابية</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>الكورة</t>
+          <t>المتن</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>الشمال</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -92409,7 +92419,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>الرابية</t>
+          <t>سد البوشريه</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -92431,7 +92441,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>سد البوشريه</t>
+          <t>مزرعة بنابيل</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -92453,17 +92463,17 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>مزرعة بنابيل</t>
+          <t>المنية</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>المتن</t>
+          <t>المنية</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>الشمال</t>
         </is>
       </c>
     </row>
@@ -92475,17 +92485,17 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>المنية</t>
+          <t>كفروة</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>المنية</t>
+          <t>النبطية</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>الشمال</t>
+          <t>النبطية</t>
         </is>
       </c>
     </row>
@@ -92497,17 +92507,17 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>كفروة</t>
+          <t>المغر وبلا</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>النبطية</t>
+          <t>بشري</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>النبطية</t>
+          <t>الشمال</t>
         </is>
       </c>
     </row>
@@ -92519,17 +92529,17 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>المغر وبلا</t>
+          <t>الحدث شمالي</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>بشري</t>
+          <t>بعبدا</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>الشمال</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -92541,7 +92551,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>الحدث شمالي</t>
+          <t>الحدث قبلي</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -92563,7 +92573,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>الحدث قبلي</t>
+          <t>الشياح حي الكنيسة</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -92585,7 +92595,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>الشياح حي الكنيسة</t>
+          <t>الشياح حي كرم الزيتون</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -92607,7 +92617,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>الشياح حي كرم الزيتون</t>
+          <t>الغبيري بئر حسن</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -92629,7 +92639,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>الغبيري بئر حسن</t>
+          <t>الغبيري حي الجامع</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -92651,7 +92661,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>الغبيري حي الجامع</t>
+          <t>الفياضية</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -92673,7 +92683,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>الفياضية</t>
+          <t>القلعه</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -92695,7 +92705,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>القلعه</t>
+          <t>المريجه</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -92717,7 +92727,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>المريجه</t>
+          <t>تحويطة النهر</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -92739,7 +92749,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>تحويطة النهر</t>
+          <t>حارة البطم</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -92761,7 +92771,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>حارة البطم</t>
+          <t>حارة حريك قرانوح</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -92783,7 +92793,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>حارة حريك قرانوح</t>
+          <t>دير مار الياس الكحلونية</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -92805,7 +92815,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>دير مار الياس الكحلونية</t>
+          <t>سبنيه</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -92827,7 +92837,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>سبنيه</t>
+          <t>قبيع</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -92849,17 +92859,17 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>قبيع</t>
+          <t>حداثا</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>بعبدا</t>
+          <t>بنت جبيل</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>النبطية</t>
         </is>
       </c>
     </row>
@@ -92871,7 +92881,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>حداثا</t>
+          <t>عيتا الجبل</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -92893,17 +92903,17 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>عيتا الجبل</t>
+          <t>الجليسه</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>بنت جبيل</t>
+          <t>جبيل</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>النبطية</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -92915,7 +92925,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>الجليسه</t>
+          <t>العاقورة - م</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -92937,7 +92947,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>العاقورة - م</t>
+          <t>الفيدار</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -92959,7 +92969,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>الفيدار</t>
+          <t>المزاريب</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -92981,7 +92991,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>المزاريب</t>
+          <t>المنصف</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -93003,7 +93013,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>المنصف</t>
+          <t>بنتاعل</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -93025,7 +93035,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>بنتاعل</t>
+          <t>دملصا</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -93047,7 +93057,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>دملصا</t>
+          <t>دير القطاره</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -93069,7 +93079,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>دير القطاره</t>
+          <t>سرعيتا</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -93091,7 +93101,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>سرعيتا</t>
+          <t>عين الدلبة</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -93113,7 +93123,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>عين الدلبة</t>
+          <t>عين الشلال</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -93135,7 +93145,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>عين الشلال</t>
+          <t>عين الغويبة</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -93157,7 +93167,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>عين الغويبة</t>
+          <t>قرطبا الشمالية</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -93179,7 +93189,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>قرطبا الشمالية</t>
+          <t>كفر مسحون</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -93201,7 +93211,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>كفر مسحون</t>
+          <t>مزرعة السياد</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -93223,17 +93233,17 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>مزرعة السياد</t>
+          <t>بحنين - كفرتعلا</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>جبيل</t>
+          <t>جزين</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>الجنوب</t>
         </is>
       </c>
     </row>
@@ -93245,7 +93255,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>بحنين - كفرتعلا</t>
+          <t>عين مجدلين</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -93267,7 +93277,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>عين مجدلين</t>
+          <t>لبعه</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -93289,17 +93299,17 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>قتالة</t>
+          <t>الكرمة</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>جزين</t>
+          <t>زحلة</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>الجنوب</t>
+          <t>البقاع</t>
         </is>
       </c>
     </row>
@@ -93311,17 +93321,17 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>لبعه</t>
+          <t>بتياس</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>جزين</t>
+          <t>زحلة</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>الجنوب</t>
+          <t>البقاع</t>
         </is>
       </c>
     </row>
@@ -93333,7 +93343,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>الكرمة</t>
+          <t>جلالا</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -93355,7 +93365,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>بتياس</t>
+          <t>حاجي حببلي</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -93377,7 +93387,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>جلالا</t>
+          <t>حي السلم</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -93399,7 +93409,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>حاجي حببلي</t>
+          <t>حي الفيكاني</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -93421,7 +93431,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>حي السلم</t>
+          <t>خضر بك</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -93443,7 +93453,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>حي الفيكاني</t>
+          <t>زحلة المعلقه</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -93465,7 +93475,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>خضر بك</t>
+          <t>زحلة المعلقه الشمالي</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -93487,7 +93497,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>زحلة المعلقه</t>
+          <t>زحلة حي السيدة</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -93509,7 +93519,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>زحلة المعلقه الشمالي</t>
+          <t>زحلة كرك نوح</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -93531,7 +93541,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>زحلة حي السيدة</t>
+          <t>زحلة مار مخايل</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -93553,7 +93563,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>زحلة كرك نوح</t>
+          <t>زحلة وادي العرايش</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -93575,7 +93585,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>زحلة مار مخايل</t>
+          <t>شهابية الفاعور</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -93597,7 +93607,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>زحلة وادي العرايش</t>
+          <t>كابوسية</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -93619,7 +93629,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>شهابية الفاعور</t>
+          <t>يوغون اولوك</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
@@ -93641,17 +93651,17 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>كابوسية</t>
+          <t>اجبع</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>زحلة</t>
+          <t>زغرتا</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>البقاع</t>
+          <t>الشمال</t>
         </is>
       </c>
     </row>
@@ -93663,17 +93673,17 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>يوغون اولوك</t>
+          <t>اسلوت</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>زحلة</t>
+          <t>زغرتا</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>البقاع</t>
+          <t>الشمال</t>
         </is>
       </c>
     </row>
@@ -93685,7 +93695,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>اجبع</t>
+          <t>القادريه</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -93707,7 +93717,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>اسلوت</t>
+          <t>بيت عبيد</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -93729,7 +93739,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>القادريه</t>
+          <t>بيت عوكر</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -93751,7 +93761,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>بيت عبيد</t>
+          <t>حارة الفوار</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -93773,7 +93783,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>بيت عوكر</t>
+          <t>حرف ارده</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -93795,7 +93805,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>حارة الفوار</t>
+          <t>حرف مزيارة</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -93817,7 +93827,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>حرف ارده</t>
+          <t>عربة قزحيا</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -93839,7 +93849,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>حرف مزيارة</t>
+          <t>مزرعة الفريديس</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -93861,7 +93871,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>عربة قزحيا</t>
+          <t>مزرعة حوقا</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -93883,17 +93893,17 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>مزرعة الفريديس</t>
+          <t>البازوريه</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>زغرتا</t>
+          <t>صور</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>الشمال</t>
+          <t>الجنوب</t>
         </is>
       </c>
     </row>
@@ -93905,17 +93915,17 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>مزرعة حوقا</t>
+          <t>البرغليه</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>زغرتا</t>
+          <t>صور</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>الشمال</t>
+          <t>الجنوب</t>
         </is>
       </c>
     </row>
@@ -93927,7 +93937,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>البازوريه</t>
+          <t>البساتين</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -93949,7 +93959,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>البرغليه</t>
+          <t>البص  قسم 1</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -93971,7 +93981,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>البساتين</t>
+          <t>البص  قسم 3</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -93993,7 +94003,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>البص  قسم 1</t>
+          <t>البص قسم 5</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -94015,7 +94025,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>البص  قسم 3</t>
+          <t>الحميري</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -94037,7 +94047,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>البص قسم 5</t>
+          <t>الرشيديه</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -94059,7 +94069,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>الحميري</t>
+          <t>الزلوطية</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -94081,7 +94091,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>الرشيديه</t>
+          <t>السماعية</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -94103,7 +94113,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>الزلوطية</t>
+          <t>الشهابية</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -94125,7 +94135,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>السماعية</t>
+          <t>الظهيرة</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -94147,7 +94157,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>الشهابية</t>
+          <t>المالكية</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -94169,7 +94179,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>الظهيرة</t>
+          <t>بثتيات</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -94191,7 +94201,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>المالكية</t>
+          <t>شبريحا</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -94213,7 +94223,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>بثتيات</t>
+          <t>شمع</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -94235,7 +94245,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>شبريحا</t>
+          <t>صور حي الارثوذكس</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -94257,7 +94267,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>شمع</t>
+          <t>صور حي الجامع</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -94279,7 +94289,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>صور حي الارثوذكس</t>
+          <t>صور حي الجورة</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -94301,7 +94311,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>صور حي الجامع</t>
+          <t>صور حي الحسينية</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -94323,7 +94333,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>صور حي الجورة</t>
+          <t>صور حي الكاثوليك</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
@@ -94345,7 +94355,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>صور حي الحسينية</t>
+          <t>صور حي المصاروي</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -94367,7 +94377,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>صور حي الكاثوليك</t>
+          <t>صور حي المنارة</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
@@ -94389,7 +94399,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>صور حي المصاروي</t>
+          <t>صور حي الموارنة</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -94411,7 +94421,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>صور حي المنارة</t>
+          <t>عين الزرقا</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -94433,7 +94443,7 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>صور حي الموارنة</t>
+          <t>محرونه</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -94455,17 +94465,17 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>عين الزرقا</t>
+          <t>البساتين</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>صور</t>
+          <t>عاليه</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>الجنوب</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -94477,17 +94487,17 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>محرونه</t>
+          <t>التعزانية</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>صور</t>
+          <t>عاليه</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>الجنوب</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -94499,7 +94509,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>البساتين</t>
+          <t>جسر القاضي</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -94521,7 +94531,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>التعزانية</t>
+          <t>عاليه قبلي</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -94543,7 +94553,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>جسر القاضي</t>
+          <t>عاليه وسطاني</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -94565,7 +94575,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>عاليه قبلي</t>
+          <t>عين الفريديس</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -94587,7 +94597,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>عاليه وسطاني</t>
+          <t>محطة بحمدون</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -94609,17 +94619,17 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>عين الفريديس</t>
+          <t>البساتين</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>عاليه</t>
+          <t>عكار</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>عكار</t>
         </is>
       </c>
     </row>
@@ -94631,17 +94641,17 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>محطة بحمدون</t>
+          <t>البقيعة</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>عاليه</t>
+          <t>عكار</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>عكار</t>
         </is>
       </c>
     </row>
@@ -94653,7 +94663,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>البساتين</t>
+          <t>الحويش</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -94675,7 +94685,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>البقيعة</t>
+          <t>الدوسه</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -94697,7 +94707,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>الحويش</t>
+          <t>السهلة</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -94719,7 +94729,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>الدوسه</t>
+          <t>الشيخ عياش</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
@@ -94741,7 +94751,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>السهلة</t>
+          <t>العماير</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -94763,7 +94773,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>الشيخ عياش</t>
+          <t>العوادة</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -94785,7 +94795,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>العماير</t>
+          <t>الفرض</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -94807,7 +94817,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>العوادة</t>
+          <t>القبيات الذوق</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -94829,7 +94839,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>الفرض</t>
+          <t>القبيات الضهر</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -94851,7 +94861,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>القبيات الذوق</t>
+          <t>القبيات الغربية</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -94873,7 +94883,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>القبيات الضهر</t>
+          <t>القبيات القطلبه</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -94895,7 +94905,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>القبيات الغربية</t>
+          <t>القبيات غوايا</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -94917,7 +94927,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>القبيات القطلبه</t>
+          <t>القبيات مرتموره</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -94939,7 +94949,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>القبيات غوايا</t>
+          <t>المونسة</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
@@ -94961,7 +94971,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>القبيات مرتموره</t>
+          <t>الهيشة</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -94983,7 +94993,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>المونسة</t>
+          <t>برج العرب</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
@@ -95005,7 +95015,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>الهيشة</t>
+          <t>بني صخر</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -95027,7 +95037,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>برج العرب</t>
+          <t>بيت الحاج</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -95049,7 +95059,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>بني صخر</t>
+          <t>تل معيان</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
@@ -95071,7 +95081,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>بيت الحاج</t>
+          <t>تلبيبة</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
@@ -95093,7 +95103,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>تل معيان</t>
+          <t>جبل المنصورة</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
@@ -95115,7 +95125,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>تلبيبة</t>
+          <t>جرمنايا</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -95137,7 +95147,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>جبل المنصورة</t>
+          <t>خربة الجرد</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -95159,7 +95169,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>جرمنايا</t>
+          <t>خريبة الجندي</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
@@ -95181,7 +95191,7 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>خربة الجرد</t>
+          <t>خط البترول</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
@@ -95203,7 +95213,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>خريبة الجندي</t>
+          <t>رجم عيسى</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
@@ -95225,7 +95235,7 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>خط البترول</t>
+          <t>ضهر القنبر</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
@@ -95247,7 +95257,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>رجم عيسى</t>
+          <t>عبودية</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
@@ -95269,7 +95279,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>ضهر القنبر</t>
+          <t>عين الذهب</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
@@ -95291,7 +95301,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>عبودية</t>
+          <t>قنية</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
@@ -95313,7 +95323,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>عين الذهب</t>
+          <t>كرم زبدين</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
@@ -95335,7 +95345,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>قنية</t>
+          <t>مراح الخوخ</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
@@ -95357,17 +95367,17 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>كرم زبدين</t>
+          <t>الحجة</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>عكار</t>
+          <t>قرى صيدا</t>
         </is>
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>عكار</t>
+          <t>الجنوب</t>
         </is>
       </c>
     </row>
@@ -95379,17 +95389,17 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>مراح الخوخ</t>
+          <t>القنيطرة</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>عكار</t>
+          <t>قرى صيدا</t>
         </is>
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>عكار</t>
+          <t>الجنوب</t>
         </is>
       </c>
     </row>
@@ -95401,7 +95411,7 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>الحجة</t>
+          <t>المعمرية</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
@@ -95423,7 +95433,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>القنيطرة</t>
+          <t>المية ومية</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
@@ -95445,7 +95455,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>المعمرية</t>
+          <t>كوثرية السياد</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
@@ -95467,17 +95477,17 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>المية ومية</t>
+          <t>الروضة</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>قرى صيدا</t>
+          <t>قضاءي البقاع الغربي وراشيا</t>
         </is>
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>الجنوب</t>
+          <t>البقاع</t>
         </is>
       </c>
     </row>
@@ -95489,17 +95499,17 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>كوثرية السياد</t>
+          <t>الشبرقية</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>قرى صيدا</t>
+          <t>قضاءي البقاع الغربي وراشيا</t>
         </is>
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>الجنوب</t>
+          <t>البقاع</t>
         </is>
       </c>
     </row>
@@ -95511,7 +95521,7 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>الروضة</t>
+          <t>عين التينه</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
@@ -95533,7 +95543,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>الشبرقية</t>
+          <t>كفردنيس</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
@@ -95555,7 +95565,7 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>عين التينه</t>
+          <t>كفرقوق</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
@@ -95577,7 +95587,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>كفردنيس</t>
+          <t>محيدثه</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
@@ -95599,17 +95609,17 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>كفرقوق</t>
+          <t>الانصار</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>قضاءي البقاع الغربي وراشيا</t>
+          <t>قضاءي بعلبك والهرمل</t>
         </is>
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>البقاع</t>
+          <t>بعلبك والهرمل</t>
         </is>
       </c>
     </row>
@@ -95621,17 +95631,17 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>محيدثه</t>
+          <t>البرانيه حي المسيحيين</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>قضاءي البقاع الغربي وراشيا</t>
+          <t>قضاءي بعلبك والهرمل</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>البقاع</t>
+          <t>بعلبك والهرمل</t>
         </is>
       </c>
     </row>
@@ -95643,7 +95653,7 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>الانصار</t>
+          <t>البرباره محلة المسيحيين</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
@@ -95665,7 +95675,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>البرانيه حي المسيحيين</t>
+          <t>البويضة</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
@@ -95687,7 +95697,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>البرباره محلة المسيحيين</t>
+          <t>البويضة الحي الغربي</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
@@ -95709,7 +95719,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>البويضة</t>
+          <t>البويضة الشمالية</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
@@ -95731,7 +95741,7 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>البويضة الحي الغربي</t>
+          <t>التوفيقيه</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
@@ -95753,7 +95763,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>البويضة الشمالية</t>
+          <t>الجوبانية</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
@@ -95775,7 +95785,7 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>التوفيقيه</t>
+          <t>الحدث الشمالي</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
@@ -95797,7 +95807,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>الجوبانية</t>
+          <t>الحدث الغربي</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
@@ -95819,7 +95829,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>الحدث الشمالي</t>
+          <t>الحريقه</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
@@ -95841,7 +95851,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>الحدث الغربي</t>
+          <t>الحلانيه</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
@@ -95863,7 +95873,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>الحريقه</t>
+          <t>الريش حي الشرقي</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
@@ -95885,7 +95895,7 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>الحلانيه</t>
+          <t>الريش حي الشميس</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
@@ -95907,7 +95917,7 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>الريش حي الشرقي</t>
+          <t>الريش حي الغربي</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
@@ -95929,7 +95939,7 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>الريش حي الشميس</t>
+          <t>الزرازير</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
@@ -95951,7 +95961,7 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>الريش حي الغربي</t>
+          <t>الزويتيني</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
@@ -95973,7 +95983,7 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>الزرازير</t>
+          <t>السعيده</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
@@ -95995,7 +96005,7 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>الزويتيني</t>
+          <t>السويسة</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
@@ -96017,7 +96027,7 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>السعيده</t>
+          <t>الشواغير التحتا</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
@@ -96039,7 +96049,7 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>السويسة</t>
+          <t>الشواغير الفوقا</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
@@ -96061,7 +96071,7 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>الشواغير التحتا</t>
+          <t>الصوانية</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
@@ -96083,7 +96093,7 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>الشواغير الفوقا</t>
+          <t>العقيدية</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
@@ -96105,7 +96115,7 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>الصوانية</t>
+          <t>العلاق</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
@@ -96127,7 +96137,7 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>العقيدية</t>
+          <t>الفاكهة حي الجامع</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
@@ -96149,7 +96159,7 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>العلاق</t>
+          <t>الفاكهة حي مار جرجس</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
@@ -96171,7 +96181,7 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>الفاكهة حي الجامع</t>
+          <t>القدام</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
@@ -96193,7 +96203,7 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>الفاكهة حي مار جرجس</t>
+          <t>القرينة</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
@@ -96215,7 +96225,7 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>القدام</t>
+          <t>القصر</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
@@ -96237,7 +96247,7 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>القرينة</t>
+          <t>الكواخ</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
@@ -96259,7 +96269,7 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>القصر</t>
+          <t>المعاصر</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
@@ -96281,7 +96291,7 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>الكواخ</t>
+          <t>النبي رشاده</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
@@ -96303,7 +96313,7 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>المعاصر</t>
+          <t>النبي نعام</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
@@ -96325,7 +96335,7 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>النبي رشاده</t>
+          <t>النقرة</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
@@ -96347,7 +96357,7 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>النبي نعام</t>
+          <t>بريصا</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
@@ -96369,7 +96379,7 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>النقرة</t>
+          <t>بيت ابو صليبي</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
@@ -96391,7 +96401,7 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>بريصا</t>
+          <t>جوار الحشيش</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
@@ -96413,7 +96423,7 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>بيت ابو صليبي</t>
+          <t>حوش السيد علي</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
@@ -96435,7 +96445,7 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>جوار الحشيش</t>
+          <t>حي الزهراء</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
@@ -96457,7 +96467,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>حوش السيد علي</t>
+          <t>حي الصلح</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
@@ -96479,7 +96489,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>حي الزهراء</t>
+          <t>حي العباسية</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
@@ -96501,7 +96511,7 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>حي الصلح</t>
+          <t>حي عز الدين</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
@@ -96523,7 +96533,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>حي العباسية</t>
+          <t>دار الواسعة</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
@@ -96545,7 +96555,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>حي عز الدين</t>
+          <t>رماسا</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
@@ -96567,7 +96577,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>دار الواسعة</t>
+          <t>سهلات الماء</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
@@ -96589,7 +96599,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>رماسا</t>
+          <t>شعت حي الضهر</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
@@ -96611,7 +96621,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>سهلات الماء</t>
+          <t>صفرا</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
@@ -96633,7 +96643,7 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>شعت حي الضهر</t>
+          <t>غفره</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
@@ -96655,7 +96665,7 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>صفرا</t>
+          <t>فلاوي</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
@@ -96677,7 +96687,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>غفره</t>
+          <t>فيسان</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
@@ -96699,7 +96709,7 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>فلاوي</t>
+          <t>قبة دورس</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
@@ -96721,7 +96731,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>فيسان</t>
+          <t>قلد السبع</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
@@ -96743,7 +96753,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>قبة دورس</t>
+          <t>قلعة</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
@@ -96765,7 +96775,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>قلد السبع</t>
+          <t>قلعة غربي</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
@@ -96787,7 +96797,7 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>قلعة</t>
+          <t>قنافذ</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
@@ -96809,7 +96819,7 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>قلعة غربي</t>
+          <t>كفردبش</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
@@ -96831,7 +96841,7 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>قنافذ</t>
+          <t>مراح العين</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
@@ -96853,7 +96863,7 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>كفردبش</t>
+          <t>مزرعة آل سويدان</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
@@ -96875,7 +96885,7 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>مراح العين</t>
+          <t>مزرعة ابو صليبي</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
@@ -96897,7 +96907,7 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>مزرعة آل سويدان</t>
+          <t>مزرعة التوت</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
@@ -96919,7 +96929,7 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>مزرعة ابو صليبي</t>
+          <t>مزرعة الضليل</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
@@ -96941,7 +96951,7 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>مزرعة التوت</t>
+          <t>مزرعة الفقيه</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
@@ -96963,7 +96973,7 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>مزرعة الضليل</t>
+          <t>مزرعة بيت الطشم</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
@@ -96985,7 +96995,7 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>مزرعة الفقيه</t>
+          <t>مزرعة بيت مطر</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
@@ -97007,7 +97017,7 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>مزرعة بيت الطشم</t>
+          <t>مزرعة سجد</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
@@ -97029,7 +97039,7 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>مزرعة بيت مطر</t>
+          <t>مصنع الزهرة</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
@@ -97051,7 +97061,7 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>مزرعة سجد</t>
+          <t>وادي التركمان</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
@@ -97073,7 +97083,7 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>مصنع الزهرة</t>
+          <t>وادي الرطل</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
@@ -97095,7 +97105,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>وادي التركمان</t>
+          <t>وادي الزين</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
@@ -97117,7 +97127,7 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>وادي الرطل</t>
+          <t>وادي الصفا الشرقي</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
@@ -97139,7 +97149,7 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>وادي الزين</t>
+          <t>وادي المشمشه</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
@@ -97161,7 +97171,7 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>وادي الصفا الشرقي</t>
+          <t>وادي النيرة</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
@@ -97183,7 +97193,7 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>وادي المشمشه</t>
+          <t>وادي بنيت</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
@@ -97205,17 +97215,17 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>وادي النيرة</t>
+          <t>الجديدة حي السراي</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>قضاءي بعلبك والهرمل</t>
+          <t>قضاءي مرجعيون وحاصبيا</t>
         </is>
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>بعلبك والهرمل</t>
+          <t>النبطية</t>
         </is>
       </c>
     </row>
@@ -97227,17 +97237,17 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>وادي بنيت</t>
+          <t>الجديدة حي العيون</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>قضاءي بعلبك والهرمل</t>
+          <t>قضاءي مرجعيون وحاصبيا</t>
         </is>
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>بعلبك والهرمل</t>
+          <t>النبطية</t>
         </is>
       </c>
     </row>
@@ -97249,7 +97259,7 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>الجديدة حي السراي</t>
+          <t>الجديدة حي القلعة</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
@@ -97271,7 +97281,7 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>الجديدة حي العيون</t>
+          <t>الجديدة حي المدارس</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
@@ -97293,7 +97303,7 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>الجديدة حي القلعة</t>
+          <t>الفرديس</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
@@ -97315,7 +97325,7 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>الجديدة حي المدارس</t>
+          <t>الوزاني</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
@@ -97337,7 +97347,7 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>الفرديس</t>
+          <t>برج الملوك</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
@@ -97359,7 +97369,7 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>الوزاني</t>
+          <t>بويضة</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
@@ -97381,7 +97391,7 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>برج الملوك</t>
+          <t>رب ثلاثين</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
@@ -97403,7 +97413,7 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>بويضة</t>
+          <t>سرده والعمره</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
@@ -97425,7 +97435,7 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>رب ثلاثين</t>
+          <t>عديسه</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
@@ -97447,7 +97457,7 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>سرده والعمره</t>
+          <t>كفرشوبا</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
@@ -97469,17 +97479,17 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>عديسه</t>
+          <t>السهيله</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>قضاءي مرجعيون وحاصبيا</t>
+          <t>كسروان</t>
         </is>
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>النبطية</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -97491,17 +97501,17 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>كفرشوبا</t>
+          <t>النموره وكفر جريف</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>قضاءي مرجعيون وحاصبيا</t>
+          <t>كسروان</t>
         </is>
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>النبطية</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -97513,7 +97523,7 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>السهيله</t>
+          <t>ساحل علما</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
@@ -97535,7 +97545,7 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>النموره وكفر جريف</t>
+          <t>شوان والعبره</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
@@ -97557,7 +97567,7 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>ساحل علما</t>
+          <t>غزير القناة</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
@@ -97579,7 +97589,7 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>شوان والعبره</t>
+          <t>غزير المعاملتين</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
@@ -97601,17 +97611,17 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>غزير القناة</t>
+          <t>التبانة</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>كسروان</t>
+          <t>مدينة طرابلس</t>
         </is>
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>الشمال</t>
         </is>
       </c>
     </row>
@@ -97623,17 +97633,17 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>غزير المعاملتين</t>
+          <t>الرمانة</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>كسروان</t>
+          <t>مدينة طرابلس</t>
         </is>
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>الشمال</t>
         </is>
       </c>
     </row>
@@ -97645,7 +97655,7 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>التبانة</t>
+          <t>الزاهرية</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
@@ -97667,7 +97677,7 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>الرمانة</t>
+          <t>السويقه</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
@@ -97689,7 +97699,7 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>الزاهرية</t>
+          <t>القبة</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
@@ -97711,7 +97721,7 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>السويقه</t>
+          <t>المهاترة</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
@@ -97733,7 +97743,7 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>القبة</t>
+          <t>وادي النحلة</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
@@ -97742,50 +97752,6 @@
         </is>
       </c>
       <c r="D663" t="inlineStr">
-        <is>
-          <t>الشمال</t>
-        </is>
-      </c>
-    </row>
-    <row r="664">
-      <c r="A664" t="inlineStr">
-        <is>
-          <t>Arabic</t>
-        </is>
-      </c>
-      <c r="B664" t="inlineStr">
-        <is>
-          <t>المهاترة</t>
-        </is>
-      </c>
-      <c r="C664" t="inlineStr">
-        <is>
-          <t>مدينة طرابلس</t>
-        </is>
-      </c>
-      <c r="D664" t="inlineStr">
-        <is>
-          <t>الشمال</t>
-        </is>
-      </c>
-    </row>
-    <row r="665">
-      <c r="A665" t="inlineStr">
-        <is>
-          <t>Arabic</t>
-        </is>
-      </c>
-      <c r="B665" t="inlineStr">
-        <is>
-          <t>وادي النحلة</t>
-        </is>
-      </c>
-      <c r="C665" t="inlineStr">
-        <is>
-          <t>مدينة طرابلس</t>
-        </is>
-      </c>
-      <c r="D665" t="inlineStr">
         <is>
           <t>الشمال</t>
         </is>
@@ -98092,7 +98058,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Mount Lebanon</t>
+          <t>South</t>
         </is>
       </c>
     </row>

--- a/FuzzyMatch/Lebanese_Villages_Matched_v6.xlsx
+++ b/FuzzyMatch/Lebanese_Villages_Matched_v6.xlsx
@@ -438,7 +438,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -450,7 +450,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>v5fix.xlsx</t>
+          <t>/home/hatch/workspace/Lebanese-Villages-List/FuzzyMatch/Grok 4.6/Lebanese_Villages_Improved_Matching_v5.xlsx</t>
         </is>
       </c>
     </row>
@@ -462,7 +462,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Offline Arabic-&gt;Latin transliteration (ya y/i, ta t/a variants) + French-dialect EN normalization; rapidfuzz WRatio; Hungarian one-to-one per (district, mohafaza) group; subdivision pass attaches qualifier-sharing arabic rows (جنوبي/شمالي/شرقي/غربي/فوقا/تحتا/حي …) to a definite match</t>
+          <t>Offline Arabic-&gt;Latin transliteration (ya y/i, ta t/a/e variants) + French-dialect EN normalization; english names also tried with a leading district-name token stripped ('Tripoli Al-Tabbaneh' -&gt; 'Al-Tabbaneh'); rapidfuzz WRatio; Hungarian one-to-one per (district, mohafaza) group; subdivision pass attaches qualifier-sharing arabic rows (جنوبي/شمالي/شرقي/غربي/فوقا/تحتا/حي …) to a definite match</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15">
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>390</v>
+        <v>385</v>
       </c>
     </row>
     <row r="18">
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>272</v>
+        <v>267</v>
       </c>
     </row>
     <row r="19">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Fuzzy-auto subdivision (81.0) [seeded]</t>
+          <t>Fuzzy-auto subdivision (81.4) [seeded]</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Fuzzy-auto subdivision (72.0) [seeded]</t>
+          <t>Fuzzy-auto subdivision (73.6) [seeded]</t>
         </is>
       </c>
     </row>
@@ -36701,7 +36701,7 @@
       </c>
       <c r="E1219" t="inlineStr">
         <is>
-          <t>Fuzzy-auto subdivision (81.0)</t>
+          <t>Fuzzy-auto subdivision (81.4)</t>
         </is>
       </c>
     </row>
@@ -39563,6 +39563,11 @@
           <t>El-Jdeidé</t>
         </is>
       </c>
+      <c r="B1346" t="inlineStr">
+        <is>
+          <t>جديدة الشوف</t>
+        </is>
+      </c>
       <c r="C1346" t="inlineStr">
         <is>
           <t>Chouf</t>
@@ -39575,7 +39580,7 @@
       </c>
       <c r="E1346" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Fuzzy-auto (100.0)</t>
         </is>
       </c>
     </row>
@@ -40172,7 +40177,7 @@
       </c>
       <c r="E1372" t="inlineStr">
         <is>
-          <t>Fuzzy-auto (88.9)</t>
+          <t>Fuzzy-auto (90.9)</t>
         </is>
       </c>
     </row>
@@ -42637,6 +42642,11 @@
           <t>Al-Minieh</t>
         </is>
       </c>
+      <c r="B1483" t="inlineStr">
+        <is>
+          <t>المنية</t>
+        </is>
+      </c>
       <c r="C1483" t="inlineStr">
         <is>
           <t>Minieh-Danieh</t>
@@ -42649,7 +42659,7 @@
       </c>
       <c r="E1483" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Fuzzy-auto (88.9)</t>
         </is>
       </c>
     </row>
@@ -42938,7 +42948,7 @@
       </c>
       <c r="E1495" t="inlineStr">
         <is>
-          <t>Fuzzy-auto (90.9)</t>
+          <t>Fuzzy-auto (100.0)</t>
         </is>
       </c>
     </row>
@@ -45512,6 +45522,11 @@
           <t>Tripoli Al-Mouhaitra</t>
         </is>
       </c>
+      <c r="B1608" t="inlineStr">
+        <is>
+          <t>المهاترة</t>
+        </is>
+      </c>
       <c r="C1608" t="inlineStr">
         <is>
           <t>Tripoli</t>
@@ -45524,7 +45539,7 @@
       </c>
       <c r="E1608" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Fuzzy-auto (100.0)</t>
         </is>
       </c>
     </row>
@@ -45534,6 +45549,11 @@
           <t>Tripoli Al-Rmmanieh</t>
         </is>
       </c>
+      <c r="B1609" t="inlineStr">
+        <is>
+          <t>الرمانة</t>
+        </is>
+      </c>
       <c r="C1609" t="inlineStr">
         <is>
           <t>Tripoli</t>
@@ -45546,7 +45566,7 @@
       </c>
       <c r="E1609" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Fuzzy-auto (90.9)</t>
         </is>
       </c>
     </row>
@@ -45578,6 +45598,11 @@
           <t>Tripoli Al-Tabbaneh</t>
         </is>
       </c>
+      <c r="B1611" t="inlineStr">
+        <is>
+          <t>التبانة</t>
+        </is>
+      </c>
       <c r="C1611" t="inlineStr">
         <is>
           <t>Tripoli</t>
@@ -45590,7 +45615,7 @@
       </c>
       <c r="E1611" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Fuzzy-auto (90.9)</t>
         </is>
       </c>
     </row>
@@ -46483,7 +46508,7 @@
       </c>
       <c r="E1650" t="inlineStr">
         <is>
-          <t>Fuzzy-auto subdivision (72.0)</t>
+          <t>Fuzzy-auto subdivision (73.6)</t>
         </is>
       </c>
     </row>
@@ -49437,6 +49462,11 @@
           <t>جديدة الشوف</t>
         </is>
       </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>El-Jdeidé</t>
+        </is>
+      </c>
       <c r="C115" t="inlineStr">
         <is>
           <t>الشوف</t>
@@ -54736,6 +54766,11 @@
           <t>المنية</t>
         </is>
       </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Al-Minieh</t>
+        </is>
+      </c>
       <c r="C362" t="inlineStr">
         <is>
           <t>المنية</t>
@@ -80986,6 +81021,11 @@
           <t>التبانة</t>
         </is>
       </c>
+      <c r="B1617" t="inlineStr">
+        <is>
+          <t>Tripoli Al-Tabbaneh</t>
+        </is>
+      </c>
       <c r="C1617" t="inlineStr">
         <is>
           <t>مدينة طرابلس</t>
@@ -81069,6 +81109,11 @@
           <t>الرمانة</t>
         </is>
       </c>
+      <c r="B1621" t="inlineStr">
+        <is>
+          <t>Tripoli Al-Rmmanieh</t>
+        </is>
+      </c>
       <c r="C1621" t="inlineStr">
         <is>
           <t>مدينة طرابلس</t>
@@ -81157,6 +81202,11 @@
       <c r="A1626" t="inlineStr">
         <is>
           <t>المهاترة</t>
+        </is>
+      </c>
+      <c r="B1626" t="inlineStr">
+        <is>
+          <t>Tripoli Al-Mouhaitra</t>
         </is>
       </c>
       <c r="C1626" t="inlineStr">
@@ -81242,7 +81292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81280,78 +81330,73 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Al Kattara</t>
+          <t>Aaiyé</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Jubail</t>
+          <t>Sour</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Mount Lebanon</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>دير القطاره (جبيل) [72.7]</t>
+          <t>السماعية (صور) [72.7]</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Al-Khaldyé</t>
+          <t>Al Kattara</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Zgharta</t>
+          <t>Jubail</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Mount Lebanon</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>القادريه (زغرتا) [72.7]</t>
+          <t>دير القطاره (جبيل) [72.7]</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Al-Kharnoubé</t>
+          <t>Al-Khaldyé</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Akkar</t>
+          <t>Zgharta</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Akkar</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>خربة الجرد (عكار) [80.0]</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>خريبة الجندي (عكار) [80.0]</t>
+          <t>القادريه (زغرتا) [72.7]</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Al-Khraibé</t>
+          <t>Al-Kharnoubé</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -81366,24 +81411,19 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>خريبة الجندي (عكار) [81.8]</t>
+          <t>خربة الجرد (عكار) [80.0]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>بني صخر (عكار) [77.1]</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>خربة الجرد (عكار) [72.0]</t>
+          <t>خريبة الجندي (عكار) [80.0]</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Al-Kneissé</t>
+          <t>Al-Khraibé</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -81398,36 +81438,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>قنية (عكار) [75.0]</t>
+          <t>خريبة الجندي (عكار) [83.1]</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>بني صخر (عكار) [77.1]</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>خربة الجرد (عكار) [75.0]</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Al-Minieh</t>
+          <t>Al-Kneissé</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Minieh-Danieh</t>
+          <t>Akkar</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Akkar</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>المنية (المنية) [75.0]</t>
+          <t>قنية (عكار) [80.0]</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Al-Qa Wadi El-Khanzir</t>
+          <t>Al-Qa El-Benjakie</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -81442,19 +81492,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>وادي النيرة (قضاءي بعلبك والهرمل) [85.5]</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>وادي الزين (قضاءي بعلبك والهرمل) [85.5]</t>
+          <t>العقيدية (قضاءي بعلبك والهرمل) [72.0]</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Al-Saïdat</t>
+          <t>Al-Qa Wadi El-Khanzir</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -81469,73 +81514,78 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>السعيده (قضاءي بعلبك والهرمل) [80.0]</t>
+          <t>وادي النيرة (قضاءي بعلبك والهرمل) [85.5]</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>وادي الزين (قضاءي بعلبك والهرمل) [85.5]</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alita</t>
+          <t>Al-Saïdat</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jubail</t>
+          <t>Baalbeck</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mount Lebanon</t>
+          <t>Baalbak - Hermel</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>سرعيتا (جبيل) [72.7]</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>دير القطاره (جبيل) [72.7]</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>مزرعة السياد (جبيل) [72.7]</t>
+          <t>السعيده (قضاءي بعلبك والهرمل) [80.0]</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Arbet Koshaya</t>
+          <t>Alita</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Zgharta</t>
+          <t>Jubail</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Mount Lebanon</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>عربة قزحيا (زغرتا) [85.7]</t>
+          <t>سرعيتا (جبيل) [72.7]</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>دير القطاره (جبيل) [72.7]</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>مزرعة السياد (جبيل) [72.7]</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Azka</t>
+          <t>Arbet Koshaya</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Minieh-Danieh</t>
+          <t>Zgharta</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -81545,63 +81595,63 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>عزقي (الضنية) [85.7]</t>
+          <t>عربة قزحيا (زغرتا) [85.7]</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Aïn Séa et Chadourah</t>
+          <t>Azka</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Baalbeck</t>
+          <t>Minieh-Danieh</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Baalbak - Hermel</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>النبي رشاده (قضاءي بعلبك والهرمل) [80.0]</t>
+          <t>عزقي (الضنية) [85.7]</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Aïn-El-Ghouaibé</t>
+          <t>Aïn Séa et Chadourah</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Jubail</t>
+          <t>Baalbeck</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mount Lebanon</t>
+          <t>Baalbak - Hermel</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>عين الغويبة (جبيل) [80.0]</t>
+          <t>النبي رشاده (قضاءي بعلبك والهرمل) [80.0]</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Aïn-el-Assad et Chmeicé</t>
+          <t>Aïn-El-Ghouaibé</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Chouf</t>
+          <t>Jubail</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -81611,342 +81661,342 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>عين الاسد والشميس (الشوف) [75.0]</t>
+          <t>عين الغويبة (جبيل) [82.4]</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Aïn-el-Tiné</t>
+          <t>Aïn-el-Assad et Chmeicé</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>West Bekaa</t>
+          <t>Chouf</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bekaa</t>
+          <t>Mount Lebanon</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>عين التينه (قضاءي البقاع الغربي وراشيا) [75.0]</t>
+          <t>عين الاسد والشميس (الشوف) [75.0]</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Bazouriat</t>
+          <t>Aïn-el-Delbé</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sour</t>
+          <t>Jubail</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Mount Lebanon</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>البازوريه (صور) [87.5]</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>الظهيرة (صور) [75.0]</t>
+          <t>عين الدلبة (جبيل) [72.7]</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bestiace</t>
+          <t>Aïn-el-Tiné</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sour</t>
+          <t>West Bekaa</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Bekaa</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>البساتين (صور) [75.0]</t>
+          <t>عين التينه (قضاءي البقاع الغربي وراشيا) [75.0]</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bfarwé</t>
+          <t>Bazouriat</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nabatiyeh</t>
+          <t>Sour</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Nabatiyeh</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>كفروة (النبطية) [75.0]</t>
+          <t>البازوريه (صور) [87.5]</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>الظهيرة (صور) [75.0]</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Bhamdoun (Gare)</t>
+          <t>Bestiace</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Aley</t>
+          <t>Sour</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Mount Lebanon</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>محطة بحمدون (عاليه) [75.0]</t>
+          <t>البساتين (صور) [75.0]</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Bhanine</t>
+          <t>Bfarwé</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Jezzine</t>
+          <t>Nabatiyeh</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Nabatiyeh</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>بحنين - كفرتعلا (جزين) [81.8]</t>
+          <t>كفروة (النبطية) [75.0]</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Btaychiyé</t>
+          <t>Bhamdoun (Gare)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sour</t>
+          <t>Aley</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Mount Lebanon</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>الشهابية (صور) [77.1]</t>
+          <t>محطة بحمدون (عاليه) [75.0]</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Bteezanieh</t>
+          <t>Bhanine</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Aley</t>
+          <t>Jezzine</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Mount Lebanon</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>التعزانية (عاليه) [75.0]</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>البساتين (عاليه) [75.0]</t>
+          <t>بحنين - كفرتعلا (جزين) [81.8]</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Chouberkié "Ammik"</t>
+          <t>Btaychiyé</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>West Bekaa</t>
+          <t>Sour</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bekaa</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>الشبرقية (قضاءي البقاع الغربي وراشيا) [83.3]</t>
+          <t>الشهابية (صور) [77.1]</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Chouma</t>
+          <t>Bteezanieh</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Batroun</t>
+          <t>Aley</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Mount Lebanon</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>غوما (البترون) [83.3]</t>
+          <t>التعزانية (عاليه) [80.0]</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>البساتين (عاليه) [75.0]</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Dahr el-Kneissé</t>
+          <t>Chouberkié "Ammik"</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Akkar</t>
+          <t>West Bekaa</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Akkar</t>
+          <t>Bekaa</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>قنية (عكار) [75.0]</t>
+          <t>الشبرقية (قضاءي البقاع الغربي وراشيا) [83.3]</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Dar El-Ouassia</t>
+          <t>Chouma</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Baalbeck</t>
+          <t>Batroun</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Baalbak - Hermel</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>الصوانية (قضاءي بعلبك والهرمل) [76.9]</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>دار الواسعة (قضاءي بعلبك والهرمل) [76.9]</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>حي العباسية (قضاءي بعلبك والهرمل) [72.0]</t>
+          <t>غوما (البترون) [83.3]</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Debbiyeh</t>
+          <t>Dahr el-Kneissé</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Chouf</t>
+          <t>Akkar</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Mount Lebanon</t>
+          <t>Akkar</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>الدبية (الشوف) [75.0]</t>
+          <t>قنية (عكار) [80.0]</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Debbiyeh (Ain el Haour)</t>
+          <t>Dar El-Ouassia</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Chouf</t>
+          <t>Baalbeck</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Mount Lebanon</t>
+          <t>Baalbak - Hermel</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>عين الحور (الشوف) [72.0]</t>
+          <t>الصوانية (قضاءي بعلبك والهرمل) [76.9]</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>دار الواسعة (قضاءي بعلبك والهرمل) [76.9]</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>حي العباسية (قضاءي بعلبك والهرمل) [72.0]</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Deir  El-Moukhalles Ech-Chouf</t>
+          <t>Debbiyeh</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -81961,41 +82011,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>المحتقره دير المخلص (الشوف) [75.0]</t>
+          <t>الدبية (الشوف) [80.0]</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Deir Mar Youhanna Douma</t>
+          <t>Debbiyeh (Ain el Haour)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Batroun</t>
+          <t>Chouf</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Mount Lebanon</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>غوما (البترون) [72.0]</t>
+          <t>عين الحور (الشوف) [72.0]</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Djounié Salel Alma</t>
+          <t>Deir  El-Moukhalles Ech-Chouf</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kasrouane</t>
+          <t>Chouf</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -82005,161 +82055,161 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ساحل علما (كسروان) [85.5]</t>
+          <t>المحتقره دير المخلص (الشوف) [75.0]</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>El-Abri et Chouan</t>
+          <t>Deir Mar Youhanna Douma</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Kasrouane</t>
+          <t>Batroun</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Mount Lebanon</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>شوان والعبره (كسروان) [81.8]</t>
+          <t>غوما (البترون) [72.0]</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>El-Fraïdice</t>
+          <t>Djounié Salel Alma</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Hasbaya</t>
+          <t>Kasrouane</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Nabatiyeh</t>
+          <t>Mount Lebanon</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>الفرديس (قضاءي مرجعيون وحاصبيا) [75.0]</t>
+          <t>ساحل علما (كسروان) [85.5]</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>El-Hajjé</t>
+          <t>El-Abri et Chouan</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Saida</t>
+          <t>Kasrouane</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Mount Lebanon</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>الحجة (قرى صيدا) [80.0]</t>
+          <t>شوان والعبره (كسروان) [81.8]</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>El-Houaïche</t>
+          <t>El-Fraïdice</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Akkar</t>
+          <t>Hasbaya</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Akkar</t>
+          <t>Nabatiyeh</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>الحويش (عكار) [83.3]</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>القبيات غوايا (عكار) [75.0]</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>الهيشة (عكار) [72.7]</t>
+          <t>الفرديس (قضاءي مرجعيون وحاصبيا) [75.0]</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>El-Jdeidé</t>
+          <t>El-Hajjé</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Chouf</t>
+          <t>Saida</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Mount Lebanon</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>جديدة الشوف (الشوف) [72.0]</t>
+          <t>الحجة (قرى صيدا) [85.7]</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>El-Kalaa</t>
+          <t>El-Houaïche</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Baabda</t>
+          <t>Akkar</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Mount Lebanon</t>
+          <t>Akkar</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>القلعه (بعبدا) [85.7]</t>
+          <t>الحويش (عكار) [83.3]</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>الهيشة (عكار) [83.3]</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>القبيات غوايا (عكار) [75.0]</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>El-Khreibé</t>
+          <t>El-Kalaa</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Chouf</t>
+          <t>Baabda</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -82169,19 +82219,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>حارة بعاصير (الشوف) [77.1]</t>
+          <t>القلعه (بعبدا) [85.7]</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>El-Kneissé</t>
+          <t>El-Khreibé</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Baabda</t>
+          <t>Chouf</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -82191,156 +82241,156 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>الشياح حي الكنيسة (بعبدا) [72.0]</t>
+          <t>حارة بعاصير (الشوف) [77.1]</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>El-Mhammariyé</t>
+          <t>El-Kneissé</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Saida</t>
+          <t>Baabda</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Mount Lebanon</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>المعمرية (قرى صيدا) [76.9]</t>
+          <t>الشياح حي الكنيسة (بعبدا) [81.8]</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>El-Mouncef</t>
+          <t>El-Mhammariyé</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Jubail</t>
+          <t>Saida</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Mount Lebanon</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>المنصف (جبيل) [75.0]</t>
+          <t>المعمرية (قرى صيدا) [80.0]</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>El-Watié et Harf Siad</t>
+          <t>El-Mouncef</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Minieh-Danieh</t>
+          <t>Jubail</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Mount Lebanon</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>حرف السياد (الضنية) [76.9]</t>
+          <t>المنصف (جبيل) [75.0]</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Eskandaroun</t>
+          <t>El-Watié et Harf Siad</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Sour</t>
+          <t>Minieh-Danieh</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>محرونه (صور) [72.0]</t>
+          <t>حرف السياد (الضنية) [76.9]</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Ghbayreh</t>
+          <t>Eskandaroun</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Baabda</t>
+          <t>Sour</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Mount Lebanon</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>الغبيري حي الجامع (بعبدا) [80.0]</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>الغبيري بئر حسن (بعبدا) [75.0]</t>
+          <t>محرونه (صور) [72.0]</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Hmairé</t>
+          <t>Ghbayreh</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Sour</t>
+          <t>Baabda</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Mount Lebanon</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>الحميري (صور) [80.0]</t>
+          <t>الغبيري حي الجامع (بعبدا) [80.0]</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>الغبيري بئر حسن (بعبدا) [75.0]</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Kaoutarite El-Riz</t>
+          <t>Hmairé</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Saida</t>
+          <t>Sour</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -82350,14 +82400,24 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>القنيطرة (قرى صيدا) [77.1]</t>
+          <t>الحميري (صور) [80.0]</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>السماعية (صور) [72.7]</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>الظهيرة (صور) [72.7]</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Kaoutarite El-Siyad</t>
+          <t>Kaoutarite El-Riz</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -82372,178 +82432,178 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>كوثرية السياد (قرى صيدا) [82.4]</t>
+          <t>القنيطرة (قرى صيدا) [77.1]</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Katté</t>
+          <t>Kaoutarite El-Siyad</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Akkar</t>
+          <t>Saida</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Akkar</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>البقيعة (عكار) [75.0]</t>
+          <t>كوثرية السياد (قرى صيدا) [82.4]</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Kfar Dabache</t>
+          <t>Katté</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Baalbeck</t>
+          <t>Akkar</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Baalbak - Hermel</t>
+          <t>Akkar</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>كفردبش (قضاءي بعلبك والهرمل) [77.1]</t>
+          <t>البقيعة (عكار) [75.0]</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Kfar Kouk</t>
+          <t>Kfar Dabache</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Rachiaya</t>
+          <t>Baalbeck</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bekaa</t>
+          <t>Baalbak - Hermel</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>كفرقوق (قضاءي البقاع الغربي وراشيا) [72.7]</t>
+          <t>كفردبش (قضاءي بعلبك والهرمل) [77.1]</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Kfar-Mashoune et Dmalsa</t>
+          <t>Kfar Kouk</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Jubail</t>
+          <t>Rachiaya</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Mount Lebanon</t>
+          <t>Bekaa</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>كفر مسحون (جبيل) [80.0]</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>مزرعة السياد (جبيل) [72.0]</t>
+          <t>كفرقوق (قضاءي البقاع الغربي وراشيا) [72.7]</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Knaissat</t>
+          <t>Kfar-Mashoune et Dmalsa</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Baalbeck</t>
+          <t>Jubail</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Baalbak - Hermel</t>
+          <t>Mount Lebanon</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>القرينة (قضاءي بعلبك والهرمل) [75.0]</t>
+          <t>كفر مسحون (جبيل) [80.0]</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>مزرعة السياد (جبيل) [72.0]</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Kobbaï</t>
+          <t>Knaissat</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Baabda</t>
+          <t>Baalbeck</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Mount Lebanon</t>
+          <t>Baalbak - Hermel</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>قبيع (بعبدا) [75.0]</t>
+          <t>القرينة (قضاءي بعلبك والهرمل) [75.0]</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Lebaa</t>
+          <t>Kobbaï</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Jezzine</t>
+          <t>Baabda</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Mount Lebanon</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>لبعه (جزين) [85.7]</t>
+          <t>قبيع (بعبدا) [75.0]</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Mazraat Dhaira</t>
+          <t>Lebaa</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Sour</t>
+          <t>Jezzine</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -82553,19 +82613,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>الظهيرة (صور) [72.7]</t>
+          <t>لبعه (جزين) [85.7]</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Mazraat Ez-Zalloutieh</t>
+          <t>Matriet El-Choumar</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Sour</t>
+          <t>Saida</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -82575,58 +82635,58 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>الزلوطية (صور) [77.1]</t>
+          <t>المعمرية (قرى صيدا) [75.0]</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Mazraet-el-Siyad</t>
+          <t>Mazraat Dhaira</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Jubail</t>
+          <t>Sour</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Mount Lebanon</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>مزرعة السياد (جبيل) [72.7]</t>
+          <t>الظهيرة (صور) [72.7]</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Mechmech</t>
+          <t>Mazraat Ez-Zalloutieh</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Jubail</t>
+          <t>Sour</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Mount Lebanon</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>كفر مسحون (جبيل) [77.1]</t>
+          <t>الزلوطية (صور) [83.1]</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Mehrine</t>
+          <t>Mazraet-el-Siyad</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -82641,249 +82701,239 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>كفر مسحون (جبيل) [75.0]</t>
+          <t>مزرعة السياد (جبيل) [72.7]</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Merh Kfarsghabe</t>
+          <t>Mechmech</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Zgharta</t>
+          <t>Jubail</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Mount Lebanon</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>مزرعة حوقا (زغرتا) [72.0]</t>
+          <t>كفر مسحون (جبيل) [77.1]</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Michaa Mrajhiné</t>
+          <t>Mehrine</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Hermel</t>
+          <t>Jubail</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Baalbak - Hermel</t>
+          <t>Mount Lebanon</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>مراح العين (قضاءي بعلبك والهرمل) [72.0]</t>
+          <t>كفر مسحون (جبيل) [75.0]</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Miemié</t>
+          <t>Merh Kfarsghabe</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Saida</t>
+          <t>Zgharta</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>المية ومية (قرى صيدا) [72.7]</t>
+          <t>مزرعة حوقا (زغرتا) [72.0]</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Mohaïdcé</t>
+          <t>Michaa Mrajhiné</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Rachiaya</t>
+          <t>Hermel</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bekaa</t>
+          <t>Baalbak - Hermel</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>محيدثه (قضاءي البقاع الغربي وراشيا) [75.0]</t>
+          <t>مراح العين (قضاءي بعلبك والهرمل) [72.0]</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Mrabine</t>
+          <t>Miemié</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Minieh-Danieh</t>
+          <t>Saida</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>نمرين (الضنية) [75.0]</t>
+          <t>المية ومية (قرى صيدا) [85.7]</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Mugher-el-Ahwel</t>
+          <t>Mohaïdcé</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Bcharre</t>
+          <t>Rachiaya</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Bekaa</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>المغر وبلا (بشري) [85.7]</t>
+          <t>محيدثه (قضاءي البقاع الغربي وراشيا) [75.0]</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Naamat</t>
+          <t>Mrabine</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Chouf</t>
+          <t>Minieh-Danieh</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Mount Lebanon</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>الناعمه (الشوف) [80.0]</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>حارة الناعمه (الشوف) [72.0]</t>
+          <t>نمرين (الضنية) [75.0]</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Nammoura et Kfar Jerif</t>
+          <t>Mugher-el-Ahwel</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Kasrouane</t>
+          <t>Bcharre</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Mount Lebanon</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>النموره وكفر جريف (كسروان) [80.0]</t>
+          <t>المغر وبلا (بشري) [85.7]</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Ouadi El-Osse</t>
+          <t>Naamat</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Hermel</t>
+          <t>Chouf</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Baalbak - Hermel</t>
+          <t>Mount Lebanon</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>وادي الصفا الشرقي (قضاءي بعلبك والهرمل) [85.5]</t>
+          <t>الناعمه (الشوف) [80.0]</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>وادي المشمشه (قضاءي بعلبك والهرمل) [85.5]</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>وادي النيرة (قضاءي بعلبك والهرمل) [85.5]</t>
+          <t>حارة الناعمه (الشوف) [72.0]</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Ras Baalbek El-Charki</t>
+          <t>Nammoura et Kfar Jerif</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Baalbeck</t>
+          <t>Kasrouane</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Baalbak - Hermel</t>
+          <t>Mount Lebanon</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>الريش حي الشرقي (قضاءي بعلبك والهرمل) [77.8]</t>
+          <t>النموره وكفر جريف (كسروان) [80.0]</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Ras Baalbek El-Gharbi</t>
+          <t>Ouadi El-Osse</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -82898,24 +82948,29 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>قلعة غربي (قضاءي بعلبك والهرمل) [81.8]</t>
+          <t>وادي المشمشه (قضاءي بعلبك والهرمل) [85.5]</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>الريش حي الغربي (قضاءي بعلبك والهرمل) [77.8]</t>
+          <t>وادي الصفا الشرقي (قضاءي بعلبك والهرمل) [85.5]</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>وادي النيرة (قضاءي بعلبك والهرمل) [85.5]</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Ras-Baalbek - Wadi Faara</t>
+          <t>Ras Baalbek El-Charki</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Hermel</t>
+          <t>Baalbeck</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -82925,51 +82980,46 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>وادي التركمان (قضاءي بعلبك والهرمل) [85.5]</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>وادي الرطل (قضاءي بعلبك والهرمل) [85.5]</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>وادي المشمشه (قضاءي بعلبك والهرمل) [85.5]</t>
+          <t>الريش حي الشرقي (قضاءي بعلبك والهرمل) [77.8]</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sarhita</t>
+          <t>Ras Baalbek El-Gharbi</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Jubail</t>
+          <t>Hermel</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Mount Lebanon</t>
+          <t>Baalbak - Hermel</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>سرعيتا (جبيل) [76.9]</t>
+          <t>قلعة غربي (قضاءي بعلبك والهرمل) [81.8]</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>الريش حي الغربي (قضاءي بعلبك والهرمل) [77.8]</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Slouky</t>
+          <t>Ras-Baalbek - Wadi Faara</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Baalbeck</t>
+          <t>Hermel</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -82979,24 +83029,29 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>مزرعة الفقيه (قضاءي بعلبك والهرمل) [75.0]</t>
+          <t>وادي التركمان (قضاءي بعلبك والهرمل) [85.5]</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>السويسة (قضاءي بعلبك والهرمل) [72.7]</t>
+          <t>وادي الرطل (قضاءي بعلبك والهرمل) [85.5]</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>وادي المشمشه (قضاءي بعلبك والهرمل) [85.5]</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Souhailet El-Faouka</t>
+          <t>Sarhita</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Kasrouane</t>
+          <t>Jubail</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -83006,152 +83061,245 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>السهيله (كسروان) [77.1]</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>ساحل علما (كسروان) [77.1]</t>
+          <t>سرعيتا (جبيل) [76.9]</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Tal Sibhel</t>
+          <t>Slouky</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Akkar</t>
+          <t>Baalbeck</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Akkar</t>
+          <t>Baalbak - Hermel</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>القبيات القطلبه (عكار) [72.0]</t>
+          <t>مزرعة الفقيه (قضاءي بعلبك والهرمل) [75.0]</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>السويسة (قضاءي بعلبك والهرمل) [72.7]</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Tripoli Al-Mouhaitra</t>
+          <t>Souhailet El-Faouka</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Tripoli</t>
+          <t>Kasrouane</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Mount Lebanon</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>المهاترة (مدينة طرابلس) [80.0]</t>
+          <t>السهيله (كسروان) [77.1]</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>ساحل علما (كسروان) [77.1]</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Wadi Abou Youssef</t>
+          <t>Tal Sibhel</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Chouf</t>
+          <t>Akkar</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Mount Lebanon</t>
+          <t>Akkar</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>وادي دير دوريت (الشوف) [85.5]</t>
+          <t>القبيات القطلبه (عكار) [72.0]</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Wadi-el-Arayeche</t>
+          <t>Tripoli Al-Kobbé</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Zahleh</t>
+          <t>Tripoli</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Bekaa</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>زحلة وادي العرايش (زحلة) [85.5]</t>
+          <t>القبة (مدينة طرابلس) [85.7]</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Zahlé (Terres)</t>
+          <t>Tripoli Al-Souéka</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Zahleh</t>
+          <t>Tripoli</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bekaa</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>زحلة وادي العرايش (زحلة) [85.7]</t>
+          <t>السويقه (مدينة طرابلس) [80.0]</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
+          <t>Tripoli Al-Zehrieh</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Tripoli</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>الزاهرية (مدينة طرابلس) [83.3]</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Wadi Abou Youssef</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Chouf</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Mount Lebanon</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>وادي دير دوريت (الشوف) [85.5]</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Wadi-el-Arayeche</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Zahleh</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Bekaa</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>زحلة وادي العرايش (زحلة) [85.5]</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Zahlé (Terres)</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Zahleh</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Bekaa</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>زحلة وادي العرايش (زحلة) [85.7]</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
           <t>Zahlé Maallaka Kerek</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>Zahleh</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>Bekaa</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>زحلة المعلقه (زحلة) [85.7]</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t>زحلة كرك نوح (زحلة) [80.0]</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>زحلة المعلقه الشمالي (زحلة) [77.1]</t>
         </is>
@@ -83168,7 +83316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D663"/>
+  <dimension ref="A1:D653"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85621,7 +85769,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>El-Jdeidé</t>
+          <t>El-Khreibé</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -85643,7 +85791,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>El-Khreibé</t>
+          <t>El-Moghaïriyeh</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -85665,7 +85813,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>El-Moghaïriyeh</t>
+          <t>Ghabet Jaafar</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -85687,7 +85835,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Ghabet Jaafar</t>
+          <t>Jdael et Kfarhi</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -85709,7 +85857,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Jdael et Kfarhi</t>
+          <t>Jebah</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -85731,7 +85879,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Jebah</t>
+          <t>Kfar Haml</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -85753,7 +85901,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Kfar Haml</t>
+          <t>Kfar Matta (Klaliyé)</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -85775,7 +85923,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Kfar Matta (Klaliyé)</t>
+          <t>Naamat</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -85797,7 +85945,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Naamat</t>
+          <t>Wadi Abou Youssef</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -85819,7 +85967,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Wadi Abou Youssef</t>
+          <t>litige</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -85841,12 +85989,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>litige</t>
+          <t>Aïn-El-Kach</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Chouf</t>
+          <t>El Metn</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -85863,7 +86011,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Aïn-El-Kach</t>
+          <t>Bsifrine et El-Zahriyé</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -85885,7 +86033,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Bsifrine et El-Zahriyé</t>
+          <t>Deir Tamiche</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -85907,7 +86055,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Deir Tamiche</t>
+          <t>El-Ouyoun</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -85929,7 +86077,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>El-Ouyoun</t>
+          <t>Haret El-Belleni</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -85951,7 +86099,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Haret El-Belleni</t>
+          <t>Hebouss</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -85973,7 +86121,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Hebouss</t>
+          <t>Majdoub</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -85995,7 +86143,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Majdoub</t>
+          <t>Mar Abda El-Mchammar</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -86017,7 +86165,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Mar Abda El-Mchammar</t>
+          <t>Mar Roukose et Dahr El-Hossain</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -86039,7 +86187,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Mar Roukose et Dahr El-Hossain</t>
+          <t>Mazraet El-Hadira</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -86061,7 +86209,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Mazraet El-Hadira</t>
+          <t>Zeghrine</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -86083,17 +86231,17 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Zeghrine</t>
+          <t>Chebaa Farms</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>El Metn</t>
+          <t>Hasbaya</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Mount Lebanon</t>
+          <t>Nabatiyeh</t>
         </is>
       </c>
     </row>
@@ -86105,7 +86253,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Chebaa Farms</t>
+          <t>El-Fraïdice</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -86127,7 +86275,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>El-Fraïdice</t>
+          <t>El-Kahlouat</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -86149,7 +86297,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>El-Kahlouat</t>
+          <t>El-Khreibé</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -86171,7 +86319,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>El-Khreibé</t>
+          <t>Mimas</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -86193,7 +86341,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Mimas</t>
+          <t>Nkhailé</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -86215,7 +86363,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Nkhailé</t>
+          <t>Slaïyeb</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -86237,17 +86385,17 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Slaïyeb</t>
+          <t>Conflict</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Hasbaya</t>
+          <t>Hermel</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Nabatiyeh</t>
+          <t>Baalbak - Hermel</t>
         </is>
       </c>
     </row>
@@ -86259,7 +86407,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Conflict</t>
+          <t>El-Méaisseri</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -86281,7 +86429,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>El-Méaisseri</t>
+          <t>Hermel Djebab</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -86303,7 +86451,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Hermel Djebab</t>
+          <t>Hermel Zighrine</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -86325,7 +86473,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Hermel Zighrine</t>
+          <t>Michaa Mrajhiné</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -86347,7 +86495,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Michaa Mrajhiné</t>
+          <t>Ouadi El-Osse</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -86369,7 +86517,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Ouadi El-Osse</t>
+          <t>Ras Baalbek El-Gharbi</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -86391,7 +86539,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Ras Baalbek El-Gharbi</t>
+          <t>Ras-Baalbek - Wadi Faara</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -86413,17 +86561,17 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Ras-Baalbek - Wadi Faara</t>
+          <t>Akmata</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Hermel</t>
+          <t>Jezzine</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Baalbak - Hermel</t>
+          <t>South</t>
         </is>
       </c>
     </row>
@@ -86435,7 +86583,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Akmata</t>
+          <t>Aramté</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -86457,7 +86605,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Aramté</t>
+          <t>Arkoub (Mazraat)</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -86479,7 +86627,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Arkoub (Mazraat)</t>
+          <t>Baba</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -86501,7 +86649,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Baba</t>
+          <t>Bhanine</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -86523,7 +86671,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Bhanine</t>
+          <t>Chabil</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -86545,7 +86693,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Chabil</t>
+          <t>El-Demachkiyeh</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -86567,7 +86715,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>El-Demachkiyeh</t>
+          <t>El-Kabeh</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -86589,7 +86737,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>El-Kabeh</t>
+          <t>El-Mahmoudiyeh</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -86611,7 +86759,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>El-Mahmoudiyeh</t>
+          <t>El-Rahbane</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -86633,7 +86781,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>El-Rahbane</t>
+          <t>El-Remmané</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -86655,7 +86803,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>El-Remmané</t>
+          <t>El-Rihane</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -86677,7 +86825,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>El-Rihane</t>
+          <t>El-Wadié</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -86699,7 +86847,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>El-Wadié</t>
+          <t>El-Zeghrine</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -86721,7 +86869,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>El-Zeghrine</t>
+          <t>Haïdab</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -86743,7 +86891,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Haïdab</t>
+          <t>Jabal Toura</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -86765,7 +86913,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Jabal Toura</t>
+          <t>Khellet Khazen</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -86787,7 +86935,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Khellet Khazen</t>
+          <t>Krouh</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -86809,7 +86957,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Krouh</t>
+          <t>Lebaa</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -86831,7 +86979,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Lebaa</t>
+          <t>Mazraat Dahr el-Deir</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -86853,7 +87001,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Mazraat Dahr el-Deir</t>
+          <t>Mazraat Daraya</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -86875,7 +87023,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Mazraat Daraya</t>
+          <t>Mazraat El Ouazaaiyé</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -86897,7 +87045,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Mazraat El Ouazaaiyé</t>
+          <t>Mazraat Louzid (Louayziyé)</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -86919,7 +87067,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Mazraat Louzid (Louayziyé)</t>
+          <t>Sfarai</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -86941,7 +87089,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Sfarai</t>
+          <t>Tamra</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -86963,7 +87111,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Tamra</t>
+          <t>Wadi Laimoune</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -86985,7 +87133,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Wadi Laimoune</t>
+          <t>litige</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -87007,17 +87155,17 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>litige</t>
+          <t>Al Kattara</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Jezzine</t>
+          <t>Jubail</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Mount Lebanon</t>
         </is>
       </c>
     </row>
@@ -87029,7 +87177,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Al Kattara</t>
+          <t>Alita</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -87051,7 +87199,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Alita</t>
+          <t>Arab El-Haibe</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -87073,7 +87221,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Arab El-Haibe</t>
+          <t>Aïn-El-Ghouaibé</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -87095,7 +87243,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Aïn-El-Ghouaibé</t>
+          <t>Aïn-el-Delbé</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -87117,7 +87265,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Aïn-el-Delbé</t>
+          <t>Belhos</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -87139,7 +87287,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Belhos</t>
+          <t>Berket Hejoula</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -87161,7 +87309,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Berket Hejoula</t>
+          <t>Bintaél (Fdar-El-Soufla)</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -87183,7 +87331,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Bintaél (Fdar-El-Soufla)</t>
+          <t>Breige</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -87205,7 +87353,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Breige</t>
+          <t>Deir Mar Sarkis</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -87227,7 +87375,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Deir Mar Sarkis</t>
+          <t>El-Jlaicé</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -87249,7 +87397,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>El-Jlaicé</t>
+          <t>El-Kfoune</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -87271,7 +87419,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>El-Kfoune</t>
+          <t>El-Mouncef</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -87293,7 +87441,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>El-Mouncef</t>
+          <t>Hboub</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -87315,7 +87463,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Hboub</t>
+          <t>Hedayné</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -87337,7 +87485,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Hedayné</t>
+          <t>Jouret-el-Kattine</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -87359,7 +87507,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Jouret-el-Kattine</t>
+          <t>Kartaboune</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -87381,7 +87529,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Kartaboune</t>
+          <t>Kfar Kaouass</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -87403,7 +87551,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Kfar Kaouass</t>
+          <t>Kfar-Mashoune et Dmalsa</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -87425,7 +87573,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Kfar-Mashoune et Dmalsa</t>
+          <t>Mastita</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -87447,7 +87595,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Mastita</t>
+          <t>Mazraet-el-Siyad</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -87469,7 +87617,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Mazraet-el-Siyad</t>
+          <t>Mechmech</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -87491,7 +87639,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Mechmech</t>
+          <t>Mehrine</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -87513,7 +87661,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Mehrine</t>
+          <t>Sarhita</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -87535,7 +87683,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Sarhita</t>
+          <t>Sirine</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -87557,7 +87705,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Sirine</t>
+          <t>Tedmor et Serghal</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -87579,7 +87727,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Tedmor et Serghal</t>
+          <t>litige</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -87601,12 +87749,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>litige</t>
+          <t>Aïn El-Delbé</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Jubail</t>
+          <t>Kasrouane</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -87623,7 +87771,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Aïn El-Delbé</t>
+          <t>Aïntoura</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -87645,7 +87793,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Aïntoura</t>
+          <t>Boukak El-Dine</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -87667,7 +87815,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Boukak El-Dine</t>
+          <t>Deir Baklouche</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -87689,7 +87837,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Deir Baklouche</t>
+          <t>Djounié Salel Alma</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -87711,7 +87859,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Djounié Salel Alma</t>
+          <t>Djounié Sarba</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -87733,7 +87881,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Djounié Sarba</t>
+          <t>El-Abri et Chouan</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -87755,7 +87903,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>El-Abri et Chouan</t>
+          <t>El-Mghaer</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -87777,7 +87925,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>El-Mghaer</t>
+          <t>Jouret Mhad</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -87799,7 +87947,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Jouret Mhad</t>
+          <t>Kharayeb Nahr Ibrahim</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -87821,7 +87969,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Kharayeb Nahr Ibrahim</t>
+          <t>Mazraet El-Ras</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -87843,7 +87991,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Mazraet El-Ras</t>
+          <t>Mazraet Mrah el-Mir</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -87865,7 +88013,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Mazraet Mrah el-Mir</t>
+          <t>Mouchaa Kesrouan (Faraya)</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -87887,7 +88035,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Mouchaa Kesrouan (Faraya)</t>
+          <t>Mouchaa Kesrouan (Kfardebian)</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -87909,7 +88057,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Mouchaa Kesrouan (Kfardebian)</t>
+          <t>Nammoura et Kfar Jerif</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -87931,7 +88079,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Nammoura et Kfar Jerif</t>
+          <t>Souhailet El-Faouka</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -87953,7 +88101,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Souhailet El-Faouka</t>
+          <t>Wata Salam</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -87975,7 +88123,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Wata Salam</t>
+          <t>litige</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -87997,17 +88145,17 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>litige</t>
+          <t>Al-Boukaia</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Kasrouane</t>
+          <t>Koura</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Mount Lebanon</t>
+          <t>North</t>
         </is>
       </c>
     </row>
@@ -88019,7 +88167,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Al-Boukaia</t>
+          <t>Al-Hraïché</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -88041,7 +88189,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Al-Hraïché</t>
+          <t>Belmand</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -88063,7 +88211,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Belmand</t>
+          <t>Kfar Hatta</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -88085,17 +88233,17 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Kfar Hatta</t>
+          <t>Adchite El-Koussair</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Koura</t>
+          <t>Marjaayoun</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Nabatiyeh</t>
         </is>
       </c>
     </row>
@@ -88107,7 +88255,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Adchite El-Koussair</t>
+          <t>Adeicé</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -88129,7 +88277,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Adeicé</t>
+          <t>Deir Mimas Doumiat</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -88151,7 +88299,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Deir Mimas Doumiat</t>
+          <t>El-Amra</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -88173,7 +88321,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>El-Amra</t>
+          <t>El-Kherbeh</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -88195,7 +88343,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>El-Kherbeh</t>
+          <t>Houra</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -88217,7 +88365,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Houra</t>
+          <t>Mazraet el-Sarada</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -88239,7 +88387,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Mazraet el-Sarada</t>
+          <t>Mazraet-El-Jrein</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -88261,7 +88409,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Mazraet-El-Jrein</t>
+          <t>Merjayoun</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -88283,7 +88431,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Merjayoun</t>
+          <t>Rabb Salacine</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -88305,17 +88453,17 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Rabb Salacine</t>
+          <t>Aassaymout</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Marjaayoun</t>
+          <t>Minieh-Danieh</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Nabatiyeh</t>
+          <t>North</t>
         </is>
       </c>
     </row>
@@ -88327,7 +88475,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Aassaymout</t>
+          <t>Al-Beddaoui</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -88349,7 +88497,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Al-Beddaoui</t>
+          <t>Al-Rihanié</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -88359,7 +88507,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Akkar</t>
         </is>
       </c>
     </row>
@@ -88371,7 +88519,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Al-Minieh</t>
+          <t>Azka</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -88393,7 +88541,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Al-Rihanié</t>
+          <t>Bchnnata</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -88403,7 +88551,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Akkar</t>
+          <t>North</t>
         </is>
       </c>
     </row>
@@ -88415,7 +88563,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Azka</t>
+          <t>Bechhara</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -88437,7 +88585,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Bchnnata</t>
+          <t>Beit Zaoud</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -88459,7 +88607,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Bechhara</t>
+          <t>Btehline</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -88481,7 +88629,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Beit Zaoud</t>
+          <t>Debaael</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -88503,7 +88651,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Btehline</t>
+          <t>El-Watié et Harf Siad</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -88525,7 +88673,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Debaael</t>
+          <t>Jarjoura</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -88547,7 +88695,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>El-Watié et Harf Siad</t>
+          <t>Jaroun</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -88569,7 +88717,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Jarjoura</t>
+          <t>Kfar Bibnine</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -88591,7 +88739,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Jaroun</t>
+          <t>Kharnoub</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -88613,7 +88761,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Kfar Bibnine</t>
+          <t>Mazraat Ketrane</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -88635,7 +88783,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Kharnoub</t>
+          <t>Mazraet El-Krême</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -88657,7 +88805,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Mazraat Ketrane</t>
+          <t>Mrabine</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -88679,7 +88827,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Mazraet El-Krême</t>
+          <t>Nemrine et Bakoura</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -88701,7 +88849,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Mrabine</t>
+          <t>Qraine</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -88723,7 +88871,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Nemrine et Bakoura</t>
+          <t>Tourbol</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -88745,7 +88893,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Qraine</t>
+          <t>Zouk Bhanine</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -88767,7 +88915,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Tourbol</t>
+          <t>litige</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -88789,17 +88937,17 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Zouk Bhanine</t>
+          <t>Abba</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Minieh-Danieh</t>
+          <t>Nabatiyeh</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Nabatiyeh</t>
         </is>
       </c>
     </row>
@@ -88811,17 +88959,17 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>litige</t>
+          <t>Ali El-Taher</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Minieh-Danieh</t>
+          <t>Nabatiyeh</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Nabatiyeh</t>
         </is>
       </c>
     </row>
@@ -88833,7 +88981,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Abba</t>
+          <t>Bfarwé</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -88855,7 +89003,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Ali El-Taher</t>
+          <t>El-Hamra</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -88877,7 +89025,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Bfarwé</t>
+          <t>Hmaïla</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -88899,7 +89047,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>El-Hamra</t>
+          <t>Izzé</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -88921,7 +89069,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Hmaïla</t>
+          <t>Jernaya</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -88931,7 +89079,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Nabatiyeh</t>
+          <t>South</t>
         </is>
       </c>
     </row>
@@ -88943,7 +89091,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Izzé</t>
+          <t>Kafr Dajjal</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -88965,7 +89113,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Jernaya</t>
+          <t>Kfar Remmane</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -88975,7 +89123,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Nabatiyeh</t>
         </is>
       </c>
     </row>
@@ -88987,7 +89135,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Kafr Dajjal</t>
+          <t>Ksaibé</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -89009,7 +89157,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Kfar Remmane</t>
+          <t>Mazraat-el-Khreibé</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -89031,7 +89179,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Ksaibé</t>
+          <t>Mazraet Bsaffour</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -89053,7 +89201,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Mazraat-el-Khreibé</t>
+          <t>Mazraet Chaal Baal</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -89075,7 +89223,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Mazraet Bsaffour</t>
+          <t>Mazraet Dmoul</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -89097,7 +89245,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Mazraet Chaal Baal</t>
+          <t>Mazraet El-Bayad</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -89119,7 +89267,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Mazraet Dmoul</t>
+          <t>Mazraet Kalaat Meiss</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -89141,7 +89289,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Mazraet El-Bayad</t>
+          <t>Mazraet Kfar Jaouz</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -89163,17 +89311,17 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Mazraet Kalaat Meiss</t>
+          <t>Aïn Horché</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Nabatiyeh</t>
+          <t>Rachiaya</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Nabatiyeh</t>
+          <t>Bekaa</t>
         </is>
       </c>
     </row>
@@ -89185,17 +89333,17 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Mazraet Kfar Jaouz</t>
+          <t>Conflict</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Nabatiyeh</t>
+          <t>Rachiaya</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Nabatiyeh</t>
+          <t>Bekaa</t>
         </is>
       </c>
     </row>
@@ -89207,7 +89355,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Aïn Horché</t>
+          <t>Haouche El-Kannabé</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -89229,7 +89377,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Conflict</t>
+          <t>Kfar Dinès</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -89251,7 +89399,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Haouche El-Kannabé</t>
+          <t>Kfar Kouk</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -89273,7 +89421,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Kfar Dinès</t>
+          <t>Mohaïdcé</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -89295,7 +89443,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Kfar Kouk</t>
+          <t>Nabi Safa</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -89317,7 +89465,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Mohaïdcé</t>
+          <t>litige</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -89339,17 +89487,17 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Nabi Safa</t>
+          <t>Arab Soukar</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Rachiaya</t>
+          <t>Saida</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Bekaa</t>
+          <t>South</t>
         </is>
       </c>
     </row>
@@ -89361,17 +89509,17 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>litige</t>
+          <t>Aïn-el-Dib</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Rachiaya</t>
+          <t>Saida</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Bekaa</t>
+          <t>South</t>
         </is>
       </c>
     </row>
@@ -89383,7 +89531,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Arab Soukar</t>
+          <t>Daoudiyé</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -89405,7 +89553,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Aïn-el-Dib</t>
+          <t>Deir Takla</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -89427,7 +89575,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Daoudiyé</t>
+          <t>El Hartiyé</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -89449,7 +89597,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Deir Takla</t>
+          <t>El-Hajjé</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -89471,7 +89619,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>El Hartiyé</t>
+          <t>El-Husseiniyé</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -89493,7 +89641,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>El-Hajjé</t>
+          <t>El-Mhammariyé</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -89515,7 +89663,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>El-Husseiniyé</t>
+          <t>Jaziré</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -89537,7 +89685,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>El-Mhammariyé</t>
+          <t>Kaoutarite El-Riz</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -89559,7 +89707,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Jaziré</t>
+          <t>Kaoutarite El-Siyad</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -89581,7 +89729,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Kaoutarite El-Riz</t>
+          <t>Kfar Badda</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -89603,7 +89751,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Kaoutarite El-Siyad</t>
+          <t>Kfar Hatta</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -89625,7 +89773,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Kfar Badda</t>
+          <t>Kherbet Bassal</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -89647,7 +89795,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Kfar Hatta</t>
+          <t>Kherbet El-Douair</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -89669,7 +89817,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Kherbet Bassal</t>
+          <t>Matriet El-Choumar</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -89691,7 +89839,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Kherbet El-Douair</t>
+          <t>Mazraat El-Wasta</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -89713,7 +89861,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Matriet El-Choumar</t>
+          <t>Mazraat Jimjim</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -89735,7 +89883,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Mazraat El-Wasta</t>
+          <t>Mazraet Matarite Jebah</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -89757,7 +89905,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Mazraat Jimjim</t>
+          <t>Miemié</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -89779,7 +89927,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Mazraet Matarite Jebah</t>
+          <t>Mohaidalé</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -89801,7 +89949,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Miemié</t>
+          <t>Msaileh</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -89823,7 +89971,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Mohaidalé</t>
+          <t>Samiate</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -89845,7 +89993,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Msaileh</t>
+          <t>Sari</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -89867,7 +90015,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Samiate</t>
+          <t>Saïda Ville</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -89889,7 +90037,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Sari</t>
+          <t>Sfenté</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -89911,7 +90059,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Saïda Ville</t>
+          <t>Snaiber</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -89933,7 +90081,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Sfenté</t>
+          <t>Tibna</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -89955,7 +90103,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Snaiber</t>
+          <t>Yahoudiat</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -89977,12 +90125,12 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Tibna</t>
+          <t>Aaiyé</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Saida</t>
+          <t>Sour</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -89999,12 +90147,12 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Yahoudiat</t>
+          <t>Abou Chech</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Saida</t>
+          <t>Sour</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -90021,7 +90169,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Aaiyé</t>
+          <t>Bazouriat</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -90043,7 +90191,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Abou Chech</t>
+          <t>Bestiace</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -90065,7 +90213,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Bazouriat</t>
+          <t>Btaychiyé</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -90087,7 +90235,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Bestiace</t>
+          <t>Chameh</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -90109,7 +90257,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Btaychiyé</t>
+          <t>Debhalé</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -90131,7 +90279,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Chameh</t>
+          <t>Eskandaroun</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -90153,7 +90301,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Debhalé</t>
+          <t>Hamoul</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -90175,7 +90323,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Eskandaroun</t>
+          <t>Hmairé</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -90197,7 +90345,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Hamoul</t>
+          <t>Izzié</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -90219,7 +90367,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Hmairé</t>
+          <t>Jejime</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -90241,7 +90389,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Izzié</t>
+          <t>Kneissé</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -90263,7 +90411,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Jejime</t>
+          <t>Mahaïlib</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -90285,7 +90433,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Kneissé</t>
+          <t>Mazraat Dhaira</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -90307,7 +90455,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Mahaïlib</t>
+          <t>Mazraat Ez-Zalloutieh</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -90329,7 +90477,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Mazraat Dhaira</t>
+          <t>Mazraat Torsemhat</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -90351,7 +90499,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Mazraat Ez-Zalloutieh</t>
+          <t>Niha</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -90373,7 +90521,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Mazraat Torsemhat</t>
+          <t>Rafid-el-Mernaba</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -90395,7 +90543,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Niha</t>
+          <t>Tairzibna</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -90417,7 +90565,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Rafid-el-Mernaba</t>
+          <t>Trafelsiyé</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -90439,17 +90587,17 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Tairzibna</t>
+          <t>Al-Mina No1</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Sour</t>
+          <t>Tripoli</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
     </row>
@@ -90461,17 +90609,17 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Trafelsiyé</t>
+          <t>Al-Mina No2</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Sour</t>
+          <t>Tripoli</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
     </row>
@@ -90483,7 +90631,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Al-Mina No1</t>
+          <t>Al-Mina No3</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -90505,7 +90653,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Al-Mina No2</t>
+          <t>Tripoli Al-Kobbé</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -90527,7 +90675,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Al-Mina No3</t>
+          <t>Tripoli Al-Souéka</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -90549,7 +90697,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Tripoli Al-Kobbé</t>
+          <t>Tripoli Al-Tal</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -90571,7 +90719,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Tripoli Al-Mouhaitra</t>
+          <t>Tripoli Al-Zehrieh</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -90593,7 +90741,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Tripoli Al-Rmmanieh</t>
+          <t>Tripoli Jardins</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -90615,7 +90763,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Tripoli Al-Souéka</t>
+          <t>Tripoli Zeitoun</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -90637,17 +90785,17 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Tripoli Al-Tabbaneh</t>
+          <t>Al-Djeziré</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Tripoli</t>
+          <t>West Bekaa</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Bekaa</t>
         </is>
       </c>
     </row>
@@ -90659,17 +90807,17 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Tripoli Al-Tal</t>
+          <t>Al-Istable</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Tripoli</t>
+          <t>West Bekaa</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Bekaa</t>
         </is>
       </c>
     </row>
@@ -90681,17 +90829,17 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Tripoli Al-Zehrieh</t>
+          <t>Al-Wakf</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Tripoli</t>
+          <t>West Bekaa</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Bekaa</t>
         </is>
       </c>
     </row>
@@ -90703,17 +90851,17 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Tripoli Jardins</t>
+          <t>Ammik et "Jouret Ammik"</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Tripoli</t>
+          <t>West Bekaa</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Bekaa</t>
         </is>
       </c>
     </row>
@@ -90725,17 +90873,17 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Tripoli Zeitoun</t>
+          <t>Aïn-el-Tiné</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Tripoli</t>
+          <t>West Bekaa</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Bekaa</t>
         </is>
       </c>
     </row>
@@ -90747,7 +90895,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Al-Djeziré</t>
+          <t>Chouberkié "Ammik"</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -90769,7 +90917,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Al-Istable</t>
+          <t>Dair Tahmiche</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -90791,7 +90939,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Al-Wakf</t>
+          <t>Deir-Aïn-el-Jaouzé</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -90813,7 +90961,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Ammik et "Jouret Ammik"</t>
+          <t>Harime-el-Soughra</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -90835,7 +90983,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Aïn-el-Tiné</t>
+          <t>Khiara-el-Atika</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -90857,12 +91005,12 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Chouberkié "Ammik"</t>
+          <t>Al-Mazraa</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>West Bekaa</t>
+          <t>Zahleh</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -90879,12 +91027,12 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Dair Tahmiche</t>
+          <t>Chouberkié  Tabet</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>West Bekaa</t>
+          <t>Zahleh</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -90901,12 +91049,12 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Deir-Aïn-el-Jaouzé</t>
+          <t>Conflict</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>West Bekaa</t>
+          <t>Zahleh</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -90923,12 +91071,12 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Harime-el-Soughra</t>
+          <t>Haouche Kaissar</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>West Bekaa</t>
+          <t>Zahleh</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -90945,12 +91093,12 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Khiara-el-Atika</t>
+          <t>Haouche Sayadi</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>West Bekaa</t>
+          <t>Zahleh</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -90967,7 +91115,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Al-Mazraa</t>
+          <t>Haouche-al-Omara (Terres)</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -90989,7 +91137,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Chouberkié  Tabet</t>
+          <t>Hochemoche</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -91011,7 +91159,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Conflict</t>
+          <t>Ksara</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -91033,7 +91181,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Haouche Kaissar</t>
+          <t>Maallaka (Terres)</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -91055,7 +91203,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Haouche Sayadi</t>
+          <t>Maazraat-el-Ramtanieh</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -91077,7 +91225,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Haouche-al-Omara (Terres)</t>
+          <t>Mandara</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -91099,7 +91247,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Hochemoche</t>
+          <t>Mejdel-Anjar</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -91121,7 +91269,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Ksara</t>
+          <t>Nasriyat Rizk</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -91143,7 +91291,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Maallaka (Terres)</t>
+          <t>Tal-al-Amara</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -91165,7 +91313,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Maazraat-el-Ramtanieh</t>
+          <t>Tchiflik Eddé</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -91187,7 +91335,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Mandara</t>
+          <t>Tchiflik Kikano</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -91209,7 +91357,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Mejdel-Anjar</t>
+          <t>Wadi-el-Arayeche</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -91231,7 +91379,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Nasriyat Rizk</t>
+          <t>Zahlé (Terres)</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -91253,7 +91401,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Tal-al-Amara</t>
+          <t>Zahlé Maallaka Kerek</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -91275,7 +91423,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Tchiflik Eddé</t>
+          <t>Zahlé Mar Gérios</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -91297,7 +91445,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Tchiflik Kikano</t>
+          <t>Zebdol</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -91319,17 +91467,17 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Wadi-el-Arayeche</t>
+          <t>Aadoua</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Zahleh</t>
+          <t>Zgharta</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>Bekaa</t>
+          <t>North</t>
         </is>
       </c>
     </row>
@@ -91341,17 +91489,17 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Zahlé (Terres)</t>
+          <t>Al-Harik</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Zahleh</t>
+          <t>Zgharta</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>Bekaa</t>
+          <t>North</t>
         </is>
       </c>
     </row>
@@ -91363,17 +91511,17 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Zahlé Maallaka Kerek</t>
+          <t>Al-Jdeidé</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Zahleh</t>
+          <t>Zgharta</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>Bekaa</t>
+          <t>North</t>
         </is>
       </c>
     </row>
@@ -91385,17 +91533,17 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Zahlé Mar Gérios</t>
+          <t>Al-Khaldyé</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Zahleh</t>
+          <t>Zgharta</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>Bekaa</t>
+          <t>North</t>
         </is>
       </c>
     </row>
@@ -91407,17 +91555,17 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Zebdol</t>
+          <t>Arbet Koshaya</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Zahleh</t>
+          <t>Zgharta</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>Bekaa</t>
+          <t>North</t>
         </is>
       </c>
     </row>
@@ -91429,7 +91577,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Aadoua</t>
+          <t>Ardate</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -91451,7 +91599,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Al-Harik</t>
+          <t>Bsebhil</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -91473,7 +91621,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Al-Jdeidé</t>
+          <t>Danhi</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -91495,7 +91643,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Al-Khaldyé</t>
+          <t>Ehden</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -91517,7 +91665,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Arbet Koshaya</t>
+          <t>Ejbeh</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -91539,7 +91687,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Ardate</t>
+          <t>El-Tellé</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -91561,7 +91709,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Bsebhil</t>
+          <t>Mazraat Ejbeh</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -91583,7 +91731,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Danhi</t>
+          <t>Mazraat Jneide</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -91605,7 +91753,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Ehden</t>
+          <t>Mejdlaya</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -91627,7 +91775,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Ejbeh</t>
+          <t>Merh Kfarsghabe</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -91649,7 +91797,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>El-Tellé</t>
+          <t>Sakhra</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -91666,110 +91814,110 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Mazraat Ejbeh</t>
+          <t>راشكده</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Zgharta</t>
+          <t>البترون</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>الشمال</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Mazraat Jneide</t>
+          <t>عورا</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Zgharta</t>
+          <t>البترون</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>الشمال</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Mejdlaya</t>
+          <t>غوما</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Zgharta</t>
+          <t>البترون</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>الشمال</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Merh Kfarsghabe</t>
+          <t>قندولا</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Zgharta</t>
+          <t>البترون</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>الشمال</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Sakhra</t>
+          <t>الدبية</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Zgharta</t>
+          <t>الشوف</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -91781,17 +91929,17 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>راشكده</t>
+          <t>المحتقره دير المخلص</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>البترون</t>
+          <t>الشوف</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>الشمال</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -91803,17 +91951,17 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>عورا</t>
+          <t>الناعمه</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>البترون</t>
+          <t>الشوف</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>الشمال</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -91825,17 +91973,17 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>غوما</t>
+          <t>بقعاتا</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>البترون</t>
+          <t>الشوف</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>الشمال</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -91847,17 +91995,17 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>قندولا</t>
+          <t>حارة الناعمه</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>البترون</t>
+          <t>الشوف</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>الشمال</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -91869,7 +92017,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>الدبية</t>
+          <t>حارة بعاصير</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -91891,7 +92039,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>المحتقره دير المخلص</t>
+          <t>عين الاسد والشميس</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -91913,7 +92061,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>الناعمه</t>
+          <t>عين الحور</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -91935,7 +92083,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>بقعاتا</t>
+          <t>كليليه</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -91957,7 +92105,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>جديدة الشوف</t>
+          <t>مرج برجا</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -91979,7 +92127,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>حارة الناعمه</t>
+          <t>وادي دير دوريت</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -92001,17 +92149,17 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>حارة بعاصير</t>
+          <t>الروضة</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>الشوف</t>
+          <t>الضنية</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>الشمال</t>
         </is>
       </c>
     </row>
@@ -92023,17 +92171,17 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>عين الاسد والشميس</t>
+          <t>المطل</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>الشوف</t>
+          <t>الضنية</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>الشمال</t>
         </is>
       </c>
     </row>
@@ -92045,17 +92193,17 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>عين الحور</t>
+          <t>حرف السياد</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>الشوف</t>
+          <t>الضنية</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>الشمال</t>
         </is>
       </c>
     </row>
@@ -92067,17 +92215,17 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>كليليه</t>
+          <t>عزقي</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>الشوف</t>
+          <t>الضنية</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>الشمال</t>
         </is>
       </c>
     </row>
@@ -92089,17 +92237,17 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>مرج برجا</t>
+          <t>قزحيا</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>الشوف</t>
+          <t>الضنية</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>الشمال</t>
         </is>
       </c>
     </row>
@@ -92111,17 +92259,17 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>وادي دير دوريت</t>
+          <t>كرم المهر</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>الشوف</t>
+          <t>الضنية</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>الشمال</t>
         </is>
       </c>
     </row>
@@ -92133,7 +92281,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>الروضة</t>
+          <t>كفربنين</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -92155,7 +92303,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>المطل</t>
+          <t>نمرين</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -92177,12 +92325,12 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>حرف السياد</t>
+          <t>البحصاص</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>الضنية</t>
+          <t>الكورة</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
@@ -92199,12 +92347,12 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>عزقي</t>
+          <t>حارة الخاصة</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>الضنية</t>
+          <t>الكورة</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
@@ -92221,12 +92369,12 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>قزحيا</t>
+          <t>ضهر العين</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>الضنية</t>
+          <t>الكورة</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
@@ -92243,12 +92391,12 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>كرم المهر</t>
+          <t>ضهور الهوا</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>الضنية</t>
+          <t>الكورة</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
@@ -92265,17 +92413,17 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>كفربنين</t>
+          <t>الرابية</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>الضنية</t>
+          <t>المتن</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>الشمال</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -92287,17 +92435,17 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>نمرين</t>
+          <t>سد البوشريه</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>الضنية</t>
+          <t>المتن</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>الشمال</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -92309,17 +92457,17 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>البحصاص</t>
+          <t>مزرعة بنابيل</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>الكورة</t>
+          <t>المتن</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>الشمال</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -92331,17 +92479,17 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>حارة الخاصة</t>
+          <t>كفروة</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>الكورة</t>
+          <t>النبطية</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>الشمال</t>
+          <t>النبطية</t>
         </is>
       </c>
     </row>
@@ -92353,12 +92501,12 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>ضهر العين</t>
+          <t>المغر وبلا</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>الكورة</t>
+          <t>بشري</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
@@ -92375,17 +92523,17 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>ضهور الهوا</t>
+          <t>الحدث شمالي</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>الكورة</t>
+          <t>بعبدا</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>الشمال</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -92397,12 +92545,12 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>الرابية</t>
+          <t>الحدث قبلي</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>المتن</t>
+          <t>بعبدا</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
@@ -92419,12 +92567,12 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>سد البوشريه</t>
+          <t>الشياح حي الكنيسة</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>المتن</t>
+          <t>بعبدا</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
@@ -92441,12 +92589,12 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>مزرعة بنابيل</t>
+          <t>الشياح حي كرم الزيتون</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>المتن</t>
+          <t>بعبدا</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
@@ -92463,17 +92611,17 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>المنية</t>
+          <t>الغبيري بئر حسن</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>المنية</t>
+          <t>بعبدا</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>الشمال</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -92485,17 +92633,17 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>كفروة</t>
+          <t>الغبيري حي الجامع</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>النبطية</t>
+          <t>بعبدا</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>النبطية</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -92507,17 +92655,17 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>المغر وبلا</t>
+          <t>الفياضية</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>بشري</t>
+          <t>بعبدا</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>الشمال</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -92529,7 +92677,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>الحدث شمالي</t>
+          <t>القلعه</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -92551,7 +92699,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>الحدث قبلي</t>
+          <t>المريجه</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -92573,7 +92721,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>الشياح حي الكنيسة</t>
+          <t>تحويطة النهر</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -92595,7 +92743,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>الشياح حي كرم الزيتون</t>
+          <t>حارة البطم</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -92617,7 +92765,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>الغبيري بئر حسن</t>
+          <t>حارة حريك قرانوح</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -92639,7 +92787,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>الغبيري حي الجامع</t>
+          <t>دير مار الياس الكحلونية</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -92661,7 +92809,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>الفياضية</t>
+          <t>سبنيه</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -92683,7 +92831,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>القلعه</t>
+          <t>قبيع</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -92705,17 +92853,17 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>المريجه</t>
+          <t>حداثا</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>بعبدا</t>
+          <t>بنت جبيل</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>النبطية</t>
         </is>
       </c>
     </row>
@@ -92727,17 +92875,17 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>تحويطة النهر</t>
+          <t>عيتا الجبل</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>بعبدا</t>
+          <t>بنت جبيل</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>النبطية</t>
         </is>
       </c>
     </row>
@@ -92749,12 +92897,12 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>حارة البطم</t>
+          <t>الجليسه</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>بعبدا</t>
+          <t>جبيل</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
@@ -92771,12 +92919,12 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>حارة حريك قرانوح</t>
+          <t>العاقورة - م</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>بعبدا</t>
+          <t>جبيل</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
@@ -92793,12 +92941,12 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>دير مار الياس الكحلونية</t>
+          <t>الفيدار</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>بعبدا</t>
+          <t>جبيل</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
@@ -92815,12 +92963,12 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>سبنيه</t>
+          <t>المزاريب</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>بعبدا</t>
+          <t>جبيل</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
@@ -92837,12 +92985,12 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>قبيع</t>
+          <t>المنصف</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>بعبدا</t>
+          <t>جبيل</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
@@ -92859,17 +93007,17 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>حداثا</t>
+          <t>بنتاعل</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>بنت جبيل</t>
+          <t>جبيل</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>النبطية</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -92881,17 +93029,17 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>عيتا الجبل</t>
+          <t>دملصا</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>بنت جبيل</t>
+          <t>جبيل</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>النبطية</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -92903,7 +93051,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>الجليسه</t>
+          <t>دير القطاره</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -92925,7 +93073,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>العاقورة - م</t>
+          <t>سرعيتا</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -92947,7 +93095,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>الفيدار</t>
+          <t>عين الدلبة</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -92969,7 +93117,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>المزاريب</t>
+          <t>عين الشلال</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -92991,7 +93139,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>المنصف</t>
+          <t>عين الغويبة</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -93013,7 +93161,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>بنتاعل</t>
+          <t>قرطبا الشمالية</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -93035,7 +93183,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>دملصا</t>
+          <t>كفر مسحون</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -93057,7 +93205,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>دير القطاره</t>
+          <t>مزرعة السياد</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -93079,17 +93227,17 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>سرعيتا</t>
+          <t>بحنين - كفرتعلا</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>جبيل</t>
+          <t>جزين</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>الجنوب</t>
         </is>
       </c>
     </row>
@@ -93101,17 +93249,17 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>عين الدلبة</t>
+          <t>عين مجدلين</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>جبيل</t>
+          <t>جزين</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>الجنوب</t>
         </is>
       </c>
     </row>
@@ -93123,17 +93271,17 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>عين الشلال</t>
+          <t>لبعه</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>جبيل</t>
+          <t>جزين</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>الجنوب</t>
         </is>
       </c>
     </row>
@@ -93145,17 +93293,17 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>عين الغويبة</t>
+          <t>الكرمة</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>جبيل</t>
+          <t>زحلة</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>البقاع</t>
         </is>
       </c>
     </row>
@@ -93167,17 +93315,17 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>قرطبا الشمالية</t>
+          <t>بتياس</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>جبيل</t>
+          <t>زحلة</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>البقاع</t>
         </is>
       </c>
     </row>
@@ -93189,17 +93337,17 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>كفر مسحون</t>
+          <t>جلالا</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>جبيل</t>
+          <t>زحلة</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>البقاع</t>
         </is>
       </c>
     </row>
@@ -93211,17 +93359,17 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>مزرعة السياد</t>
+          <t>حاجي حببلي</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>جبيل</t>
+          <t>زحلة</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>البقاع</t>
         </is>
       </c>
     </row>
@@ -93233,17 +93381,17 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>بحنين - كفرتعلا</t>
+          <t>حي السلم</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>جزين</t>
+          <t>زحلة</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>الجنوب</t>
+          <t>البقاع</t>
         </is>
       </c>
     </row>
@@ -93255,17 +93403,17 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>عين مجدلين</t>
+          <t>حي الفيكاني</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>جزين</t>
+          <t>زحلة</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>الجنوب</t>
+          <t>البقاع</t>
         </is>
       </c>
     </row>
@@ -93277,17 +93425,17 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>لبعه</t>
+          <t>خضر بك</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>جزين</t>
+          <t>زحلة</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>الجنوب</t>
+          <t>البقاع</t>
         </is>
       </c>
     </row>
@@ -93299,7 +93447,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>الكرمة</t>
+          <t>زحلة المعلقه</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -93321,7 +93469,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>بتياس</t>
+          <t>زحلة المعلقه الشمالي</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -93343,7 +93491,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>جلالا</t>
+          <t>زحلة حي السيدة</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -93365,7 +93513,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>حاجي حببلي</t>
+          <t>زحلة كرك نوح</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -93387,7 +93535,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>حي السلم</t>
+          <t>زحلة مار مخايل</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -93409,7 +93557,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>حي الفيكاني</t>
+          <t>زحلة وادي العرايش</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -93431,7 +93579,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>خضر بك</t>
+          <t>شهابية الفاعور</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -93453,7 +93601,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>زحلة المعلقه</t>
+          <t>كابوسية</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -93475,7 +93623,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>زحلة المعلقه الشمالي</t>
+          <t>يوغون اولوك</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -93497,17 +93645,17 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>زحلة حي السيدة</t>
+          <t>اجبع</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>زحلة</t>
+          <t>زغرتا</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>البقاع</t>
+          <t>الشمال</t>
         </is>
       </c>
     </row>
@@ -93519,17 +93667,17 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>زحلة كرك نوح</t>
+          <t>اسلوت</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>زحلة</t>
+          <t>زغرتا</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>البقاع</t>
+          <t>الشمال</t>
         </is>
       </c>
     </row>
@@ -93541,17 +93689,17 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>زحلة مار مخايل</t>
+          <t>القادريه</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>زحلة</t>
+          <t>زغرتا</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>البقاع</t>
+          <t>الشمال</t>
         </is>
       </c>
     </row>
@@ -93563,17 +93711,17 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>زحلة وادي العرايش</t>
+          <t>بيت عبيد</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>زحلة</t>
+          <t>زغرتا</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>البقاع</t>
+          <t>الشمال</t>
         </is>
       </c>
     </row>
@@ -93585,17 +93733,17 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>شهابية الفاعور</t>
+          <t>بيت عوكر</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>زحلة</t>
+          <t>زغرتا</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>البقاع</t>
+          <t>الشمال</t>
         </is>
       </c>
     </row>
@@ -93607,17 +93755,17 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>كابوسية</t>
+          <t>حارة الفوار</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>زحلة</t>
+          <t>زغرتا</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>البقاع</t>
+          <t>الشمال</t>
         </is>
       </c>
     </row>
@@ -93629,17 +93777,17 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>يوغون اولوك</t>
+          <t>حرف ارده</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>زحلة</t>
+          <t>زغرتا</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>البقاع</t>
+          <t>الشمال</t>
         </is>
       </c>
     </row>
@@ -93651,7 +93799,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>اجبع</t>
+          <t>حرف مزيارة</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -93673,7 +93821,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>اسلوت</t>
+          <t>عربة قزحيا</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -93695,7 +93843,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>القادريه</t>
+          <t>مزرعة الفريديس</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -93717,7 +93865,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>بيت عبيد</t>
+          <t>مزرعة حوقا</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -93739,17 +93887,17 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>بيت عوكر</t>
+          <t>البازوريه</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>زغرتا</t>
+          <t>صور</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>الشمال</t>
+          <t>الجنوب</t>
         </is>
       </c>
     </row>
@@ -93761,17 +93909,17 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>حارة الفوار</t>
+          <t>البرغليه</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>زغرتا</t>
+          <t>صور</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>الشمال</t>
+          <t>الجنوب</t>
         </is>
       </c>
     </row>
@@ -93783,17 +93931,17 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>حرف ارده</t>
+          <t>البساتين</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>زغرتا</t>
+          <t>صور</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>الشمال</t>
+          <t>الجنوب</t>
         </is>
       </c>
     </row>
@@ -93805,17 +93953,17 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>حرف مزيارة</t>
+          <t>البص  قسم 1</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>زغرتا</t>
+          <t>صور</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>الشمال</t>
+          <t>الجنوب</t>
         </is>
       </c>
     </row>
@@ -93827,17 +93975,17 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>عربة قزحيا</t>
+          <t>البص  قسم 3</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>زغرتا</t>
+          <t>صور</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>الشمال</t>
+          <t>الجنوب</t>
         </is>
       </c>
     </row>
@@ -93849,17 +93997,17 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>مزرعة الفريديس</t>
+          <t>البص قسم 5</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>زغرتا</t>
+          <t>صور</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>الشمال</t>
+          <t>الجنوب</t>
         </is>
       </c>
     </row>
@@ -93871,17 +94019,17 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>مزرعة حوقا</t>
+          <t>الحميري</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>زغرتا</t>
+          <t>صور</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>الشمال</t>
+          <t>الجنوب</t>
         </is>
       </c>
     </row>
@@ -93893,7 +94041,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>البازوريه</t>
+          <t>الرشيديه</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -93915,7 +94063,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>البرغليه</t>
+          <t>الزلوطية</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
@@ -93937,7 +94085,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>البساتين</t>
+          <t>السماعية</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -93959,7 +94107,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>البص  قسم 1</t>
+          <t>الشهابية</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -93981,7 +94129,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>البص  قسم 3</t>
+          <t>الظهيرة</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -94003,7 +94151,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>البص قسم 5</t>
+          <t>المالكية</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -94025,7 +94173,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>الحميري</t>
+          <t>بثتيات</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -94047,7 +94195,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>الرشيديه</t>
+          <t>شبريحا</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -94069,7 +94217,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>الزلوطية</t>
+          <t>شمع</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -94091,7 +94239,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>السماعية</t>
+          <t>صور حي الارثوذكس</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -94113,7 +94261,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>الشهابية</t>
+          <t>صور حي الجامع</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -94135,7 +94283,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>الظهيرة</t>
+          <t>صور حي الجورة</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -94157,7 +94305,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>المالكية</t>
+          <t>صور حي الحسينية</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -94179,7 +94327,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>بثتيات</t>
+          <t>صور حي الكاثوليك</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -94201,7 +94349,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>شبريحا</t>
+          <t>صور حي المصاروي</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -94223,7 +94371,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>شمع</t>
+          <t>صور حي المنارة</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -94245,7 +94393,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>صور حي الارثوذكس</t>
+          <t>صور حي الموارنة</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -94267,7 +94415,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>صور حي الجامع</t>
+          <t>عين الزرقا</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -94289,7 +94437,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>صور حي الجورة</t>
+          <t>محرونه</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -94311,17 +94459,17 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>صور حي الحسينية</t>
+          <t>البساتين</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>صور</t>
+          <t>عاليه</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>الجنوب</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -94333,17 +94481,17 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>صور حي الكاثوليك</t>
+          <t>التعزانية</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>صور</t>
+          <t>عاليه</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>الجنوب</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -94355,17 +94503,17 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>صور حي المصاروي</t>
+          <t>جسر القاضي</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>صور</t>
+          <t>عاليه</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>الجنوب</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -94377,17 +94525,17 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>صور حي المنارة</t>
+          <t>عاليه قبلي</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>صور</t>
+          <t>عاليه</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>الجنوب</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -94399,17 +94547,17 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>صور حي الموارنة</t>
+          <t>عاليه وسطاني</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>صور</t>
+          <t>عاليه</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>الجنوب</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -94421,17 +94569,17 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>عين الزرقا</t>
+          <t>عين الفريديس</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>صور</t>
+          <t>عاليه</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>الجنوب</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -94443,17 +94591,17 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>محرونه</t>
+          <t>محطة بحمدون</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>صور</t>
+          <t>عاليه</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>الجنوب</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -94470,12 +94618,12 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>عاليه</t>
+          <t>عكار</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>عكار</t>
         </is>
       </c>
     </row>
@@ -94487,17 +94635,17 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>التعزانية</t>
+          <t>البقيعة</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>عاليه</t>
+          <t>عكار</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>عكار</t>
         </is>
       </c>
     </row>
@@ -94509,17 +94657,17 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>جسر القاضي</t>
+          <t>الحويش</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>عاليه</t>
+          <t>عكار</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>عكار</t>
         </is>
       </c>
     </row>
@@ -94531,17 +94679,17 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>عاليه قبلي</t>
+          <t>الدوسه</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>عاليه</t>
+          <t>عكار</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>عكار</t>
         </is>
       </c>
     </row>
@@ -94553,17 +94701,17 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>عاليه وسطاني</t>
+          <t>السهلة</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>عاليه</t>
+          <t>عكار</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>عكار</t>
         </is>
       </c>
     </row>
@@ -94575,17 +94723,17 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>عين الفريديس</t>
+          <t>الشيخ عياش</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>عاليه</t>
+          <t>عكار</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>عكار</t>
         </is>
       </c>
     </row>
@@ -94597,17 +94745,17 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>محطة بحمدون</t>
+          <t>العماير</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>عاليه</t>
+          <t>عكار</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>عكار</t>
         </is>
       </c>
     </row>
@@ -94619,7 +94767,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>البساتين</t>
+          <t>العوادة</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -94641,7 +94789,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>البقيعة</t>
+          <t>الفرض</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -94663,7 +94811,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>الحويش</t>
+          <t>القبيات الذوق</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -94685,7 +94833,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>الدوسه</t>
+          <t>القبيات الضهر</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -94707,7 +94855,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>السهلة</t>
+          <t>القبيات الغربية</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -94729,7 +94877,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>الشيخ عياش</t>
+          <t>القبيات القطلبه</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
@@ -94751,7 +94899,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>العماير</t>
+          <t>القبيات غوايا</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -94773,7 +94921,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>العوادة</t>
+          <t>القبيات مرتموره</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -94795,7 +94943,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>الفرض</t>
+          <t>المونسة</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -94817,7 +94965,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>القبيات الذوق</t>
+          <t>الهيشة</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -94839,7 +94987,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>القبيات الضهر</t>
+          <t>برج العرب</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -94861,7 +95009,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>القبيات الغربية</t>
+          <t>بني صخر</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -94883,7 +95031,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>القبيات القطلبه</t>
+          <t>بيت الحاج</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -94905,7 +95053,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>القبيات غوايا</t>
+          <t>تل معيان</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -94927,7 +95075,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>القبيات مرتموره</t>
+          <t>تلبيبة</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -94949,7 +95097,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>المونسة</t>
+          <t>جبل المنصورة</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
@@ -94971,7 +95119,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>الهيشة</t>
+          <t>جرمنايا</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -94993,7 +95141,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>برج العرب</t>
+          <t>خربة الجرد</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
@@ -95015,7 +95163,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>بني صخر</t>
+          <t>خريبة الجندي</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -95037,7 +95185,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>بيت الحاج</t>
+          <t>خط البترول</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -95059,7 +95207,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>تل معيان</t>
+          <t>رجم عيسى</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
@@ -95081,7 +95229,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>تلبيبة</t>
+          <t>ضهر القنبر</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
@@ -95103,7 +95251,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>جبل المنصورة</t>
+          <t>عبودية</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
@@ -95125,7 +95273,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>جرمنايا</t>
+          <t>عين الذهب</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -95147,7 +95295,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>خربة الجرد</t>
+          <t>قنية</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -95169,7 +95317,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>خريبة الجندي</t>
+          <t>كرم زبدين</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
@@ -95191,7 +95339,7 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>خط البترول</t>
+          <t>مراح الخوخ</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
@@ -95213,17 +95361,17 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>رجم عيسى</t>
+          <t>الحجة</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>عكار</t>
+          <t>قرى صيدا</t>
         </is>
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>عكار</t>
+          <t>الجنوب</t>
         </is>
       </c>
     </row>
@@ -95235,17 +95383,17 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>ضهر القنبر</t>
+          <t>القنيطرة</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>عكار</t>
+          <t>قرى صيدا</t>
         </is>
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>عكار</t>
+          <t>الجنوب</t>
         </is>
       </c>
     </row>
@@ -95257,17 +95405,17 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>عبودية</t>
+          <t>المعمرية</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>عكار</t>
+          <t>قرى صيدا</t>
         </is>
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>عكار</t>
+          <t>الجنوب</t>
         </is>
       </c>
     </row>
@@ -95279,17 +95427,17 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>عين الذهب</t>
+          <t>المية ومية</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>عكار</t>
+          <t>قرى صيدا</t>
         </is>
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>عكار</t>
+          <t>الجنوب</t>
         </is>
       </c>
     </row>
@@ -95301,17 +95449,17 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>قنية</t>
+          <t>كوثرية السياد</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>عكار</t>
+          <t>قرى صيدا</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>عكار</t>
+          <t>الجنوب</t>
         </is>
       </c>
     </row>
@@ -95323,17 +95471,17 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>كرم زبدين</t>
+          <t>الروضة</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>عكار</t>
+          <t>قضاءي البقاع الغربي وراشيا</t>
         </is>
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>عكار</t>
+          <t>البقاع</t>
         </is>
       </c>
     </row>
@@ -95345,17 +95493,17 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>مراح الخوخ</t>
+          <t>الشبرقية</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>عكار</t>
+          <t>قضاءي البقاع الغربي وراشيا</t>
         </is>
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>عكار</t>
+          <t>البقاع</t>
         </is>
       </c>
     </row>
@@ -95367,17 +95515,17 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>الحجة</t>
+          <t>عين التينه</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>قرى صيدا</t>
+          <t>قضاءي البقاع الغربي وراشيا</t>
         </is>
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>الجنوب</t>
+          <t>البقاع</t>
         </is>
       </c>
     </row>
@@ -95389,17 +95537,17 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>القنيطرة</t>
+          <t>كفردنيس</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>قرى صيدا</t>
+          <t>قضاءي البقاع الغربي وراشيا</t>
         </is>
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>الجنوب</t>
+          <t>البقاع</t>
         </is>
       </c>
     </row>
@@ -95411,17 +95559,17 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>المعمرية</t>
+          <t>كفرقوق</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>قرى صيدا</t>
+          <t>قضاءي البقاع الغربي وراشيا</t>
         </is>
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>الجنوب</t>
+          <t>البقاع</t>
         </is>
       </c>
     </row>
@@ -95433,17 +95581,17 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>المية ومية</t>
+          <t>محيدثه</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>قرى صيدا</t>
+          <t>قضاءي البقاع الغربي وراشيا</t>
         </is>
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>الجنوب</t>
+          <t>البقاع</t>
         </is>
       </c>
     </row>
@@ -95455,17 +95603,17 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>كوثرية السياد</t>
+          <t>الانصار</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>قرى صيدا</t>
+          <t>قضاءي بعلبك والهرمل</t>
         </is>
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>الجنوب</t>
+          <t>بعلبك والهرمل</t>
         </is>
       </c>
     </row>
@@ -95477,17 +95625,17 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>الروضة</t>
+          <t>البرانيه حي المسيحيين</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>قضاءي البقاع الغربي وراشيا</t>
+          <t>قضاءي بعلبك والهرمل</t>
         </is>
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>البقاع</t>
+          <t>بعلبك والهرمل</t>
         </is>
       </c>
     </row>
@@ -95499,17 +95647,17 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>الشبرقية</t>
+          <t>البرباره محلة المسيحيين</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>قضاءي البقاع الغربي وراشيا</t>
+          <t>قضاءي بعلبك والهرمل</t>
         </is>
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>البقاع</t>
+          <t>بعلبك والهرمل</t>
         </is>
       </c>
     </row>
@@ -95521,17 +95669,17 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>عين التينه</t>
+          <t>البويضة</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>قضاءي البقاع الغربي وراشيا</t>
+          <t>قضاءي بعلبك والهرمل</t>
         </is>
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>البقاع</t>
+          <t>بعلبك والهرمل</t>
         </is>
       </c>
     </row>
@@ -95543,17 +95691,17 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>كفردنيس</t>
+          <t>البويضة الحي الغربي</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>قضاءي البقاع الغربي وراشيا</t>
+          <t>قضاءي بعلبك والهرمل</t>
         </is>
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>البقاع</t>
+          <t>بعلبك والهرمل</t>
         </is>
       </c>
     </row>
@@ -95565,17 +95713,17 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>كفرقوق</t>
+          <t>البويضة الشمالية</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>قضاءي البقاع الغربي وراشيا</t>
+          <t>قضاءي بعلبك والهرمل</t>
         </is>
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>البقاع</t>
+          <t>بعلبك والهرمل</t>
         </is>
       </c>
     </row>
@@ -95587,17 +95735,17 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>محيدثه</t>
+          <t>التوفيقيه</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>قضاءي البقاع الغربي وراشيا</t>
+          <t>قضاءي بعلبك والهرمل</t>
         </is>
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>البقاع</t>
+          <t>بعلبك والهرمل</t>
         </is>
       </c>
     </row>
@@ -95609,7 +95757,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>الانصار</t>
+          <t>الجوبانية</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
@@ -95631,7 +95779,7 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>البرانيه حي المسيحيين</t>
+          <t>الحدث الشمالي</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
@@ -95653,7 +95801,7 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>البرباره محلة المسيحيين</t>
+          <t>الحدث الغربي</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
@@ -95675,7 +95823,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>البويضة</t>
+          <t>الحريقه</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
@@ -95697,7 +95845,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>البويضة الحي الغربي</t>
+          <t>الحلانيه</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
@@ -95719,7 +95867,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>البويضة الشمالية</t>
+          <t>الريش حي الشرقي</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
@@ -95741,7 +95889,7 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>التوفيقيه</t>
+          <t>الريش حي الشميس</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
@@ -95763,7 +95911,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>الجوبانية</t>
+          <t>الريش حي الغربي</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
@@ -95785,7 +95933,7 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>الحدث الشمالي</t>
+          <t>الزرازير</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
@@ -95807,7 +95955,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>الحدث الغربي</t>
+          <t>الزويتيني</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
@@ -95829,7 +95977,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>الحريقه</t>
+          <t>السعيده</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
@@ -95851,7 +95999,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>الحلانيه</t>
+          <t>السويسة</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
@@ -95873,7 +96021,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>الريش حي الشرقي</t>
+          <t>الشواغير التحتا</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
@@ -95895,7 +96043,7 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>الريش حي الشميس</t>
+          <t>الشواغير الفوقا</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
@@ -95917,7 +96065,7 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>الريش حي الغربي</t>
+          <t>الصوانية</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
@@ -95939,7 +96087,7 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>الزرازير</t>
+          <t>العقيدية</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
@@ -95961,7 +96109,7 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>الزويتيني</t>
+          <t>العلاق</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
@@ -95983,7 +96131,7 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>السعيده</t>
+          <t>الفاكهة حي الجامع</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
@@ -96005,7 +96153,7 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>السويسة</t>
+          <t>الفاكهة حي مار جرجس</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
@@ -96027,7 +96175,7 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>الشواغير التحتا</t>
+          <t>القدام</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
@@ -96049,7 +96197,7 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>الشواغير الفوقا</t>
+          <t>القرينة</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
@@ -96071,7 +96219,7 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>الصوانية</t>
+          <t>القصر</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
@@ -96093,7 +96241,7 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>العقيدية</t>
+          <t>الكواخ</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
@@ -96115,7 +96263,7 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>العلاق</t>
+          <t>المعاصر</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
@@ -96137,7 +96285,7 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>الفاكهة حي الجامع</t>
+          <t>النبي رشاده</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
@@ -96159,7 +96307,7 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>الفاكهة حي مار جرجس</t>
+          <t>النبي نعام</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
@@ -96181,7 +96329,7 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>القدام</t>
+          <t>النقرة</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
@@ -96203,7 +96351,7 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>القرينة</t>
+          <t>بريصا</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
@@ -96225,7 +96373,7 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>القصر</t>
+          <t>بيت ابو صليبي</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
@@ -96247,7 +96395,7 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>الكواخ</t>
+          <t>جوار الحشيش</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
@@ -96269,7 +96417,7 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>المعاصر</t>
+          <t>حوش السيد علي</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
@@ -96291,7 +96439,7 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>النبي رشاده</t>
+          <t>حي الزهراء</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
@@ -96313,7 +96461,7 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>النبي نعام</t>
+          <t>حي الصلح</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
@@ -96335,7 +96483,7 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>النقرة</t>
+          <t>حي العباسية</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
@@ -96357,7 +96505,7 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>بريصا</t>
+          <t>حي عز الدين</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
@@ -96379,7 +96527,7 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>بيت ابو صليبي</t>
+          <t>دار الواسعة</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
@@ -96401,7 +96549,7 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>جوار الحشيش</t>
+          <t>رماسا</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
@@ -96423,7 +96571,7 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>حوش السيد علي</t>
+          <t>سهلات الماء</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
@@ -96445,7 +96593,7 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>حي الزهراء</t>
+          <t>شعت حي الضهر</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
@@ -96467,7 +96615,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>حي الصلح</t>
+          <t>صفرا</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
@@ -96489,7 +96637,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>حي العباسية</t>
+          <t>غفره</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
@@ -96511,7 +96659,7 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>حي عز الدين</t>
+          <t>فلاوي</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
@@ -96533,7 +96681,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>دار الواسعة</t>
+          <t>فيسان</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
@@ -96555,7 +96703,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>رماسا</t>
+          <t>قبة دورس</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
@@ -96577,7 +96725,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>سهلات الماء</t>
+          <t>قلد السبع</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
@@ -96599,7 +96747,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>شعت حي الضهر</t>
+          <t>قلعة</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
@@ -96621,7 +96769,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>صفرا</t>
+          <t>قلعة غربي</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
@@ -96643,7 +96791,7 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>غفره</t>
+          <t>قنافذ</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
@@ -96665,7 +96813,7 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>فلاوي</t>
+          <t>كفردبش</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
@@ -96687,7 +96835,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>فيسان</t>
+          <t>مراح العين</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
@@ -96709,7 +96857,7 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>قبة دورس</t>
+          <t>مزرعة آل سويدان</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
@@ -96731,7 +96879,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>قلد السبع</t>
+          <t>مزرعة ابو صليبي</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
@@ -96753,7 +96901,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>قلعة</t>
+          <t>مزرعة التوت</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
@@ -96775,7 +96923,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>قلعة غربي</t>
+          <t>مزرعة الضليل</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
@@ -96797,7 +96945,7 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>قنافذ</t>
+          <t>مزرعة الفقيه</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
@@ -96819,7 +96967,7 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>كفردبش</t>
+          <t>مزرعة بيت الطشم</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
@@ -96841,7 +96989,7 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>مراح العين</t>
+          <t>مزرعة بيت مطر</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
@@ -96863,7 +97011,7 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>مزرعة آل سويدان</t>
+          <t>مزرعة سجد</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
@@ -96885,7 +97033,7 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>مزرعة ابو صليبي</t>
+          <t>مصنع الزهرة</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
@@ -96907,7 +97055,7 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>مزرعة التوت</t>
+          <t>وادي التركمان</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
@@ -96929,7 +97077,7 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>مزرعة الضليل</t>
+          <t>وادي الرطل</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
@@ -96951,7 +97099,7 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>مزرعة الفقيه</t>
+          <t>وادي الزين</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
@@ -96973,7 +97121,7 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>مزرعة بيت الطشم</t>
+          <t>وادي الصفا الشرقي</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
@@ -96995,7 +97143,7 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>مزرعة بيت مطر</t>
+          <t>وادي المشمشه</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
@@ -97017,7 +97165,7 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>مزرعة سجد</t>
+          <t>وادي النيرة</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
@@ -97039,7 +97187,7 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>مصنع الزهرة</t>
+          <t>وادي بنيت</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
@@ -97061,17 +97209,17 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>وادي التركمان</t>
+          <t>الجديدة حي السراي</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>قضاءي بعلبك والهرمل</t>
+          <t>قضاءي مرجعيون وحاصبيا</t>
         </is>
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>بعلبك والهرمل</t>
+          <t>النبطية</t>
         </is>
       </c>
     </row>
@@ -97083,17 +97231,17 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>وادي الرطل</t>
+          <t>الجديدة حي العيون</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>قضاءي بعلبك والهرمل</t>
+          <t>قضاءي مرجعيون وحاصبيا</t>
         </is>
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>بعلبك والهرمل</t>
+          <t>النبطية</t>
         </is>
       </c>
     </row>
@@ -97105,17 +97253,17 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>وادي الزين</t>
+          <t>الجديدة حي القلعة</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>قضاءي بعلبك والهرمل</t>
+          <t>قضاءي مرجعيون وحاصبيا</t>
         </is>
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>بعلبك والهرمل</t>
+          <t>النبطية</t>
         </is>
       </c>
     </row>
@@ -97127,17 +97275,17 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>وادي الصفا الشرقي</t>
+          <t>الجديدة حي المدارس</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>قضاءي بعلبك والهرمل</t>
+          <t>قضاءي مرجعيون وحاصبيا</t>
         </is>
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>بعلبك والهرمل</t>
+          <t>النبطية</t>
         </is>
       </c>
     </row>
@@ -97149,17 +97297,17 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>وادي المشمشه</t>
+          <t>الفرديس</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>قضاءي بعلبك والهرمل</t>
+          <t>قضاءي مرجعيون وحاصبيا</t>
         </is>
       </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>بعلبك والهرمل</t>
+          <t>النبطية</t>
         </is>
       </c>
     </row>
@@ -97171,17 +97319,17 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>وادي النيرة</t>
+          <t>الوزاني</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>قضاءي بعلبك والهرمل</t>
+          <t>قضاءي مرجعيون وحاصبيا</t>
         </is>
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>بعلبك والهرمل</t>
+          <t>النبطية</t>
         </is>
       </c>
     </row>
@@ -97193,17 +97341,17 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>وادي بنيت</t>
+          <t>برج الملوك</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>قضاءي بعلبك والهرمل</t>
+          <t>قضاءي مرجعيون وحاصبيا</t>
         </is>
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>بعلبك والهرمل</t>
+          <t>النبطية</t>
         </is>
       </c>
     </row>
@@ -97215,7 +97363,7 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>الجديدة حي السراي</t>
+          <t>بويضة</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
@@ -97237,7 +97385,7 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>الجديدة حي العيون</t>
+          <t>رب ثلاثين</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
@@ -97259,7 +97407,7 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>الجديدة حي القلعة</t>
+          <t>سرده والعمره</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
@@ -97281,7 +97429,7 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>الجديدة حي المدارس</t>
+          <t>عديسه</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
@@ -97303,7 +97451,7 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>الفرديس</t>
+          <t>كفرشوبا</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
@@ -97325,17 +97473,17 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>الوزاني</t>
+          <t>السهيله</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>قضاءي مرجعيون وحاصبيا</t>
+          <t>كسروان</t>
         </is>
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>النبطية</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -97347,17 +97495,17 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>برج الملوك</t>
+          <t>النموره وكفر جريف</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>قضاءي مرجعيون وحاصبيا</t>
+          <t>كسروان</t>
         </is>
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>النبطية</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -97369,17 +97517,17 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>بويضة</t>
+          <t>ساحل علما</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>قضاءي مرجعيون وحاصبيا</t>
+          <t>كسروان</t>
         </is>
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>النبطية</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -97391,17 +97539,17 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>رب ثلاثين</t>
+          <t>شوان والعبره</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>قضاءي مرجعيون وحاصبيا</t>
+          <t>كسروان</t>
         </is>
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>النبطية</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -97413,17 +97561,17 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>سرده والعمره</t>
+          <t>غزير القناة</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>قضاءي مرجعيون وحاصبيا</t>
+          <t>كسروان</t>
         </is>
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>النبطية</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -97435,17 +97583,17 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>عديسه</t>
+          <t>غزير المعاملتين</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>قضاءي مرجعيون وحاصبيا</t>
+          <t>كسروان</t>
         </is>
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>النبطية</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -97457,17 +97605,17 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>كفرشوبا</t>
+          <t>الزاهرية</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>قضاءي مرجعيون وحاصبيا</t>
+          <t>مدينة طرابلس</t>
         </is>
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>النبطية</t>
+          <t>الشمال</t>
         </is>
       </c>
     </row>
@@ -97479,17 +97627,17 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>السهيله</t>
+          <t>السويقه</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>كسروان</t>
+          <t>مدينة طرابلس</t>
         </is>
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>الشمال</t>
         </is>
       </c>
     </row>
@@ -97501,17 +97649,17 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>النموره وكفر جريف</t>
+          <t>القبة</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>كسروان</t>
+          <t>مدينة طرابلس</t>
         </is>
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>الشمال</t>
         </is>
       </c>
     </row>
@@ -97523,235 +97671,15 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>ساحل علما</t>
+          <t>وادي النحلة</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>كسروان</t>
+          <t>مدينة طرابلس</t>
         </is>
       </c>
       <c r="D653" t="inlineStr">
-        <is>
-          <t>جبل لبنان</t>
-        </is>
-      </c>
-    </row>
-    <row r="654">
-      <c r="A654" t="inlineStr">
-        <is>
-          <t>Arabic</t>
-        </is>
-      </c>
-      <c r="B654" t="inlineStr">
-        <is>
-          <t>شوان والعبره</t>
-        </is>
-      </c>
-      <c r="C654" t="inlineStr">
-        <is>
-          <t>كسروان</t>
-        </is>
-      </c>
-      <c r="D654" t="inlineStr">
-        <is>
-          <t>جبل لبنان</t>
-        </is>
-      </c>
-    </row>
-    <row r="655">
-      <c r="A655" t="inlineStr">
-        <is>
-          <t>Arabic</t>
-        </is>
-      </c>
-      <c r="B655" t="inlineStr">
-        <is>
-          <t>غزير القناة</t>
-        </is>
-      </c>
-      <c r="C655" t="inlineStr">
-        <is>
-          <t>كسروان</t>
-        </is>
-      </c>
-      <c r="D655" t="inlineStr">
-        <is>
-          <t>جبل لبنان</t>
-        </is>
-      </c>
-    </row>
-    <row r="656">
-      <c r="A656" t="inlineStr">
-        <is>
-          <t>Arabic</t>
-        </is>
-      </c>
-      <c r="B656" t="inlineStr">
-        <is>
-          <t>غزير المعاملتين</t>
-        </is>
-      </c>
-      <c r="C656" t="inlineStr">
-        <is>
-          <t>كسروان</t>
-        </is>
-      </c>
-      <c r="D656" t="inlineStr">
-        <is>
-          <t>جبل لبنان</t>
-        </is>
-      </c>
-    </row>
-    <row r="657">
-      <c r="A657" t="inlineStr">
-        <is>
-          <t>Arabic</t>
-        </is>
-      </c>
-      <c r="B657" t="inlineStr">
-        <is>
-          <t>التبانة</t>
-        </is>
-      </c>
-      <c r="C657" t="inlineStr">
-        <is>
-          <t>مدينة طرابلس</t>
-        </is>
-      </c>
-      <c r="D657" t="inlineStr">
-        <is>
-          <t>الشمال</t>
-        </is>
-      </c>
-    </row>
-    <row r="658">
-      <c r="A658" t="inlineStr">
-        <is>
-          <t>Arabic</t>
-        </is>
-      </c>
-      <c r="B658" t="inlineStr">
-        <is>
-          <t>الرمانة</t>
-        </is>
-      </c>
-      <c r="C658" t="inlineStr">
-        <is>
-          <t>مدينة طرابلس</t>
-        </is>
-      </c>
-      <c r="D658" t="inlineStr">
-        <is>
-          <t>الشمال</t>
-        </is>
-      </c>
-    </row>
-    <row r="659">
-      <c r="A659" t="inlineStr">
-        <is>
-          <t>Arabic</t>
-        </is>
-      </c>
-      <c r="B659" t="inlineStr">
-        <is>
-          <t>الزاهرية</t>
-        </is>
-      </c>
-      <c r="C659" t="inlineStr">
-        <is>
-          <t>مدينة طرابلس</t>
-        </is>
-      </c>
-      <c r="D659" t="inlineStr">
-        <is>
-          <t>الشمال</t>
-        </is>
-      </c>
-    </row>
-    <row r="660">
-      <c r="A660" t="inlineStr">
-        <is>
-          <t>Arabic</t>
-        </is>
-      </c>
-      <c r="B660" t="inlineStr">
-        <is>
-          <t>السويقه</t>
-        </is>
-      </c>
-      <c r="C660" t="inlineStr">
-        <is>
-          <t>مدينة طرابلس</t>
-        </is>
-      </c>
-      <c r="D660" t="inlineStr">
-        <is>
-          <t>الشمال</t>
-        </is>
-      </c>
-    </row>
-    <row r="661">
-      <c r="A661" t="inlineStr">
-        <is>
-          <t>Arabic</t>
-        </is>
-      </c>
-      <c r="B661" t="inlineStr">
-        <is>
-          <t>القبة</t>
-        </is>
-      </c>
-      <c r="C661" t="inlineStr">
-        <is>
-          <t>مدينة طرابلس</t>
-        </is>
-      </c>
-      <c r="D661" t="inlineStr">
-        <is>
-          <t>الشمال</t>
-        </is>
-      </c>
-    </row>
-    <row r="662">
-      <c r="A662" t="inlineStr">
-        <is>
-          <t>Arabic</t>
-        </is>
-      </c>
-      <c r="B662" t="inlineStr">
-        <is>
-          <t>المهاترة</t>
-        </is>
-      </c>
-      <c r="C662" t="inlineStr">
-        <is>
-          <t>مدينة طرابلس</t>
-        </is>
-      </c>
-      <c r="D662" t="inlineStr">
-        <is>
-          <t>الشمال</t>
-        </is>
-      </c>
-    </row>
-    <row r="663">
-      <c r="A663" t="inlineStr">
-        <is>
-          <t>Arabic</t>
-        </is>
-      </c>
-      <c r="B663" t="inlineStr">
-        <is>
-          <t>وادي النحلة</t>
-        </is>
-      </c>
-      <c r="C663" t="inlineStr">
-        <is>
-          <t>مدينة طرابلس</t>
-        </is>
-      </c>
-      <c r="D663" t="inlineStr">
         <is>
           <t>الشمال</t>
         </is>

--- a/FuzzyMatch/Lebanese_Villages_Matched_v6.xlsx
+++ b/FuzzyMatch/Lebanese_Villages_Matched_v6.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E158"/>
+  <dimension ref="A1:E165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
@@ -578,283 +578,271 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Suggestions skipped/conflicted/duplicated</t>
+          <t>Reviewer-approved matches applied (--accept)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Still unmatched English</t>
+          <t>Suggestions skipped/conflicted/duplicated</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Still unmatched Arabic</t>
+          <t>Still unmatched English</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>267</v>
+        <v>382</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Arabic rows dropped as already-matched (one-to-one)</t>
+          <t>Still unmatched Arabic</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>44</v>
+        <v>264</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>One-to-one conflicts needing human review</t>
+          <t>Arabic rows dropped as already-matched (one-to-one)</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Subdivision groups in source (expanded to pairs)</t>
+          <t>One-to-one conflicts needing human review</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>Subdivision groups in source (expanded to pairs)</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>Subdivision pairs auto-discovered</t>
         </is>
       </c>
-      <c r="B22" t="n">
+      <c r="B23" t="n">
         <v>56</v>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>SUBDIVISION GROUPS (source workbook)</t>
-        </is>
-      </c>
-    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>English Name</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>District</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Mohafaza</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Arabic subdivisions</t>
+          <t>SUBDIVISION GROUPS (source workbook)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Amioune</t>
+          <t>English Name</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Koura</t>
+          <t>District</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Mohafaza</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>اميون شرقي | اميون غربي</t>
+          <t>Arabic subdivisions</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Arsale</t>
+          <t>Amioune</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Baalbeck</t>
+          <t>Koura</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Baalbak - Hermel</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>عرسال جنوبي | عرسال شرقي | عرسال شمالي | عين السوداء</t>
+          <t>اميون شرقي | اميون غربي</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Aïn-Ebel</t>
+          <t>Arsale</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Bint Jbayl</t>
+          <t>Baalbeck</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Nabatiyeh</t>
+          <t>Baalbak - Hermel</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>عين ابل حي الدير | عين ابل حي العين | عين ابل حي الكنيسة</t>
+          <t>عرسال جنوبي | عرسال شرقي | عرسال شمالي | عين السوداء</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Baskinta</t>
+          <t>Aïn-Ebel</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>El Metn</t>
+          <t>Bint Jbayl</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Mount Lebanon</t>
+          <t>Nabatiyeh</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>بسكنتا جنوبي | بسكنتا شمالي</t>
+          <t>عين ابل حي الدير | عين ابل حي العين | عين ابل حي الكنيسة</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Bint Jbail</t>
+          <t>Baskinta</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Bint Jbayl</t>
+          <t>El Metn</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Nabatiyeh</t>
+          <t>Mount Lebanon</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>بنت جبيل حي البركه | بنت جبيل حي الجامع | بنت جبيل حي الحسينية | بنت جبيل حي الحواره | بنت جبيل حي عين الصغيرة</t>
+          <t>بسكنتا جنوبي | بسكنتا شمالي</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Brital</t>
+          <t>Bint Jbail</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Baalbeck</t>
+          <t>Bint Jbayl</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Baalbak - Hermel</t>
+          <t>Nabatiyeh</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>بريتال اليونسية | بريتال حي التين | بريتال شرقي | بريتال شميس | بريتال شميس غربي | بريتال عين البنيه | بريتال عين الجوز | بريتال غربي</t>
+          <t>بنت جبيل حي البركه | بنت جبيل حي الجامع | بنت جبيل حي الحسينية | بنت جبيل حي الحواره | بنت جبيل حي عين الصغيرة</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Chabaaa</t>
+          <t>Brital</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Hasbaya</t>
+          <t>Baalbeck</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Nabatiyeh</t>
+          <t>Baalbak - Hermel</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>شبعا شرقي | شبعا غربي</t>
+          <t>بريتال اليونسية | بريتال حي التين | بريتال شرقي | بريتال شميس | بريتال شميس غربي | بريتال عين البنيه | بريتال عين الجوز | بريتال غربي</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Chemistar</t>
+          <t>Chabaaa</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Baalbeck</t>
+          <t>Hasbaya</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Baalbak - Hermel</t>
+          <t>Nabatiyeh</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>شمسطار الجنوبي | شمسطار الشرقي | شمسطار الشمالي | شمسطار الغربي</t>
+          <t>شبعا شرقي | شبعا غربي</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Douress</t>
+          <t>Chemistar</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -869,41 +857,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>دورس حي البير | دورس حي السيدة | دورس حي الشحاديه</t>
+          <t>شمسطار الجنوبي | شمسطار الشرقي | شمسطار الشمالي | شمسطار الغربي</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>EL-Khiam</t>
+          <t>Douress</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Marjaayoun</t>
+          <t>Baalbeck</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Nabatiyeh</t>
+          <t>Baalbak - Hermel</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>الخيام جنوبي | الخيام شرقي | الخيام شمالي | الخيام غربي</t>
+          <t>دورس حي البير | دورس حي السيدة | دورس حي الشحاديه</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Hasbaya</t>
+          <t>EL-Khiam</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Hasbaya</t>
+          <t>Marjaayoun</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -913,36 +901,36 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>حاصبيا حي السراي | حاصبيا حي العين | حاصبيا حي الفوقاني | حاصبيا حي صفيفة</t>
+          <t>الخيام جنوبي | الخيام شرقي | الخيام شمالي | الخيام غربي</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Hourtala</t>
+          <t>Hasbaya</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Baalbeck</t>
+          <t>Hasbaya</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Baalbak - Hermel</t>
+          <t>Nabatiyeh</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>حور تعلا | حور تعلا حي الشعب | حور تعلا حي الوادي | حور تعلا حي حقل العرجة</t>
+          <t>حاصبيا حي السراي | حاصبيا حي العين | حاصبيا حي الفوقاني | حاصبيا حي صفيفة</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Kfardan</t>
+          <t>Hourtala</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -957,146 +945,146 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>كفردان | كفردان الغربي</t>
+          <t>حور تعلا | حور تعلا حي الشعب | حور تعلا حي الوادي | حور تعلا حي حقل العرجة</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Maska et El-Ghabeh</t>
+          <t>Kfardan</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>El Metn</t>
+          <t>Baalbeck</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Mount Lebanon</t>
+          <t>Baalbak - Hermel</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>الغابه | المسقى</t>
+          <t>كفردان | كفردان الغربي</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Nabatiyé El-Tahta</t>
+          <t>Maska et El-Ghabeh</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Nabatiyeh</t>
+          <t>El Metn</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Nabatiyeh</t>
+          <t>Mount Lebanon</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>النبطية التحتا حي البياض | النبطية التحتا حي السراي | النبطية التحتا حي المسيحيين | النبطية التحتا حي الميدان</t>
+          <t>الغابه | المسقى</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Nabha</t>
+          <t>Nabatiyé El-Tahta</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Baalbeck</t>
+          <t>Nabatiyeh</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Baalbak - Hermel</t>
+          <t>Nabatiyeh</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>نبحا الحرفوش | نبحا الدمدوم | نبحا المحفارة | نبحا حي الجامع</t>
+          <t>النبطية التحتا حي البياض | النبطية التحتا حي السراي | النبطية التحتا حي المسيحيين | النبطية التحتا حي الميدان</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Ras Maska</t>
+          <t>Nabha</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Koura</t>
+          <t>Baalbeck</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Baalbak - Hermel</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>راس مسقا الجنوبية | راس مسقا الشمالية</t>
+          <t>نبحا الحرفوش | نبحا الدمدوم | نبحا المحفارة | نبحا حي الجامع</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sakiet-El-Misk et Bhorsaf</t>
+          <t>Ras Maska</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>El Metn</t>
+          <t>Koura</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Mount Lebanon</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ساقية المسك | بحر صاف</t>
+          <t>راس مسقا الجنوبية | راس مسقا الشمالية</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Serraaine El Faouka</t>
+          <t>Sakiet-El-Misk et Bhorsaf</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Baalbeck</t>
+          <t>El Metn</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Baalbak - Hermel</t>
+          <t>Mount Lebanon</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>سرعين الفوقا حي الجامع | سرعين الفوقا حي الحارة | سرعين الفوقا شرقي | سرعين الفوقا غربي</t>
+          <t>ساقية المسك | بحر صاف</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Taraya</t>
+          <t>Serraaine El Faouka</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1111,130 +1099,125 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>طاريا الجنوبي | طاريا الشمالي</t>
+          <t>سرعين الفوقا حي الجامع | سرعين الفوقا حي الحارة | سرعين الفوقا شرقي | سرعين الفوقا غربي</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Tibnine</t>
+          <t>Taraya</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Bint Jbayl</t>
+          <t>Baalbeck</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Nabatiyeh</t>
+          <t>Baalbak - Hermel</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>تبنين حي التحتاني | تبنين حي الفوقاني | تبنين حي الكاثوليك | تبنين حي آل بري</t>
+          <t>طاريا الجنوبي | طاريا الشمالي</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>Tibnine</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Bint Jbayl</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Nabatiyeh</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>تبنين حي التحتاني | تبنين حي الفوقاني | تبنين حي الكاثوليك | تبنين حي آل بري</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>Younine</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>Baalbeck</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Baalbak - Hermel</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>يونين جنوبي | يونين شرقي | يونين شمالي | يونين غربي</t>
         </is>
       </c>
     </row>
-    <row r="48"/>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>SUBDIVISION PAIRS AUTO-DISCOVERED</t>
-        </is>
-      </c>
-    </row>
+    <row r="49"/>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>English Name</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Arabic Name</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>District</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Mohafaza</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>SUBDIVISION PAIRS AUTO-DISCOVERED</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Aley</t>
+          <t>English Name</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>عاليه غربي</t>
+          <t>Arabic Name</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Aley</t>
+          <t>District</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Mount Lebanon</t>
+          <t>Mohafaza</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Fuzzy-auto subdivision (46.2) [seeded]</t>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Borge el Baragenat</t>
+          <t>Aley</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>برج البراجنة حي السياد</t>
+          <t>عاليه غربي</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Baabda</t>
+          <t>Aley</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1244,7 +1227,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Fuzzy-auto subdivision (57.1) [seeded]</t>
+          <t>Fuzzy-auto subdivision (46.2) [seeded]</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1239,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>برج البراجنة حي المنشية</t>
+          <t>برج البراجنة حي السياد</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1271,19 +1254,19 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Fuzzy-auto subdivision (55.4) [seeded]</t>
+          <t>Fuzzy-auto subdivision (57.1) [seeded]</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Haret Horaïk</t>
+          <t>Borge el Baragenat</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>حارة حريك حي الكنيسة</t>
+          <t>برج البراجنة حي المنشية</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1298,34 +1281,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Fuzzy-auto subdivision (81.8) [seeded]</t>
+          <t>Fuzzy-auto subdivision (55.4) [seeded]</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Al-Nabi Chite</t>
+          <t>Haret Horaïk</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>النبي شيت حي الجنوبي</t>
+          <t>حارة حريك حي الكنيسة</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Baalbeck</t>
+          <t>Baabda</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Baalbak - Hermel</t>
+          <t>Mount Lebanon</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Fuzzy-auto subdivision (80.0) [seeded]</t>
+          <t>Fuzzy-auto subdivision (81.8) [seeded]</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1320,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>النبي شيت حي الشرقي</t>
+          <t>النبي شيت حي الجنوبي</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1364,7 +1347,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>النبي شيت حي الشمالي</t>
+          <t>النبي شيت حي الشرقي</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1391,7 +1374,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>النبي شيت حي العريض</t>
+          <t>النبي شيت حي الشمالي</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1418,7 +1401,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>النبي شيت حي العقبة</t>
+          <t>النبي شيت حي العريض</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1445,7 +1428,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>النبي شيت حي الغربي</t>
+          <t>النبي شيت حي العقبة</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1472,7 +1455,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>النبي شيت حي طبشار</t>
+          <t>النبي شيت حي الغربي</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1494,27 +1477,27 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Bcharré</t>
+          <t>Al-Nabi Chite</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>بشري حي المقدمين</t>
+          <t>النبي شيت حي طبشار</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bcharre</t>
+          <t>Baalbeck</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Baalbak - Hermel</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Fuzzy-auto subdivision (65.5) [seeded]</t>
+          <t>Fuzzy-auto subdivision (80.0) [seeded]</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1509,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>بشري حي مار سابا</t>
+          <t>بشري حي المقدمين</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1553,7 +1536,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>بشري حي مار يوحنا</t>
+          <t>بشري حي مار سابا</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1575,39 +1558,39 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Baakline</t>
+          <t>Bcharré</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>بعقلين الفوقا</t>
+          <t>بشري حي مار يوحنا</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chouf</t>
+          <t>Bcharre</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Mount Lebanon</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Fuzzy-auto subdivision (100.0) [seeded]</t>
+          <t>Fuzzy-auto subdivision (65.5) [seeded]</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Chehime</t>
+          <t>Baakline</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>شحيم حي البيادر</t>
+          <t>بعقلين الفوقا</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1622,7 +1605,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Fuzzy-auto subdivision (75.0) [seeded]</t>
+          <t>Fuzzy-auto subdivision (100.0) [seeded]</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1617,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>شحيم حي الجامع</t>
+          <t>شحيم حي البيادر</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1661,7 +1644,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>شحيم حي السهله</t>
+          <t>شحيم حي الجامع</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1688,7 +1671,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>شحيم حي الشريفة</t>
+          <t>شحيم حي السهله</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -1715,7 +1698,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>شحيم حي الوسطاني</t>
+          <t>شحيم حي الشريفة</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1742,7 +1725,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>شحيم حي شحرور</t>
+          <t>شحيم حي الوسطاني</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1764,27 +1747,27 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Hermel</t>
+          <t>Chehime</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>الهرمل حي الوقف</t>
+          <t>شحيم حي شحرور</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Hermel</t>
+          <t>Chouf</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Baalbak - Hermel</t>
+          <t>Mount Lebanon</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Fuzzy-auto subdivision (72.0) [seeded]</t>
+          <t>Fuzzy-auto subdivision (75.0) [seeded]</t>
         </is>
       </c>
     </row>
@@ -1796,7 +1779,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>الهرمل حي بديتا</t>
+          <t>الهرمل حي الوقف</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -1818,27 +1801,27 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Meis El-Jabal</t>
+          <t>Hermel</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ميس الجبل شرقي</t>
+          <t>الهرمل حي بديتا</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Marjaayoun</t>
+          <t>Hermel</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Nabatiyeh</t>
+          <t>Baalbak - Hermel</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Fuzzy-auto subdivision (85.5) [seeded]</t>
+          <t>Fuzzy-auto subdivision (72.0) [seeded]</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1833,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ميس الجبل شمالي</t>
+          <t>ميس الجبل شرقي</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -1877,7 +1860,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ميس الجبل غربي</t>
+          <t>ميس الجبل شمالي</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -1899,27 +1882,27 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Saïda Dekerman</t>
+          <t>Meis El-Jabal</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>صيدا حي الزويتيني</t>
+          <t>ميس الجبل غربي</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Saida</t>
+          <t>Marjaayoun</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Nabatiyeh</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Fuzzy-auto subdivision (46.2) [seeded]</t>
+          <t>Fuzzy-auto subdivision (85.5) [seeded]</t>
         </is>
       </c>
     </row>
@@ -1931,7 +1914,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>صيدا حي السبيل</t>
+          <t>صيدا حي الزويتيني</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -1946,7 +1929,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Fuzzy-auto subdivision (42.9) [seeded]</t>
+          <t>Fuzzy-auto subdivision (46.2) [seeded]</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1941,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>صيدا حي السراي</t>
+          <t>صيدا حي السبيل</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -1973,7 +1956,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Fuzzy-auto subdivision (50.0) [seeded]</t>
+          <t>Fuzzy-auto subdivision (42.9) [seeded]</t>
         </is>
       </c>
     </row>
@@ -1985,7 +1968,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>صيدا حي الشارع</t>
+          <t>صيدا حي السراي</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2000,7 +1983,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Fuzzy-auto subdivision (48.3) [seeded]</t>
+          <t>Fuzzy-auto subdivision (50.0) [seeded]</t>
         </is>
       </c>
     </row>
@@ -2012,7 +1995,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>صيدا حي القناية</t>
+          <t>صيدا حي الشارع</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2027,7 +2010,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Fuzzy-auto subdivision (66.7) [seeded]</t>
+          <t>Fuzzy-auto subdivision (48.3) [seeded]</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2022,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>صيدا حي الكشك</t>
+          <t>صيدا حي القناية</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2054,7 +2037,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Fuzzy-auto subdivision (42.9) [seeded]</t>
+          <t>Fuzzy-auto subdivision (66.7) [seeded]</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2049,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>صيدا حي الكنان</t>
+          <t>صيدا حي الكشك</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2081,7 +2064,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Fuzzy-auto subdivision (66.7) [seeded]</t>
+          <t>Fuzzy-auto subdivision (42.9) [seeded]</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2076,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>صيدا حي المسالخية</t>
+          <t>صيدا حي الكنان</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2108,7 +2091,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Fuzzy-auto subdivision (49.1) [seeded]</t>
+          <t>Fuzzy-auto subdivision (66.7) [seeded]</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2103,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>صيدا حي رجال الاربعين</t>
+          <t>صيدا حي المسالخية</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2135,7 +2118,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Fuzzy-auto subdivision (54.0) [seeded]</t>
+          <t>Fuzzy-auto subdivision (49.1) [seeded]</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2130,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>صيدا حي مار نقولا</t>
+          <t>صيدا حي رجال الاربعين</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2162,7 +2145,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Fuzzy-auto subdivision (60.0) [seeded]</t>
+          <t>Fuzzy-auto subdivision (54.0) [seeded]</t>
         </is>
       </c>
     </row>
@@ -2174,7 +2157,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>صيدا حي مكسر العبد</t>
+          <t>صيدا حي مار نقولا</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2189,51 +2172,51 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Fuzzy-auto subdivision (54.0) [seeded]</t>
+          <t>Fuzzy-auto subdivision (60.0) [seeded]</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Soltan-Yacoub</t>
+          <t>Saïda Dekerman</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>السلطان يعقوب الفوقا</t>
+          <t>صيدا حي مكسر العبد</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>West Bekaa</t>
+          <t>Saida</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Bekaa</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Fuzzy-auto subdivision (79.2) [seeded]</t>
+          <t>Fuzzy-auto subdivision (54.0) [seeded]</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Fourzol</t>
+          <t>Soltan-Yacoub</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>الفرزل الفوقا</t>
+          <t>السلطان يعقوب الفوقا</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Zahleh</t>
+          <t>West Bekaa</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2243,19 +2226,19 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Fuzzy-auto subdivision (90.0) [seeded]</t>
+          <t>Fuzzy-auto subdivision (79.2) [seeded]</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Zahlé Midan</t>
+          <t>Fourzol</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>زحلة الميدان الغربي</t>
+          <t>الفرزل الفوقا</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2270,34 +2253,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Fuzzy-auto subdivision (81.4) [seeded]</t>
+          <t>Fuzzy-auto subdivision (90.0) [seeded]</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Zghorta</t>
+          <t>Zahlé Midan</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>زغرتا حي السيدة الغربي</t>
+          <t>زحلة الميدان الغربي</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Zgharta</t>
+          <t>Zahleh</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Bekaa</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Fuzzy-auto subdivision (83.1) [seeded]</t>
+          <t>Fuzzy-auto subdivision (81.4) [seeded]</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2292,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>زغرتا حي الصليب الجنوبي</t>
+          <t>زغرتا حي السيدة الغربي</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2336,7 +2319,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>زغرتا حي الصليب الشمالي</t>
+          <t>زغرتا حي الصليب الجنوبي</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2363,7 +2346,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>زغرتا حي المعاصر</t>
+          <t>زغرتا حي الصليب الشمالي</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2385,44 +2368,44 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Machghara</t>
+          <t>Zghorta</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>مشغره الفوقا</t>
+          <t>زغرتا حي المعاصر</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>West Bekaa</t>
+          <t>Zgharta</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Bekaa</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Fuzzy-auto subdivision (90.0) [seeded]</t>
+          <t>Fuzzy-auto subdivision (83.1) [seeded]</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Zahlé Al-Rassié</t>
+          <t>Machghara</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>زحلة الراسيه التحتا</t>
+          <t>مشغره الفوقا</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Zahleh</t>
+          <t>West Bekaa</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -2432,34 +2415,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Fuzzy-auto subdivision (73.6) [seeded]</t>
+          <t>Fuzzy-auto subdivision (90.0) [seeded]</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Al-Khodré</t>
+          <t>Zahlé Al-Rassié</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>الخضر الشرقي</t>
+          <t>زحلة الراسيه التحتا</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Baalbeck</t>
+          <t>Zahleh</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Baalbak - Hermel</t>
+          <t>Bekaa</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Fuzzy-auto subdivision (72.0) [unseeded]</t>
+          <t>Fuzzy-auto subdivision (73.6) [seeded]</t>
         </is>
       </c>
     </row>
@@ -2471,7 +2454,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>الخضر الغربي</t>
+          <t>الخضر الشرقي</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -2498,7 +2481,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>الخضر حي الاشعل</t>
+          <t>الخضر الغربي</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -2525,7 +2508,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>الخضر حي الجنوبي</t>
+          <t>الخضر حي الاشعل</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -2552,7 +2535,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>الخضر حي الشعب</t>
+          <t>الخضر حي الجنوبي</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -2574,22 +2557,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Rachaya El-Wadi</t>
+          <t>Al-Khodré</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>راشيا حي الفوقا</t>
+          <t>الخضر حي الشعب</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Rachiaya</t>
+          <t>Baalbeck</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Bekaa</t>
+          <t>Baalbak - Hermel</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -2606,7 +2589,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>راشيا حي الكواسبه</t>
+          <t>راشيا حي الفوقا</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -2633,7 +2616,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>راشيا حي الميدان</t>
+          <t>راشيا حي الكواسبه</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -2648,24 +2631,24 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Fuzzy-auto subdivision (62.1) [unseeded]</t>
+          <t>Fuzzy-auto subdivision (72.0) [unseeded]</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Kab Elias</t>
+          <t>Rachaya El-Wadi</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>قب الياس التحتا</t>
+          <t>راشيا حي الميدان</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Zahleh</t>
+          <t>Rachiaya</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -2675,7 +2658,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Fuzzy-auto subdivision (74.1) [unseeded]</t>
+          <t>Fuzzy-auto subdivision (62.1) [unseeded]</t>
         </is>
       </c>
     </row>
@@ -2687,257 +2670,226 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
+          <t>قب الياس التحتا</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Zahleh</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Bekaa</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Fuzzy-auto subdivision (74.1) [unseeded]</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Kab Elias</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
           <t>قب الياس الفوقا</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="C107" t="inlineStr">
         <is>
           <t>Zahleh</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
+      <c r="D107" t="inlineStr">
         <is>
           <t>Bekaa</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
+      <c r="E107" t="inlineStr">
         <is>
           <t>Fuzzy-auto subdivision (74.8) [unseeded]</t>
         </is>
       </c>
     </row>
-    <row r="107"/>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>DROPPED — arabic village already matched in the same district+mohafaza</t>
-        </is>
-      </c>
-    </row>
+    <row r="108"/>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Arabic Name</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>District</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Mohafaza</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>Matched English</t>
+          <t>REVIEWER-APPROVED MATCHES (--accept overrides)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>اجد عبرين</t>
+          <t>English Name</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>الكورة</t>
+          <t>Arabic Name</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>الشمال</t>
+          <t>District</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Ejdabrine</t>
+          <t>Status</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>افقا</t>
+          <t>Tripoli Al-Kobbé</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>جبيل</t>
+          <t>القبة</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>Tripoli</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Afka</t>
+          <t>applied</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>الحيصه</t>
+          <t>Tripoli Al-Souéka</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>عكار</t>
+          <t>السويقه</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>عكار</t>
+          <t>Tripoli</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Al-Hissa</t>
+          <t>applied</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>الخيام جنوبي</t>
+          <t>Tripoli Al-Zehrieh</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>قضاءي مرجعيون وحاصبيا</t>
+          <t>الزاهرية</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>النبطية</t>
+          <t>Tripoli</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>EL-Khiam</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>الخيام شرقي</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>قضاءي مرجعيون وحاصبيا</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>النبطية</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>EL-Khiam</t>
-        </is>
-      </c>
-    </row>
+          <t>applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="114"/>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>الخيام شمالي</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>قضاءي مرجعيون وحاصبيا</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>النبطية</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>EL-Khiam</t>
+          <t>DROPPED — arabic village already matched in the same district+mohafaza</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>الخيام غربي</t>
+          <t>Arabic Name</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>قضاءي مرجعيون وحاصبيا</t>
+          <t>District</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>النبطية</t>
+          <t>Mohafaza</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>EL-Khiam</t>
+          <t>Matched English</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>الرجمة</t>
+          <t>اجد عبرين</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>عاليه</t>
+          <t>الكورة</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>الشمال</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>El-Rejmeh</t>
+          <t>Ejdabrine</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>الريحانية</t>
+          <t>افقا</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>المنية</t>
+          <t>جبيل</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>الشمال</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Qarhaiya</t>
+          <t>Afka</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>الزواريب</t>
+          <t>الحيصه</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -2952,146 +2904,146 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Al-Zoureiribe</t>
+          <t>Al-Hissa</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>القرنة</t>
+          <t>الخيام جنوبي</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>عكار</t>
+          <t>قضاءي مرجعيون وحاصبيا</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>عكار</t>
+          <t>النبطية</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>El-Korné</t>
+          <t>EL-Khiam</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>القنطره</t>
+          <t>الخيام شرقي</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>عكار</t>
+          <t>قضاءي مرجعيون وحاصبيا</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>عكار</t>
+          <t>النبطية</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>El-Kantara</t>
+          <t>EL-Khiam</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>الكحالة</t>
+          <t>الخيام شمالي</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>عاليه</t>
+          <t>قضاءي مرجعيون وحاصبيا</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>النبطية</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>El-Kahalé</t>
+          <t>EL-Khiam</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>الكنيسة</t>
+          <t>الخيام غربي</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>الشوف</t>
+          <t>قضاءي مرجعيون وحاصبيا</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>النبطية</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>El-Kneissé</t>
+          <t>EL-Khiam</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>الكنيسة</t>
+          <t>الرجمة</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>عكار</t>
+          <t>عاليه</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>عكار</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>El-Kneissé</t>
+          <t>El-Rejmeh</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>الكواشره</t>
+          <t>الريحانية</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>عكار</t>
+          <t>المنية</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>عكار</t>
+          <t>الشمال</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>El-Kouachra</t>
+          <t>Qarhaiya</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>المسعوديه</t>
+          <t>الزواريب</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3106,14 +3058,14 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Al-Massoudié</t>
+          <t>Al-Zoureiribe</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>المقيطع</t>
+          <t>القرنة</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3128,14 +3080,14 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Al-Moukaiteh</t>
+          <t>El-Korné</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>النفيسه</t>
+          <t>القنطره</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3150,41 +3102,41 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>El-Nfeicé</t>
+          <t>El-Kantara</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>النهرية وبستان الحرش</t>
+          <t>الكحالة</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>عكار</t>
+          <t>عاليه</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>عكار</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Mazraet-El-Nahrieh</t>
+          <t>El-Kahalé</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>بخعاز</t>
+          <t>الكنيسة</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>جبيل</t>
+          <t>الشوف</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -3194,173 +3146,173 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Bakhaase</t>
+          <t>El-Kneissé</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>تبنين حي آل بري</t>
+          <t>الكنيسة</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>بنت جبيل</t>
+          <t>عكار</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>النبطية</t>
+          <t>عكار</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Tibnine</t>
+          <t>El-Kneissé</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>تبنين حي التحتاني</t>
+          <t>الكواشره</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>بنت جبيل</t>
+          <t>عكار</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>النبطية</t>
+          <t>عكار</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Tibnine</t>
+          <t>El-Kouachra</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>تبنين حي الفوقاني</t>
+          <t>المسعوديه</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>بنت جبيل</t>
+          <t>عكار</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>النبطية</t>
+          <t>عكار</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Tibnine</t>
+          <t>Al-Massoudié</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>تبنين حي الكاثوليك</t>
+          <t>المقيطع</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>بنت جبيل</t>
+          <t>عكار</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>النبطية</t>
+          <t>عكار</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Tibnine</t>
+          <t>Al-Moukaiteh</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>تل الاخضر</t>
+          <t>النفيسه</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>زحلة</t>
+          <t>عكار</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>البقاع</t>
+          <t>عكار</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Tal-el-Akhdar</t>
+          <t>El-Nfeicé</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>جباع</t>
+          <t>النهرية وبستان الحرش</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>الشوف</t>
+          <t>عكار</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>عكار</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>El-Bkaya</t>
+          <t>Mazraet-El-Nahrieh</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>جديدة القيطع</t>
+          <t>بخعاز</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>عكار</t>
+          <t>جبيل</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>عكار</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Al-Jédidé | Jedeidet-El-Kayteh</t>
+          <t>Bakhaase</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>حاصبيا حي السراي</t>
+          <t>تبنين حي آل بري</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>قضاءي مرجعيون وحاصبيا</t>
+          <t>بنت جبيل</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -3370,19 +3322,19 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Hasbaya</t>
+          <t>Tibnine</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>حاصبيا حي العين</t>
+          <t>تبنين حي التحتاني</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>قضاءي مرجعيون وحاصبيا</t>
+          <t>بنت جبيل</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -3392,19 +3344,19 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Hasbaya</t>
+          <t>Tibnine</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>حاصبيا حي الفوقاني</t>
+          <t>تبنين حي الفوقاني</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>قضاءي مرجعيون وحاصبيا</t>
+          <t>بنت جبيل</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -3414,19 +3366,19 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Hasbaya</t>
+          <t>Tibnine</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>حاصبيا حي صفيفة</t>
+          <t>تبنين حي الكاثوليك</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>قضاءي مرجعيون وحاصبيا</t>
+          <t>بنت جبيل</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -3436,58 +3388,58 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Hasbaya</t>
+          <t>Tibnine</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>زوق الحصينه</t>
+          <t>تل الاخضر</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>عكار</t>
+          <t>زحلة</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>عكار</t>
+          <t>البقاع</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Zouk-El-Hosmieh et Dahr Ayasse</t>
+          <t>Tal-el-Akhdar</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>زوق حداره</t>
+          <t>جباع</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>عكار</t>
+          <t>الشوف</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>عكار</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Dahr Haddara</t>
+          <t>El-Bkaya</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>سفينة القيطع</t>
+          <t>جديدة القيطع</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3502,102 +3454,102 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Safiné-El-Kayteh</t>
+          <t>Al-Jédidé | Jedeidet-El-Kayteh</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>سلعا</t>
+          <t>حاصبيا حي السراي</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>صور</t>
+          <t>قضاءي مرجعيون وحاصبيا</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>الجنوب</t>
+          <t>النبطية</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Salha</t>
+          <t>Hasbaya</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>عماره</t>
+          <t>حاصبيا حي العين</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>عكار</t>
+          <t>قضاءي مرجعيون وحاصبيا</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>عكار</t>
+          <t>النبطية</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Al-Amara</t>
+          <t>Hasbaya</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>عيحا</t>
+          <t>حاصبيا حي الفوقاني</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>قضاءي البقاع الغربي وراشيا</t>
+          <t>قضاءي مرجعيون وحاصبيا</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>البقاع</t>
+          <t>النبطية</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Aïha</t>
+          <t>Hasbaya</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>عيمار</t>
+          <t>حاصبيا حي صفيفة</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>الضنية</t>
+          <t>قضاءي مرجعيون وحاصبيا</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>الشمال</t>
+          <t>النبطية</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Omar</t>
+          <t>Hasbaya</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>غزيله</t>
+          <t>زوق الحصينه</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -3612,14 +3564,14 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>El-Ghozaili</t>
+          <t>Zouk-El-Hosmieh et Dahr Ayasse</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>قليعات</t>
+          <t>زوق حداره</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -3634,14 +3586,14 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Al-Kleiat</t>
+          <t>Dahr Haddara</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>كوشا</t>
+          <t>سفينة القيطع</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -3656,123 +3608,277 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Al-Khraibé (Kousha)</t>
+          <t>Safiné-El-Kayteh</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>مراح السفيرة</t>
+          <t>سلعا</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>الضنية</t>
+          <t>صور</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>الشمال</t>
+          <t>الجنوب</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Mrah-El-Sfiré</t>
+          <t>Salha</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>مزرعة طبايا</t>
+          <t>عماره</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>قرى صيدا</t>
+          <t>عكار</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>الجنوب</t>
+          <t>عكار</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Arab Tabbaya</t>
-        </is>
-      </c>
-    </row>
-    <row r="154"/>
+          <t>Al-Amara</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>عيحا</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>قضاءي البقاع الغربي وراشيا</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>البقاع</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Aïha</t>
+        </is>
+      </c>
+    </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>CONFLICTS — one arabic+district claimed by 2+ english names (resolve in v5 source)</t>
+          <t>عيمار</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>الضنية</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>الشمال</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Omar</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Arabic (normalized)</t>
+          <t>غزيله</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>District</t>
+          <t>عكار</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Mohafaza</t>
+          <t>عكار</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>English names</t>
+          <t>El-Ghozaili</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>جديده القيطع</t>
+          <t>قليعات</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Akkar</t>
+          <t>عكار</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Akkar</t>
+          <t>عكار</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Al-Jédidé | Jedeidet-El-Kayteh</t>
+          <t>Al-Kleiat</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
+          <t>كوشا</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>عكار</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>عكار</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Al-Khraibé (Kousha)</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>مراح السفيرة</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>الضنية</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>الشمال</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Mrah-El-Sfiré</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>مزرعة طبايا</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>قرى صيدا</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>الجنوب</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Arab Tabbaya</t>
+        </is>
+      </c>
+    </row>
+    <row r="161"/>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>CONFLICTS — one arabic+district claimed by 2+ english names (resolve in v5 source)</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Arabic (normalized)</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>District</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Mohafaza</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>English names</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>جديده القيطع</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Akkar</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Akkar</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Al-Jédidé | Jedeidet-El-Kayteh</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
           <t>كفر قاهل</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr">
+      <c r="B165" t="inlineStr">
         <is>
           <t>Koura</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr">
+      <c r="C165" t="inlineStr">
         <is>
           <t>North</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr">
+      <c r="D165" t="inlineStr">
         <is>
           <t>Kfar Hazir | Kfar Kahel</t>
         </is>
@@ -45500,6 +45606,11 @@
           <t>Tripoli Al-Kobbé</t>
         </is>
       </c>
+      <c r="B1607" t="inlineStr">
+        <is>
+          <t>القبة</t>
+        </is>
+      </c>
       <c r="C1607" t="inlineStr">
         <is>
           <t>Tripoli</t>
@@ -45512,7 +45623,7 @@
       </c>
       <c r="E1607" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Reviewer-approved</t>
         </is>
       </c>
     </row>
@@ -45576,6 +45687,11 @@
           <t>Tripoli Al-Souéka</t>
         </is>
       </c>
+      <c r="B1610" t="inlineStr">
+        <is>
+          <t>السويقه</t>
+        </is>
+      </c>
       <c r="C1610" t="inlineStr">
         <is>
           <t>Tripoli</t>
@@ -45588,7 +45704,7 @@
       </c>
       <c r="E1610" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Reviewer-approved</t>
         </is>
       </c>
     </row>
@@ -45647,6 +45763,11 @@
           <t>Tripoli Al-Zehrieh</t>
         </is>
       </c>
+      <c r="B1613" t="inlineStr">
+        <is>
+          <t>الزاهرية</t>
+        </is>
+      </c>
       <c r="C1613" t="inlineStr">
         <is>
           <t>Tripoli</t>
@@ -45659,7 +45780,7 @@
       </c>
       <c r="E1613" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Reviewer-approved</t>
         </is>
       </c>
     </row>
@@ -81131,6 +81252,11 @@
           <t>الزاهرية</t>
         </is>
       </c>
+      <c r="B1622" t="inlineStr">
+        <is>
+          <t>Tripoli Al-Zehrieh</t>
+        </is>
+      </c>
       <c r="C1622" t="inlineStr">
         <is>
           <t>مدينة طرابلس</t>
@@ -81148,6 +81274,11 @@
           <t>السويقه</t>
         </is>
       </c>
+      <c r="B1623" t="inlineStr">
+        <is>
+          <t>Tripoli Al-Souéka</t>
+        </is>
+      </c>
       <c r="C1623" t="inlineStr">
         <is>
           <t>مدينة طرابلس</t>
@@ -81163,6 +81294,11 @@
       <c r="A1624" t="inlineStr">
         <is>
           <t>القبة</t>
+        </is>
+      </c>
+      <c r="B1624" t="inlineStr">
+        <is>
+          <t>Tripoli Al-Kobbé</t>
         </is>
       </c>
       <c r="C1624" t="inlineStr">
@@ -81292,7 +81428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F85"/>
+  <dimension ref="A1:F82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83144,162 +83280,96 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Tripoli Al-Kobbé</t>
+          <t>Wadi Abou Youssef</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Tripoli</t>
+          <t>Chouf</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Mount Lebanon</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>القبة (مدينة طرابلس) [85.7]</t>
+          <t>وادي دير دوريت (الشوف) [85.5]</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Tripoli Al-Souéka</t>
+          <t>Wadi-el-Arayeche</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Tripoli</t>
+          <t>Zahleh</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Bekaa</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>السويقه (مدينة طرابلس) [80.0]</t>
+          <t>زحلة وادي العرايش (زحلة) [85.5]</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Tripoli Al-Zehrieh</t>
+          <t>Zahlé (Terres)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Tripoli</t>
+          <t>Zahleh</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Bekaa</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>الزاهرية (مدينة طرابلس) [83.3]</t>
+          <t>زحلة وادي العرايش (زحلة) [85.7]</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Wadi Abou Youssef</t>
+          <t>Zahlé Maallaka Kerek</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Chouf</t>
+          <t>Zahleh</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Mount Lebanon</t>
+          <t>Bekaa</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>وادي دير دوريت (الشوف) [85.5]</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Wadi-el-Arayeche</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Zahleh</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Bekaa</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>زحلة وادي العرايش (زحلة) [85.5]</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Zahlé (Terres)</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Zahleh</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Bekaa</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>زحلة وادي العرايش (زحلة) [85.7]</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Zahlé Maallaka Kerek</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Zahleh</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Bekaa</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
           <t>زحلة المعلقه (زحلة) [85.7]</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>زحلة كرك نوح (زحلة) [80.0]</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>زحلة المعلقه الشمالي (زحلة) [77.1]</t>
         </is>
@@ -83316,7 +83386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D653"/>
+  <dimension ref="A1:D647"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -90653,7 +90723,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Tripoli Al-Kobbé</t>
+          <t>Tripoli Al-Tal</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -90675,7 +90745,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Tripoli Al-Souéka</t>
+          <t>Tripoli Jardins</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -90697,7 +90767,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Tripoli Al-Tal</t>
+          <t>Tripoli Zeitoun</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -90719,17 +90789,17 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Tripoli Al-Zehrieh</t>
+          <t>Al-Djeziré</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Tripoli</t>
+          <t>West Bekaa</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Bekaa</t>
         </is>
       </c>
     </row>
@@ -90741,17 +90811,17 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Tripoli Jardins</t>
+          <t>Al-Istable</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Tripoli</t>
+          <t>West Bekaa</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Bekaa</t>
         </is>
       </c>
     </row>
@@ -90763,17 +90833,17 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Tripoli Zeitoun</t>
+          <t>Al-Wakf</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Tripoli</t>
+          <t>West Bekaa</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Bekaa</t>
         </is>
       </c>
     </row>
@@ -90785,7 +90855,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Al-Djeziré</t>
+          <t>Ammik et "Jouret Ammik"</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -90807,7 +90877,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Al-Istable</t>
+          <t>Aïn-el-Tiné</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -90829,7 +90899,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Al-Wakf</t>
+          <t>Chouberkié "Ammik"</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -90851,7 +90921,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Ammik et "Jouret Ammik"</t>
+          <t>Dair Tahmiche</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -90873,7 +90943,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Aïn-el-Tiné</t>
+          <t>Deir-Aïn-el-Jaouzé</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -90895,7 +90965,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Chouberkié "Ammik"</t>
+          <t>Harime-el-Soughra</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -90917,7 +90987,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Dair Tahmiche</t>
+          <t>Khiara-el-Atika</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -90939,12 +91009,12 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Deir-Aïn-el-Jaouzé</t>
+          <t>Al-Mazraa</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>West Bekaa</t>
+          <t>Zahleh</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -90961,12 +91031,12 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Harime-el-Soughra</t>
+          <t>Chouberkié  Tabet</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>West Bekaa</t>
+          <t>Zahleh</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -90983,12 +91053,12 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Khiara-el-Atika</t>
+          <t>Conflict</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>West Bekaa</t>
+          <t>Zahleh</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -91005,7 +91075,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Al-Mazraa</t>
+          <t>Haouche Kaissar</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -91027,7 +91097,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Chouberkié  Tabet</t>
+          <t>Haouche Sayadi</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -91049,7 +91119,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Conflict</t>
+          <t>Haouche-al-Omara (Terres)</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -91071,7 +91141,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Haouche Kaissar</t>
+          <t>Hochemoche</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -91093,7 +91163,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Haouche Sayadi</t>
+          <t>Ksara</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -91115,7 +91185,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Haouche-al-Omara (Terres)</t>
+          <t>Maallaka (Terres)</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -91137,7 +91207,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Hochemoche</t>
+          <t>Maazraat-el-Ramtanieh</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -91159,7 +91229,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Ksara</t>
+          <t>Mandara</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -91181,7 +91251,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Maallaka (Terres)</t>
+          <t>Mejdel-Anjar</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -91203,7 +91273,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Maazraat-el-Ramtanieh</t>
+          <t>Nasriyat Rizk</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -91225,7 +91295,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Mandara</t>
+          <t>Tal-al-Amara</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -91247,7 +91317,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Mejdel-Anjar</t>
+          <t>Tchiflik Eddé</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -91269,7 +91339,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Nasriyat Rizk</t>
+          <t>Tchiflik Kikano</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -91291,7 +91361,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Tal-al-Amara</t>
+          <t>Wadi-el-Arayeche</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -91313,7 +91383,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Tchiflik Eddé</t>
+          <t>Zahlé (Terres)</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -91335,7 +91405,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Tchiflik Kikano</t>
+          <t>Zahlé Maallaka Kerek</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -91357,7 +91427,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Wadi-el-Arayeche</t>
+          <t>Zahlé Mar Gérios</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -91379,7 +91449,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Zahlé (Terres)</t>
+          <t>Zebdol</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -91401,17 +91471,17 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Zahlé Maallaka Kerek</t>
+          <t>Aadoua</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Zahleh</t>
+          <t>Zgharta</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>Bekaa</t>
+          <t>North</t>
         </is>
       </c>
     </row>
@@ -91423,17 +91493,17 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Zahlé Mar Gérios</t>
+          <t>Al-Harik</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Zahleh</t>
+          <t>Zgharta</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>Bekaa</t>
+          <t>North</t>
         </is>
       </c>
     </row>
@@ -91445,17 +91515,17 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Zebdol</t>
+          <t>Al-Jdeidé</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Zahleh</t>
+          <t>Zgharta</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>Bekaa</t>
+          <t>North</t>
         </is>
       </c>
     </row>
@@ -91467,7 +91537,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Aadoua</t>
+          <t>Al-Khaldyé</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -91489,7 +91559,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Al-Harik</t>
+          <t>Arbet Koshaya</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -91511,7 +91581,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Al-Jdeidé</t>
+          <t>Ardate</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -91533,7 +91603,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Al-Khaldyé</t>
+          <t>Bsebhil</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -91555,7 +91625,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Arbet Koshaya</t>
+          <t>Danhi</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -91577,7 +91647,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Ardate</t>
+          <t>Ehden</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -91599,7 +91669,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Bsebhil</t>
+          <t>Ejbeh</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -91621,7 +91691,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Danhi</t>
+          <t>El-Tellé</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -91643,7 +91713,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Ehden</t>
+          <t>Mazraat Ejbeh</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -91665,7 +91735,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Ejbeh</t>
+          <t>Mazraat Jneide</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -91687,7 +91757,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>El-Tellé</t>
+          <t>Mejdlaya</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -91709,7 +91779,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Mazraat Ejbeh</t>
+          <t>Merh Kfarsghabe</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -91731,7 +91801,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Mazraat Jneide</t>
+          <t>Sakhra</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -91748,66 +91818,66 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Mejdlaya</t>
+          <t>راشكده</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Zgharta</t>
+          <t>البترون</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>الشمال</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Merh Kfarsghabe</t>
+          <t>عورا</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Zgharta</t>
+          <t>البترون</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>الشمال</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Sakhra</t>
+          <t>غوما</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Zgharta</t>
+          <t>البترون</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>الشمال</t>
         </is>
       </c>
     </row>
@@ -91819,7 +91889,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>راشكده</t>
+          <t>قندولا</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -91841,17 +91911,17 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>عورا</t>
+          <t>الدبية</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>البترون</t>
+          <t>الشوف</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>الشمال</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -91863,17 +91933,17 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>غوما</t>
+          <t>المحتقره دير المخلص</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>البترون</t>
+          <t>الشوف</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>الشمال</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -91885,17 +91955,17 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>قندولا</t>
+          <t>الناعمه</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>البترون</t>
+          <t>الشوف</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>الشمال</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -91907,7 +91977,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>الدبية</t>
+          <t>بقعاتا</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -91929,7 +91999,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>المحتقره دير المخلص</t>
+          <t>حارة الناعمه</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -91951,7 +92021,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>الناعمه</t>
+          <t>حارة بعاصير</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -91973,7 +92043,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>بقعاتا</t>
+          <t>عين الاسد والشميس</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -91995,7 +92065,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>حارة الناعمه</t>
+          <t>عين الحور</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -92017,7 +92087,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>حارة بعاصير</t>
+          <t>كليليه</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -92039,7 +92109,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>عين الاسد والشميس</t>
+          <t>مرج برجا</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -92061,7 +92131,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>عين الحور</t>
+          <t>وادي دير دوريت</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -92083,17 +92153,17 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>كليليه</t>
+          <t>الروضة</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>الشوف</t>
+          <t>الضنية</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>الشمال</t>
         </is>
       </c>
     </row>
@@ -92105,17 +92175,17 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>مرج برجا</t>
+          <t>المطل</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>الشوف</t>
+          <t>الضنية</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>الشمال</t>
         </is>
       </c>
     </row>
@@ -92127,17 +92197,17 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>وادي دير دوريت</t>
+          <t>حرف السياد</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>الشوف</t>
+          <t>الضنية</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>الشمال</t>
         </is>
       </c>
     </row>
@@ -92149,7 +92219,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>الروضة</t>
+          <t>عزقي</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -92171,7 +92241,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>المطل</t>
+          <t>قزحيا</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -92193,7 +92263,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>حرف السياد</t>
+          <t>كرم المهر</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -92215,7 +92285,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>عزقي</t>
+          <t>كفربنين</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -92237,7 +92307,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>قزحيا</t>
+          <t>نمرين</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -92259,12 +92329,12 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>كرم المهر</t>
+          <t>البحصاص</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>الضنية</t>
+          <t>الكورة</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
@@ -92281,12 +92351,12 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>كفربنين</t>
+          <t>حارة الخاصة</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>الضنية</t>
+          <t>الكورة</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -92303,12 +92373,12 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>نمرين</t>
+          <t>ضهر العين</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>الضنية</t>
+          <t>الكورة</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
@@ -92325,7 +92395,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>البحصاص</t>
+          <t>ضهور الهوا</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -92347,17 +92417,17 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>حارة الخاصة</t>
+          <t>الرابية</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>الكورة</t>
+          <t>المتن</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>الشمال</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -92369,17 +92439,17 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>ضهر العين</t>
+          <t>سد البوشريه</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>الكورة</t>
+          <t>المتن</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>الشمال</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -92391,17 +92461,17 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>ضهور الهوا</t>
+          <t>مزرعة بنابيل</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>الكورة</t>
+          <t>المتن</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>الشمال</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -92413,17 +92483,17 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>الرابية</t>
+          <t>كفروة</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>المتن</t>
+          <t>النبطية</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>النبطية</t>
         </is>
       </c>
     </row>
@@ -92435,17 +92505,17 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>سد البوشريه</t>
+          <t>المغر وبلا</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>المتن</t>
+          <t>بشري</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>الشمال</t>
         </is>
       </c>
     </row>
@@ -92457,12 +92527,12 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>مزرعة بنابيل</t>
+          <t>الحدث شمالي</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>المتن</t>
+          <t>بعبدا</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
@@ -92479,17 +92549,17 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>كفروة</t>
+          <t>الحدث قبلي</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>النبطية</t>
+          <t>بعبدا</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>النبطية</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -92501,17 +92571,17 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>المغر وبلا</t>
+          <t>الشياح حي الكنيسة</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>بشري</t>
+          <t>بعبدا</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>الشمال</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -92523,7 +92593,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>الحدث شمالي</t>
+          <t>الشياح حي كرم الزيتون</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -92545,7 +92615,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>الحدث قبلي</t>
+          <t>الغبيري بئر حسن</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -92567,7 +92637,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>الشياح حي الكنيسة</t>
+          <t>الغبيري حي الجامع</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -92589,7 +92659,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>الشياح حي كرم الزيتون</t>
+          <t>الفياضية</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -92611,7 +92681,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>الغبيري بئر حسن</t>
+          <t>القلعه</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -92633,7 +92703,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>الغبيري حي الجامع</t>
+          <t>المريجه</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -92655,7 +92725,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>الفياضية</t>
+          <t>تحويطة النهر</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -92677,7 +92747,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>القلعه</t>
+          <t>حارة البطم</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -92699,7 +92769,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>المريجه</t>
+          <t>حارة حريك قرانوح</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -92721,7 +92791,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>تحويطة النهر</t>
+          <t>دير مار الياس الكحلونية</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -92743,7 +92813,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>حارة البطم</t>
+          <t>سبنيه</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -92765,7 +92835,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>حارة حريك قرانوح</t>
+          <t>قبيع</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -92787,17 +92857,17 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>دير مار الياس الكحلونية</t>
+          <t>حداثا</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>بعبدا</t>
+          <t>بنت جبيل</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>النبطية</t>
         </is>
       </c>
     </row>
@@ -92809,17 +92879,17 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>سبنيه</t>
+          <t>عيتا الجبل</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>بعبدا</t>
+          <t>بنت جبيل</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>النبطية</t>
         </is>
       </c>
     </row>
@@ -92831,12 +92901,12 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>قبيع</t>
+          <t>الجليسه</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>بعبدا</t>
+          <t>جبيل</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
@@ -92853,17 +92923,17 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>حداثا</t>
+          <t>العاقورة - م</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>بنت جبيل</t>
+          <t>جبيل</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>النبطية</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -92875,17 +92945,17 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>عيتا الجبل</t>
+          <t>الفيدار</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>بنت جبيل</t>
+          <t>جبيل</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>النبطية</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -92897,7 +92967,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>الجليسه</t>
+          <t>المزاريب</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -92919,7 +92989,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>العاقورة - م</t>
+          <t>المنصف</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -92941,7 +93011,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>الفيدار</t>
+          <t>بنتاعل</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -92963,7 +93033,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>المزاريب</t>
+          <t>دملصا</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -92985,7 +93055,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>المنصف</t>
+          <t>دير القطاره</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -93007,7 +93077,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>بنتاعل</t>
+          <t>سرعيتا</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -93029,7 +93099,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>دملصا</t>
+          <t>عين الدلبة</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -93051,7 +93121,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>دير القطاره</t>
+          <t>عين الشلال</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -93073,7 +93143,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>سرعيتا</t>
+          <t>عين الغويبة</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -93095,7 +93165,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>عين الدلبة</t>
+          <t>قرطبا الشمالية</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -93117,7 +93187,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>عين الشلال</t>
+          <t>كفر مسحون</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -93139,7 +93209,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>عين الغويبة</t>
+          <t>مزرعة السياد</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -93161,17 +93231,17 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>قرطبا الشمالية</t>
+          <t>بحنين - كفرتعلا</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>جبيل</t>
+          <t>جزين</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>الجنوب</t>
         </is>
       </c>
     </row>
@@ -93183,17 +93253,17 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>كفر مسحون</t>
+          <t>عين مجدلين</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>جبيل</t>
+          <t>جزين</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>الجنوب</t>
         </is>
       </c>
     </row>
@@ -93205,17 +93275,17 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>مزرعة السياد</t>
+          <t>لبعه</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>جبيل</t>
+          <t>جزين</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>الجنوب</t>
         </is>
       </c>
     </row>
@@ -93227,17 +93297,17 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>بحنين - كفرتعلا</t>
+          <t>الكرمة</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>جزين</t>
+          <t>زحلة</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>الجنوب</t>
+          <t>البقاع</t>
         </is>
       </c>
     </row>
@@ -93249,17 +93319,17 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>عين مجدلين</t>
+          <t>بتياس</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>جزين</t>
+          <t>زحلة</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>الجنوب</t>
+          <t>البقاع</t>
         </is>
       </c>
     </row>
@@ -93271,17 +93341,17 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>لبعه</t>
+          <t>جلالا</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>جزين</t>
+          <t>زحلة</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>الجنوب</t>
+          <t>البقاع</t>
         </is>
       </c>
     </row>
@@ -93293,7 +93363,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>الكرمة</t>
+          <t>حاجي حببلي</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -93315,7 +93385,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>بتياس</t>
+          <t>حي السلم</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -93337,7 +93407,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>جلالا</t>
+          <t>حي الفيكاني</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -93359,7 +93429,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>حاجي حببلي</t>
+          <t>خضر بك</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -93381,7 +93451,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>حي السلم</t>
+          <t>زحلة المعلقه</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -93403,7 +93473,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>حي الفيكاني</t>
+          <t>زحلة المعلقه الشمالي</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -93425,7 +93495,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>خضر بك</t>
+          <t>زحلة حي السيدة</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -93447,7 +93517,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>زحلة المعلقه</t>
+          <t>زحلة كرك نوح</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -93469,7 +93539,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>زحلة المعلقه الشمالي</t>
+          <t>زحلة مار مخايل</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -93491,7 +93561,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>زحلة حي السيدة</t>
+          <t>زحلة وادي العرايش</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -93513,7 +93583,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>زحلة كرك نوح</t>
+          <t>شهابية الفاعور</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -93535,7 +93605,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>زحلة مار مخايل</t>
+          <t>كابوسية</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -93557,7 +93627,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>زحلة وادي العرايش</t>
+          <t>يوغون اولوك</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -93579,17 +93649,17 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>شهابية الفاعور</t>
+          <t>اجبع</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>زحلة</t>
+          <t>زغرتا</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>البقاع</t>
+          <t>الشمال</t>
         </is>
       </c>
     </row>
@@ -93601,17 +93671,17 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>كابوسية</t>
+          <t>اسلوت</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>زحلة</t>
+          <t>زغرتا</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>البقاع</t>
+          <t>الشمال</t>
         </is>
       </c>
     </row>
@@ -93623,17 +93693,17 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>يوغون اولوك</t>
+          <t>القادريه</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>زحلة</t>
+          <t>زغرتا</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>البقاع</t>
+          <t>الشمال</t>
         </is>
       </c>
     </row>
@@ -93645,7 +93715,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>اجبع</t>
+          <t>بيت عبيد</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -93667,7 +93737,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>اسلوت</t>
+          <t>بيت عوكر</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -93689,7 +93759,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>القادريه</t>
+          <t>حارة الفوار</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -93711,7 +93781,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>بيت عبيد</t>
+          <t>حرف ارده</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -93733,7 +93803,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>بيت عوكر</t>
+          <t>حرف مزيارة</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -93755,7 +93825,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>حارة الفوار</t>
+          <t>عربة قزحيا</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -93777,7 +93847,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>حرف ارده</t>
+          <t>مزرعة الفريديس</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
@@ -93799,7 +93869,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>حرف مزيارة</t>
+          <t>مزرعة حوقا</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -93821,17 +93891,17 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>عربة قزحيا</t>
+          <t>البازوريه</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>زغرتا</t>
+          <t>صور</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>الشمال</t>
+          <t>الجنوب</t>
         </is>
       </c>
     </row>
@@ -93843,17 +93913,17 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>مزرعة الفريديس</t>
+          <t>البرغليه</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>زغرتا</t>
+          <t>صور</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>الشمال</t>
+          <t>الجنوب</t>
         </is>
       </c>
     </row>
@@ -93865,17 +93935,17 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>مزرعة حوقا</t>
+          <t>البساتين</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>زغرتا</t>
+          <t>صور</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>الشمال</t>
+          <t>الجنوب</t>
         </is>
       </c>
     </row>
@@ -93887,7 +93957,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>البازوريه</t>
+          <t>البص  قسم 1</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -93909,7 +93979,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>البرغليه</t>
+          <t>البص  قسم 3</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -93931,7 +94001,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>البساتين</t>
+          <t>البص قسم 5</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -93953,7 +94023,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>البص  قسم 1</t>
+          <t>الحميري</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -93975,7 +94045,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>البص  قسم 3</t>
+          <t>الرشيديه</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -93997,7 +94067,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>البص قسم 5</t>
+          <t>الزلوطية</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -94019,7 +94089,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>الحميري</t>
+          <t>السماعية</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -94041,7 +94111,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>الرشيديه</t>
+          <t>الشهابية</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -94063,7 +94133,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>الزلوطية</t>
+          <t>الظهيرة</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
@@ -94085,7 +94155,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>السماعية</t>
+          <t>المالكية</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -94107,7 +94177,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>الشهابية</t>
+          <t>بثتيات</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -94129,7 +94199,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>الظهيرة</t>
+          <t>شبريحا</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -94151,7 +94221,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>المالكية</t>
+          <t>شمع</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -94173,7 +94243,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>بثتيات</t>
+          <t>صور حي الارثوذكس</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -94195,7 +94265,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>شبريحا</t>
+          <t>صور حي الجامع</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -94217,7 +94287,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>شمع</t>
+          <t>صور حي الجورة</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -94239,7 +94309,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>صور حي الارثوذكس</t>
+          <t>صور حي الحسينية</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -94261,7 +94331,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>صور حي الجامع</t>
+          <t>صور حي الكاثوليك</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -94283,7 +94353,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>صور حي الجورة</t>
+          <t>صور حي المصاروي</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -94305,7 +94375,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>صور حي الحسينية</t>
+          <t>صور حي المنارة</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -94327,7 +94397,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>صور حي الكاثوليك</t>
+          <t>صور حي الموارنة</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -94349,7 +94419,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>صور حي المصاروي</t>
+          <t>عين الزرقا</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -94371,7 +94441,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>صور حي المنارة</t>
+          <t>محرونه</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -94393,17 +94463,17 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>صور حي الموارنة</t>
+          <t>البساتين</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>صور</t>
+          <t>عاليه</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>الجنوب</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -94415,17 +94485,17 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>عين الزرقا</t>
+          <t>التعزانية</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>صور</t>
+          <t>عاليه</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>الجنوب</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -94437,17 +94507,17 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>محرونه</t>
+          <t>جسر القاضي</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>صور</t>
+          <t>عاليه</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>الجنوب</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -94459,7 +94529,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>البساتين</t>
+          <t>عاليه قبلي</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -94481,7 +94551,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>التعزانية</t>
+          <t>عاليه وسطاني</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
@@ -94503,7 +94573,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>جسر القاضي</t>
+          <t>عين الفريديس</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -94525,7 +94595,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>عاليه قبلي</t>
+          <t>محطة بحمدون</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
@@ -94547,17 +94617,17 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>عاليه وسطاني</t>
+          <t>البساتين</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>عاليه</t>
+          <t>عكار</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>عكار</t>
         </is>
       </c>
     </row>
@@ -94569,17 +94639,17 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>عين الفريديس</t>
+          <t>البقيعة</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>عاليه</t>
+          <t>عكار</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>عكار</t>
         </is>
       </c>
     </row>
@@ -94591,17 +94661,17 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>محطة بحمدون</t>
+          <t>الحويش</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>عاليه</t>
+          <t>عكار</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>جبل لبنان</t>
+          <t>عكار</t>
         </is>
       </c>
     </row>
@@ -94613,7 +94683,7 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>البساتين</t>
+          <t>الدوسه</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -94635,7 +94705,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>البقيعة</t>
+          <t>السهلة</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -94657,7 +94727,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>الحويش</t>
+          <t>الشيخ عياش</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -94679,7 +94749,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>الدوسه</t>
+          <t>العماير</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -94701,7 +94771,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>السهلة</t>
+          <t>العوادة</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -94723,7 +94793,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>الشيخ عياش</t>
+          <t>الفرض</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -94745,7 +94815,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>العماير</t>
+          <t>القبيات الذوق</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -94767,7 +94837,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>العوادة</t>
+          <t>القبيات الضهر</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -94789,7 +94859,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>الفرض</t>
+          <t>القبيات الغربية</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -94811,7 +94881,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>القبيات الذوق</t>
+          <t>القبيات القطلبه</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -94833,7 +94903,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>القبيات الضهر</t>
+          <t>القبيات غوايا</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -94855,7 +94925,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>القبيات الغربية</t>
+          <t>القبيات مرتموره</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -94877,7 +94947,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>القبيات القطلبه</t>
+          <t>المونسة</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
@@ -94899,7 +94969,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>القبيات غوايا</t>
+          <t>الهيشة</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -94921,7 +94991,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>القبيات مرتموره</t>
+          <t>برج العرب</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -94943,7 +95013,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>المونسة</t>
+          <t>بني صخر</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -94965,7 +95035,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>الهيشة</t>
+          <t>بيت الحاج</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -94987,7 +95057,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>برج العرب</t>
+          <t>تل معيان</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -95009,7 +95079,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>بني صخر</t>
+          <t>تلبيبة</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -95031,7 +95101,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>بيت الحاج</t>
+          <t>جبل المنصورة</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -95053,7 +95123,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>تل معيان</t>
+          <t>جرمنايا</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -95075,7 +95145,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>تلبيبة</t>
+          <t>خربة الجرد</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -95097,7 +95167,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>جبل المنصورة</t>
+          <t>خريبة الجندي</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
@@ -95119,7 +95189,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>جرمنايا</t>
+          <t>خط البترول</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -95141,7 +95211,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>خربة الجرد</t>
+          <t>رجم عيسى</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
@@ -95163,7 +95233,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>خريبة الجندي</t>
+          <t>ضهر القنبر</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -95185,7 +95255,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>خط البترول</t>
+          <t>عبودية</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -95207,7 +95277,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>رجم عيسى</t>
+          <t>عين الذهب</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
@@ -95229,7 +95299,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>ضهر القنبر</t>
+          <t>قنية</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
@@ -95251,7 +95321,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>عبودية</t>
+          <t>كرم زبدين</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
@@ -95273,7 +95343,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>عين الذهب</t>
+          <t>مراح الخوخ</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -95295,17 +95365,17 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>قنية</t>
+          <t>الحجة</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>عكار</t>
+          <t>قرى صيدا</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>عكار</t>
+          <t>الجنوب</t>
         </is>
       </c>
     </row>
@@ -95317,17 +95387,17 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>كرم زبدين</t>
+          <t>القنيطرة</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>عكار</t>
+          <t>قرى صيدا</t>
         </is>
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>عكار</t>
+          <t>الجنوب</t>
         </is>
       </c>
     </row>
@@ -95339,17 +95409,17 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>مراح الخوخ</t>
+          <t>المعمرية</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>عكار</t>
+          <t>قرى صيدا</t>
         </is>
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>عكار</t>
+          <t>الجنوب</t>
         </is>
       </c>
     </row>
@@ -95361,7 +95431,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>الحجة</t>
+          <t>المية ومية</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
@@ -95383,7 +95453,7 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>القنيطرة</t>
+          <t>كوثرية السياد</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
@@ -95405,17 +95475,17 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>المعمرية</t>
+          <t>الروضة</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>قرى صيدا</t>
+          <t>قضاءي البقاع الغربي وراشيا</t>
         </is>
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>الجنوب</t>
+          <t>البقاع</t>
         </is>
       </c>
     </row>
@@ -95427,17 +95497,17 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>المية ومية</t>
+          <t>الشبرقية</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>قرى صيدا</t>
+          <t>قضاءي البقاع الغربي وراشيا</t>
         </is>
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>الجنوب</t>
+          <t>البقاع</t>
         </is>
       </c>
     </row>
@@ -95449,17 +95519,17 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>كوثرية السياد</t>
+          <t>عين التينه</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>قرى صيدا</t>
+          <t>قضاءي البقاع الغربي وراشيا</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>الجنوب</t>
+          <t>البقاع</t>
         </is>
       </c>
     </row>
@@ -95471,7 +95541,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>الروضة</t>
+          <t>كفردنيس</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
@@ -95493,7 +95563,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>الشبرقية</t>
+          <t>كفرقوق</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
@@ -95515,7 +95585,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>عين التينه</t>
+          <t>محيدثه</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -95537,17 +95607,17 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>كفردنيس</t>
+          <t>الانصار</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>قضاءي البقاع الغربي وراشيا</t>
+          <t>قضاءي بعلبك والهرمل</t>
         </is>
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>البقاع</t>
+          <t>بعلبك والهرمل</t>
         </is>
       </c>
     </row>
@@ -95559,17 +95629,17 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>كفرقوق</t>
+          <t>البرانيه حي المسيحيين</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>قضاءي البقاع الغربي وراشيا</t>
+          <t>قضاءي بعلبك والهرمل</t>
         </is>
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>البقاع</t>
+          <t>بعلبك والهرمل</t>
         </is>
       </c>
     </row>
@@ -95581,17 +95651,17 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>محيدثه</t>
+          <t>البرباره محلة المسيحيين</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>قضاءي البقاع الغربي وراشيا</t>
+          <t>قضاءي بعلبك والهرمل</t>
         </is>
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>البقاع</t>
+          <t>بعلبك والهرمل</t>
         </is>
       </c>
     </row>
@@ -95603,7 +95673,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>الانصار</t>
+          <t>البويضة</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
@@ -95625,7 +95695,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>البرانيه حي المسيحيين</t>
+          <t>البويضة الحي الغربي</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
@@ -95647,7 +95717,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>البرباره محلة المسيحيين</t>
+          <t>البويضة الشمالية</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
@@ -95669,7 +95739,7 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>البويضة</t>
+          <t>التوفيقيه</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
@@ -95691,7 +95761,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>البويضة الحي الغربي</t>
+          <t>الجوبانية</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
@@ -95713,7 +95783,7 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>البويضة الشمالية</t>
+          <t>الحدث الشمالي</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
@@ -95735,7 +95805,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>التوفيقيه</t>
+          <t>الحدث الغربي</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
@@ -95757,7 +95827,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>الجوبانية</t>
+          <t>الحريقه</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
@@ -95779,7 +95849,7 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>الحدث الشمالي</t>
+          <t>الحلانيه</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
@@ -95801,7 +95871,7 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>الحدث الغربي</t>
+          <t>الريش حي الشرقي</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
@@ -95823,7 +95893,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>الحريقه</t>
+          <t>الريش حي الشميس</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
@@ -95845,7 +95915,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>الحلانيه</t>
+          <t>الريش حي الغربي</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
@@ -95867,7 +95937,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>الريش حي الشرقي</t>
+          <t>الزرازير</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
@@ -95889,7 +95959,7 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>الريش حي الشميس</t>
+          <t>الزويتيني</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
@@ -95911,7 +95981,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>الريش حي الغربي</t>
+          <t>السعيده</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
@@ -95933,7 +96003,7 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>الزرازير</t>
+          <t>السويسة</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
@@ -95955,7 +96025,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>الزويتيني</t>
+          <t>الشواغير التحتا</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
@@ -95977,7 +96047,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>السعيده</t>
+          <t>الشواغير الفوقا</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
@@ -95999,7 +96069,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>السويسة</t>
+          <t>الصوانية</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
@@ -96021,7 +96091,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>الشواغير التحتا</t>
+          <t>العقيدية</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
@@ -96043,7 +96113,7 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>الشواغير الفوقا</t>
+          <t>العلاق</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
@@ -96065,7 +96135,7 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>الصوانية</t>
+          <t>الفاكهة حي الجامع</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
@@ -96087,7 +96157,7 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>العقيدية</t>
+          <t>الفاكهة حي مار جرجس</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
@@ -96109,7 +96179,7 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>العلاق</t>
+          <t>القدام</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
@@ -96131,7 +96201,7 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>الفاكهة حي الجامع</t>
+          <t>القرينة</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
@@ -96153,7 +96223,7 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>الفاكهة حي مار جرجس</t>
+          <t>القصر</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
@@ -96175,7 +96245,7 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>القدام</t>
+          <t>الكواخ</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
@@ -96197,7 +96267,7 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>القرينة</t>
+          <t>المعاصر</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
@@ -96219,7 +96289,7 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>القصر</t>
+          <t>النبي رشاده</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
@@ -96241,7 +96311,7 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>الكواخ</t>
+          <t>النبي نعام</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
@@ -96263,7 +96333,7 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>المعاصر</t>
+          <t>النقرة</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
@@ -96285,7 +96355,7 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>النبي رشاده</t>
+          <t>بريصا</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
@@ -96307,7 +96377,7 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>النبي نعام</t>
+          <t>بيت ابو صليبي</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
@@ -96329,7 +96399,7 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>النقرة</t>
+          <t>جوار الحشيش</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
@@ -96351,7 +96421,7 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>بريصا</t>
+          <t>حوش السيد علي</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
@@ -96373,7 +96443,7 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>بيت ابو صليبي</t>
+          <t>حي الزهراء</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
@@ -96395,7 +96465,7 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>جوار الحشيش</t>
+          <t>حي الصلح</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
@@ -96417,7 +96487,7 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>حوش السيد علي</t>
+          <t>حي العباسية</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
@@ -96439,7 +96509,7 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>حي الزهراء</t>
+          <t>حي عز الدين</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
@@ -96461,7 +96531,7 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>حي الصلح</t>
+          <t>دار الواسعة</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
@@ -96483,7 +96553,7 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>حي العباسية</t>
+          <t>رماسا</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
@@ -96505,7 +96575,7 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>حي عز الدين</t>
+          <t>سهلات الماء</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
@@ -96527,7 +96597,7 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>دار الواسعة</t>
+          <t>شعت حي الضهر</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
@@ -96549,7 +96619,7 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>رماسا</t>
+          <t>صفرا</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
@@ -96571,7 +96641,7 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>سهلات الماء</t>
+          <t>غفره</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
@@ -96593,7 +96663,7 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>شعت حي الضهر</t>
+          <t>فلاوي</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
@@ -96615,7 +96685,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>صفرا</t>
+          <t>فيسان</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
@@ -96637,7 +96707,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>غفره</t>
+          <t>قبة دورس</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
@@ -96659,7 +96729,7 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>فلاوي</t>
+          <t>قلد السبع</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
@@ -96681,7 +96751,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>فيسان</t>
+          <t>قلعة</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
@@ -96703,7 +96773,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>قبة دورس</t>
+          <t>قلعة غربي</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
@@ -96725,7 +96795,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>قلد السبع</t>
+          <t>قنافذ</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
@@ -96747,7 +96817,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>قلعة</t>
+          <t>كفردبش</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
@@ -96769,7 +96839,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>قلعة غربي</t>
+          <t>مراح العين</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
@@ -96791,7 +96861,7 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>قنافذ</t>
+          <t>مزرعة آل سويدان</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
@@ -96813,7 +96883,7 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>كفردبش</t>
+          <t>مزرعة ابو صليبي</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
@@ -96835,7 +96905,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>مراح العين</t>
+          <t>مزرعة التوت</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
@@ -96857,7 +96927,7 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>مزرعة آل سويدان</t>
+          <t>مزرعة الضليل</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
@@ -96879,7 +96949,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>مزرعة ابو صليبي</t>
+          <t>مزرعة الفقيه</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
@@ -96901,7 +96971,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>مزرعة التوت</t>
+          <t>مزرعة بيت الطشم</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
@@ -96923,7 +96993,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>مزرعة الضليل</t>
+          <t>مزرعة بيت مطر</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
@@ -96945,7 +97015,7 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>مزرعة الفقيه</t>
+          <t>مزرعة سجد</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
@@ -96967,7 +97037,7 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>مزرعة بيت الطشم</t>
+          <t>مصنع الزهرة</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
@@ -96989,7 +97059,7 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>مزرعة بيت مطر</t>
+          <t>وادي التركمان</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
@@ -97011,7 +97081,7 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>مزرعة سجد</t>
+          <t>وادي الرطل</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
@@ -97033,7 +97103,7 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>مصنع الزهرة</t>
+          <t>وادي الزين</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
@@ -97055,7 +97125,7 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>وادي التركمان</t>
+          <t>وادي الصفا الشرقي</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
@@ -97077,7 +97147,7 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>وادي الرطل</t>
+          <t>وادي المشمشه</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
@@ -97099,7 +97169,7 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>وادي الزين</t>
+          <t>وادي النيرة</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
@@ -97121,7 +97191,7 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>وادي الصفا الشرقي</t>
+          <t>وادي بنيت</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
@@ -97143,17 +97213,17 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>وادي المشمشه</t>
+          <t>الجديدة حي السراي</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>قضاءي بعلبك والهرمل</t>
+          <t>قضاءي مرجعيون وحاصبيا</t>
         </is>
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>بعلبك والهرمل</t>
+          <t>النبطية</t>
         </is>
       </c>
     </row>
@@ -97165,17 +97235,17 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>وادي النيرة</t>
+          <t>الجديدة حي العيون</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>قضاءي بعلبك والهرمل</t>
+          <t>قضاءي مرجعيون وحاصبيا</t>
         </is>
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>بعلبك والهرمل</t>
+          <t>النبطية</t>
         </is>
       </c>
     </row>
@@ -97187,17 +97257,17 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>وادي بنيت</t>
+          <t>الجديدة حي القلعة</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>قضاءي بعلبك والهرمل</t>
+          <t>قضاءي مرجعيون وحاصبيا</t>
         </is>
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>بعلبك والهرمل</t>
+          <t>النبطية</t>
         </is>
       </c>
     </row>
@@ -97209,7 +97279,7 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>الجديدة حي السراي</t>
+          <t>الجديدة حي المدارس</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
@@ -97231,7 +97301,7 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>الجديدة حي العيون</t>
+          <t>الفرديس</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
@@ -97253,7 +97323,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>الجديدة حي القلعة</t>
+          <t>الوزاني</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
@@ -97275,7 +97345,7 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>الجديدة حي المدارس</t>
+          <t>برج الملوك</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
@@ -97297,7 +97367,7 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>الفرديس</t>
+          <t>بويضة</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
@@ -97319,7 +97389,7 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>الوزاني</t>
+          <t>رب ثلاثين</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
@@ -97341,7 +97411,7 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>برج الملوك</t>
+          <t>سرده والعمره</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
@@ -97363,7 +97433,7 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>بويضة</t>
+          <t>عديسه</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
@@ -97385,7 +97455,7 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>رب ثلاثين</t>
+          <t>كفرشوبا</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
@@ -97407,17 +97477,17 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>سرده والعمره</t>
+          <t>السهيله</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>قضاءي مرجعيون وحاصبيا</t>
+          <t>كسروان</t>
         </is>
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>النبطية</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -97429,17 +97499,17 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>عديسه</t>
+          <t>النموره وكفر جريف</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>قضاءي مرجعيون وحاصبيا</t>
+          <t>كسروان</t>
         </is>
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>النبطية</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -97451,17 +97521,17 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>كفرشوبا</t>
+          <t>ساحل علما</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>قضاءي مرجعيون وحاصبيا</t>
+          <t>كسروان</t>
         </is>
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>النبطية</t>
+          <t>جبل لبنان</t>
         </is>
       </c>
     </row>
@@ -97473,7 +97543,7 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>السهيله</t>
+          <t>شوان والعبره</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
@@ -97495,7 +97565,7 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>النموره وكفر جريف</t>
+          <t>غزير القناة</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
@@ -97517,7 +97587,7 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>ساحل علما</t>
+          <t>غزير المعاملتين</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
@@ -97539,147 +97609,15 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>شوان والعبره</t>
+          <t>وادي النحلة</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>كسروان</t>
+          <t>مدينة طرابلس</t>
         </is>
       </c>
       <c r="D647" t="inlineStr">
-        <is>
-          <t>جبل لبنان</t>
-        </is>
-      </c>
-    </row>
-    <row r="648">
-      <c r="A648" t="inlineStr">
-        <is>
-          <t>Arabic</t>
-        </is>
-      </c>
-      <c r="B648" t="inlineStr">
-        <is>
-          <t>غزير القناة</t>
-        </is>
-      </c>
-      <c r="C648" t="inlineStr">
-        <is>
-          <t>كسروان</t>
-        </is>
-      </c>
-      <c r="D648" t="inlineStr">
-        <is>
-          <t>جبل لبنان</t>
-        </is>
-      </c>
-    </row>
-    <row r="649">
-      <c r="A649" t="inlineStr">
-        <is>
-          <t>Arabic</t>
-        </is>
-      </c>
-      <c r="B649" t="inlineStr">
-        <is>
-          <t>غزير المعاملتين</t>
-        </is>
-      </c>
-      <c r="C649" t="inlineStr">
-        <is>
-          <t>كسروان</t>
-        </is>
-      </c>
-      <c r="D649" t="inlineStr">
-        <is>
-          <t>جبل لبنان</t>
-        </is>
-      </c>
-    </row>
-    <row r="650">
-      <c r="A650" t="inlineStr">
-        <is>
-          <t>Arabic</t>
-        </is>
-      </c>
-      <c r="B650" t="inlineStr">
-        <is>
-          <t>الزاهرية</t>
-        </is>
-      </c>
-      <c r="C650" t="inlineStr">
-        <is>
-          <t>مدينة طرابلس</t>
-        </is>
-      </c>
-      <c r="D650" t="inlineStr">
-        <is>
-          <t>الشمال</t>
-        </is>
-      </c>
-    </row>
-    <row r="651">
-      <c r="A651" t="inlineStr">
-        <is>
-          <t>Arabic</t>
-        </is>
-      </c>
-      <c r="B651" t="inlineStr">
-        <is>
-          <t>السويقه</t>
-        </is>
-      </c>
-      <c r="C651" t="inlineStr">
-        <is>
-          <t>مدينة طرابلس</t>
-        </is>
-      </c>
-      <c r="D651" t="inlineStr">
-        <is>
-          <t>الشمال</t>
-        </is>
-      </c>
-    </row>
-    <row r="652">
-      <c r="A652" t="inlineStr">
-        <is>
-          <t>Arabic</t>
-        </is>
-      </c>
-      <c r="B652" t="inlineStr">
-        <is>
-          <t>القبة</t>
-        </is>
-      </c>
-      <c r="C652" t="inlineStr">
-        <is>
-          <t>مدينة طرابلس</t>
-        </is>
-      </c>
-      <c r="D652" t="inlineStr">
-        <is>
-          <t>الشمال</t>
-        </is>
-      </c>
-    </row>
-    <row r="653">
-      <c r="A653" t="inlineStr">
-        <is>
-          <t>Arabic</t>
-        </is>
-      </c>
-      <c r="B653" t="inlineStr">
-        <is>
-          <t>وادي النحلة</t>
-        </is>
-      </c>
-      <c r="C653" t="inlineStr">
-        <is>
-          <t>مدينة طرابلس</t>
-        </is>
-      </c>
-      <c r="D653" t="inlineStr">
         <is>
           <t>الشمال</t>
         </is>
